--- a/tables/N-Retention/Local_perf_matrix_protection_False_vo_False_CUE_False.xlsx
+++ b/tables/N-Retention/Local_perf_matrix_protection_False_vo_False_CUE_False.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -668,28 +668,28 @@
         <v>0.01736455621136393</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5553102597959685</v>
+        <v>0.5642466039963522</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5530673431724717</v>
+        <v>0.5600604317922732</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3054742950927372</v>
+        <v>0.3115413050704156</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04137256263972743</v>
+        <v>0.04316546565134319</v>
       </c>
       <c r="O2" t="n">
-        <v>4.403789484409526</v>
+        <v>4.470333763738433</v>
       </c>
       <c r="P2" t="n">
-        <v>4.387084161400733</v>
+        <v>4.439163888185504</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9923922211296556</v>
+        <v>0.9928303656964881</v>
       </c>
       <c r="R2" t="n">
-        <v>0.005361575398851574</v>
+        <v>0.005204895081949752</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
@@ -699,38 +699,38 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.9884161411632302</v>
+        <v>0.9900361442677965</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007805102785072749</v>
+        <v>0.007238785599476895</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>0.9995828078576297</v>
+        <v>0.9996418919322152</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0001343954152107312</v>
+        <v>0.0001245155083495076</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>0.9965986802853406</v>
+        <v>0.9967185295930294</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.002460753450957183</v>
+        <v>0.002417010965324996</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>0.9632642967023151</v>
+        <v>0.9626874346096489</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.008155736048597297</v>
+        <v>0.008219521528311862</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>0.9285215391227373</v>
+        <v>0.9324701748037454</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0008045379153514032</v>
+        <v>0.0007819999628291574</v>
       </c>
       <c r="AN2" t="inlineStr"/>
     </row>
@@ -772,28 +772,28 @@
         <v>0.02342462405894816</v>
       </c>
       <c r="K3" t="n">
-        <v>0.543211050881103</v>
+        <v>0.5500633872661924</v>
       </c>
       <c r="L3" t="n">
-        <v>0.543968232079016</v>
+        <v>0.5568990549743057</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4799164286561859</v>
+        <v>0.9969047014159728</v>
       </c>
       <c r="N3" t="n">
-        <v>0.14709881341085</v>
+        <v>0.9935845596183941</v>
       </c>
       <c r="O3" t="n">
-        <v>4.313657841931784</v>
+        <v>4.364708589435769</v>
       </c>
       <c r="P3" t="n">
-        <v>4.319299543791253</v>
+        <v>4.415621198484515</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9880753307992648</v>
+        <v>0.9879759116995286</v>
       </c>
       <c r="R3" t="n">
-        <v>0.006640380099522415</v>
+        <v>0.006668003938890086</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
@@ -803,38 +803,38 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9784453490099697</v>
+        <v>0.9787807615872389</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.009434047085027692</v>
+        <v>0.00936035754344834</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>0.9999916761879417</v>
+        <v>-1.057186228100539</v>
       </c>
       <c r="AD3" t="n">
-        <v>7.064882236709783e-06</v>
+        <v>0.003512210996364732</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>0.9643265692633654</v>
+        <v>0.9640213864734405</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.009160504711879455</v>
+        <v>0.009199604886482747</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>0.953015963219692</v>
+        <v>0.9621069258529816</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.005256845030235407</v>
+        <v>0.004720955755810866</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>0.6861743877459707</v>
+        <v>0.7158513143953831</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.002285712022423698</v>
+        <v>0.002174954349716137</v>
       </c>
       <c r="AN3" t="inlineStr"/>
     </row>
@@ -876,28 +876,28 @@
         <v>0.001786449637055907</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5609844350785387</v>
+        <v>0.5593743245998097</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5561183073282349</v>
+        <v>0.5642265507449217</v>
       </c>
       <c r="M4" t="n">
-        <v>0.447696239265903</v>
+        <v>0.3976351111137273</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05693065188325196</v>
+        <v>0.0476639932013033</v>
       </c>
       <c r="O4" t="n">
-        <v>4.446044591924739</v>
+        <v>4.434055121667282</v>
       </c>
       <c r="P4" t="n">
-        <v>4.409801859444107</v>
+        <v>4.470183147467676</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9175278750020083</v>
+        <v>0.9300663600145919</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01878614463972518</v>
+        <v>0.01729924446944472</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -907,38 +907,38 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>0.8718014598930679</v>
+        <v>0.9108761258733526</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03152674544845425</v>
+        <v>0.0262866128401436</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0.9989780933261744</v>
+        <v>0.9985733007969231</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0003978447470010283</v>
+        <v>0.0004700826471958413</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>0.4413979630390418</v>
+        <v>0.4286801650323083</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02432532521891598</v>
+        <v>0.02460067643119307</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0.9669070355332233</v>
+        <v>0.9444163706116997</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.007545719933989867</v>
+        <v>0.009779266826449634</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>0.8342738559132857</v>
+        <v>0.8207175031984019</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.002062976842688117</v>
+        <v>0.002145693995884795</v>
       </c>
       <c r="AN4" t="inlineStr"/>
     </row>
@@ -980,28 +980,28 @@
         <v>0.03029424940398749</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5465143135659691</v>
+        <v>0.5455450639454225</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5557941184821144</v>
+        <v>0.5561727268014236</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2985280202696864</v>
+        <v>0.2956961141435077</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04405903580963149</v>
+        <v>0.04353140792920152</v>
       </c>
       <c r="O5" t="n">
-        <v>4.338269228295625</v>
+        <v>4.3310480335764</v>
       </c>
       <c r="P5" t="n">
-        <v>4.407390840640833</v>
+        <v>4.410210185213942</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9972688116295111</v>
+        <v>0.9972489848169036</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003093239640619139</v>
+        <v>0.003104446883283346</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -1011,38 +1011,38 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>0.9945354936084487</v>
+        <v>0.9944887057469326</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.005294721257406647</v>
+        <v>0.005317340013197305</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>0.9999312913133951</v>
+        <v>0.9999540343022505</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.108118229650735e-05</v>
+        <v>4.178034729557198e-05</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>0.9974146627965961</v>
+        <v>0.9974327082621375</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.002363593992122069</v>
+        <v>0.002355330690529882</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>0.9904615925397102</v>
+        <v>0.9903471913824016</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.003247217483378835</v>
+        <v>0.00326663257940252</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>0.9777146114821449</v>
+        <v>0.9778428152075118</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0006960384694889258</v>
+        <v>0.0006940334913633781</v>
       </c>
       <c r="AN5" t="inlineStr"/>
     </row>
@@ -1084,28 +1084,28 @@
         <v>0.01850467691463906</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5579375908730039</v>
+        <v>0.5529797707778151</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5654283947546263</v>
+        <v>0.5586029469598892</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9958820455685092</v>
+        <v>0.3222223782457707</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9928189648054001</v>
+        <v>0.07547153673851013</v>
       </c>
       <c r="O6" t="n">
-        <v>4.423356086505447</v>
+        <v>4.386431974980576</v>
       </c>
       <c r="P6" t="n">
-        <v>4.47913091014173</v>
+        <v>4.428309714956633</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9791715026732385</v>
+        <v>0.9802776578016524</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008724475894725995</v>
+        <v>0.008489646803062814</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -1115,38 +1115,38 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>0.9640059738668267</v>
+        <v>0.9747679560460246</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01094355555609834</v>
+        <v>0.009162615230539909</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>-1.052399706356037</v>
+        <v>0.9999912811409317</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.003826332795191352</v>
+        <v>7.886450777379478e-06</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>0.983888350912395</v>
+        <v>0.9839624732715443</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.005206111770747372</v>
+        <v>0.005194122491021331</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>0.8128758353898308</v>
+        <v>0.7876673446288028</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01405335055436965</v>
+        <v>0.01497005299893108</v>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>0.8040552718550399</v>
+        <v>0.7639236147119302</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.00104308201327847</v>
+        <v>0.001144927372073617</v>
       </c>
       <c r="AN6" t="inlineStr"/>
     </row>
@@ -1188,28 +1188,28 @@
         <v>0.01739226579276497</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5443964843424103</v>
+        <v>0.5559179333411531</v>
       </c>
       <c r="L7" t="n">
-        <v>0.539369348359546</v>
+        <v>0.5558627807473355</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9971673100175726</v>
+        <v>0.5709597665635073</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9911296748856896</v>
+        <v>0.1535577457270393</v>
       </c>
       <c r="O7" t="n">
-        <v>4.322490428799298</v>
+        <v>4.408315197949928</v>
       </c>
       <c r="P7" t="n">
-        <v>4.285027450735387</v>
+        <v>4.407904079674585</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9726843049440004</v>
+        <v>0.9723637397464224</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01004192569923113</v>
+        <v>0.01010067768112661</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -1219,38 +1219,38 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>0.9448060608792204</v>
+        <v>0.9402764797245806</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01782490117334124</v>
+        <v>0.01854189574058069</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>-1.032359569609413</v>
+        <v>0.9999993816223586</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.006150454745413989</v>
+        <v>3.392609260420041e-06</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>0.9371096847039608</v>
+        <v>0.933763054346792</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.009997403497909996</v>
+        <v>0.01025995565312062</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>0.973629386778017</v>
+        <v>0.9749701057516975</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.00427625543520108</v>
+        <v>0.004166132057610829</v>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>0.6624555675013343</v>
+        <v>0.6524941662225709</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.003067191988016402</v>
+        <v>0.003112121446456149</v>
       </c>
       <c r="AN7" t="inlineStr"/>
     </row>
@@ -1292,28 +1292,28 @@
         <v>0.02806021357785015</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5541896777331705</v>
+        <v>0.5696724953710857</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5423816672738454</v>
+        <v>0.5582304145031345</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5567940097716422</v>
+        <v>0.5656129037576733</v>
       </c>
       <c r="N8" t="n">
-        <v>0.117974823599734</v>
+        <v>0.123469185332697</v>
       </c>
       <c r="O8" t="n">
-        <v>4.395443563473687</v>
+        <v>4.510727168591731</v>
       </c>
       <c r="P8" t="n">
-        <v>4.307474491821922</v>
+        <v>4.42553379663859</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9911496087810079</v>
+        <v>0.9912273778190596</v>
       </c>
       <c r="R8" t="n">
-        <v>0.005068145899477109</v>
+        <v>0.005045829682511346</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -1323,38 +1323,38 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>0.9873858314936673</v>
+        <v>0.9879209337806626</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.007494366841184998</v>
+        <v>0.007333686055246319</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>0.999911209262628</v>
+        <v>0.9999499565778071</v>
       </c>
       <c r="AD8" t="n">
-        <v>6.185017438956952e-05</v>
+        <v>4.643341202094378e-05</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>0.9841732096936305</v>
+        <v>0.9842187517718755</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.006229525296006442</v>
+        <v>0.00622055601322734</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>0.9865432231898944</v>
+        <v>0.9857714815979933</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.004911933731845199</v>
+        <v>0.005050819101523772</v>
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>0.9425711698573811</v>
+        <v>0.9381952946474335</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0008753953163458127</v>
+        <v>0.0009081341428959874</v>
       </c>
       <c r="AN8" t="inlineStr"/>
     </row>
@@ -1396,28 +1396,28 @@
         <v>0.03857825619785213</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5446247616500003</v>
+        <v>0.5453351465816443</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5533796251842628</v>
+        <v>0.556554213922496</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4860633718071323</v>
+        <v>0.4828014850071219</v>
       </c>
       <c r="N9" t="n">
-        <v>0.09782281391573035</v>
+        <v>0.09699572675597476</v>
       </c>
       <c r="O9" t="n">
-        <v>4.324191261447337</v>
+        <v>4.329484052021317</v>
       </c>
       <c r="P9" t="n">
-        <v>4.389408798389304</v>
+        <v>4.413051445738119</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9959230382307875</v>
+        <v>0.995969469611047</v>
       </c>
       <c r="R9" t="n">
-        <v>0.00345326562879456</v>
+        <v>0.003433545180892337</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -1427,38 +1427,38 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>0.9936554947153767</v>
+        <v>0.9939044813677833</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.005749277911363593</v>
+        <v>0.005635335178453466</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>0.9999896345577026</v>
+        <v>0.9999854215510335</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.843833543779749e-05</v>
+        <v>2.186671038014954e-05</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>0.9996851774566335</v>
+        <v>0.9996751176891397</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0007179611339318488</v>
+        <v>0.000729341718533743</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>0.9846574114569796</v>
+        <v>0.9842085349449278</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.004673594460143994</v>
+        <v>0.004741469022100936</v>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>0.9934210059578494</v>
+        <v>0.9932051596523748</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0004876745801286739</v>
+        <v>0.0004956099315675032</v>
       </c>
       <c r="AN9" t="inlineStr"/>
     </row>
@@ -1500,28 +1500,28 @@
         <v>0.033842442806071</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5232820486869063</v>
+        <v>0.5415086286978176</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5225359771079994</v>
+        <v>0.5458309682770885</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3896311851257893</v>
+        <v>0.3986701795954545</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05556153712080843</v>
+        <v>0.05992434306972079</v>
       </c>
       <c r="O10" t="n">
-        <v>4.165105484036478</v>
+        <v>4.300972493242484</v>
       </c>
       <c r="P10" t="n">
-        <v>4.15954151520474</v>
+        <v>4.333177849306642</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9851089459102219</v>
+        <v>0.9854271349723449</v>
       </c>
       <c r="R10" t="n">
-        <v>0.007751629887334067</v>
+        <v>0.00766836505128327</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1531,38 +1531,38 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>0.981984296975733</v>
+        <v>0.9823762407769263</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01187235006681965</v>
+        <v>0.01174249440687682</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0.9999355617688758</v>
+        <v>0.9999433595113485</v>
       </c>
       <c r="AD10" t="n">
-        <v>6.709586951525456e-05</v>
+        <v>6.290533449707162e-05</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>0.9241120894742566</v>
+        <v>0.9257446684795817</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01126406583060594</v>
+        <v>0.01114224498330956</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>0.9681558177871215</v>
+        <v>0.9679127369888821</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.002823347833231662</v>
+        <v>0.002834103281497369</v>
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>0.8774057360646172</v>
+        <v>0.8842271591027899</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.00214555467834359</v>
+        <v>0.002085008629297619</v>
       </c>
       <c r="AN10" t="inlineStr"/>
     </row>
@@ -1604,28 +1604,28 @@
         <v>0.02959337905881725</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5138467452580261</v>
+        <v>0.5232073771356348</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5274032161299249</v>
+        <v>0.5438853471604912</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5084850491162495</v>
+        <v>0.5083450037344445</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1003432946221131</v>
+        <v>0.1033850603426523</v>
       </c>
       <c r="O11" t="n">
-        <v>4.094730808965064</v>
+        <v>4.164548646870926</v>
       </c>
       <c r="P11" t="n">
-        <v>4.195831719563943</v>
+        <v>4.318675838034389</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.973398620141506</v>
+        <v>0.9732819856645946</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01213371066205197</v>
+        <v>0.01216028186135488</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
@@ -1635,38 +1635,38 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>0.9579959755259371</v>
+        <v>0.957795624283472</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0256245348807678</v>
+        <v>0.02568557427021327</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>0.9999956235968698</v>
+        <v>0.9999970036279392</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.473517712697742e-05</v>
+        <v>1.219255070018111e-05</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>0.9508342596882785</v>
+        <v>0.9509628516722497</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.003930521278518168</v>
+        <v>0.003925377814322443</v>
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>0.8864401346591089</v>
+        <v>0.8869736977496876</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.003786740162782746</v>
+        <v>0.003777833654889559</v>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>0.9635759079403043</v>
+        <v>0.9642268614891987</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0008085147831290847</v>
+        <v>0.000801257522120928</v>
       </c>
       <c r="AN11" t="inlineStr"/>
     </row>
@@ -1708,28 +1708,28 @@
         <v>0.0207241649964606</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5090733310675523</v>
+        <v>0.4987727432373008</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5119180867522365</v>
+        <v>0.5383950290610813</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7601605624591168</v>
+        <v>0.7487064795573467</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3125216263403952</v>
+        <v>0.3185967204065523</v>
       </c>
       <c r="O12" t="n">
-        <v>4.059116436759205</v>
+        <v>3.982237472851483</v>
       </c>
       <c r="P12" t="n">
-        <v>4.080341936104141</v>
+        <v>4.277758912669679</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.9478352124999335</v>
+        <v>0.947437558166937</v>
       </c>
       <c r="R12" t="n">
-        <v>0.02485713263664516</v>
+        <v>0.02495169623840094</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
@@ -1739,38 +1739,38 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>0.7073834332469211</v>
+        <v>0.7052580634734094</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.05347174507131902</v>
+        <v>0.05366558510878599</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>0.9999943882733603</v>
+        <v>0.9999879060034488</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.563131548690477e-06</v>
+        <v>8.166876649055178e-06</v>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
-        <v>0.9842095695900901</v>
+        <v>0.9833717895763443</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.004751607187476589</v>
+        <v>0.004876029252967263</v>
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>0.9174773246574314</v>
+        <v>0.9158445769773014</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.001248077452980644</v>
+        <v>0.001260363860230257</v>
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>0.9845581280581071</v>
+        <v>0.9884096156565162</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0002513771597763711</v>
+        <v>0.0002177833934109597</v>
       </c>
       <c r="AN12" t="inlineStr"/>
     </row>
@@ -1812,28 +1812,28 @@
         <v>0.05578662037324268</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5435255052404684</v>
+        <v>0.5485841142950727</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5398083553074149</v>
+        <v>0.5653524252994078</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5010033979554966</v>
+        <v>0.4766883541347894</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1809868599840367</v>
+        <v>0.1744981835547542</v>
       </c>
       <c r="O13" t="n">
-        <v>4.316000860305166</v>
+        <v>4.353688955519708</v>
       </c>
       <c r="P13" t="n">
-        <v>4.288300737059664</v>
+        <v>4.478562639926059</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9959625446713499</v>
+        <v>0.9959027740660206</v>
       </c>
       <c r="R13" t="n">
-        <v>0.00363619019216607</v>
+        <v>0.00366300644198031</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
@@ -1843,38 +1843,38 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>0.263173863702668</v>
+        <v>0.2511616036557029</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.006767733872961714</v>
+        <v>0.006822677036309507</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>0.9291108557399124</v>
+        <v>0.9296560921948005</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0002039017276599606</v>
+        <v>0.0002031160696128928</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
-        <v>0.6902977134487098</v>
+        <v>0.6914577501947159</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.003979550848016771</v>
+        <v>0.003972090851091277</v>
       </c>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>0.9996470990791189</v>
+        <v>0.9993451484223673</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0007589449446753003</v>
+        <v>0.001033844723912316</v>
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>0.962602450160133</v>
+        <v>0.9645555570890871</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.001962848821801693</v>
+        <v>0.001910906132687272</v>
       </c>
       <c r="AN13" t="inlineStr"/>
     </row>
@@ -1916,28 +1916,28 @@
         <v>0.008819171744597891</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5453363230856951</v>
+        <v>0.5536207568821497</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5461973662132655</v>
+        <v>0.5572253833098649</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8972195079149219</v>
+        <v>0.9005092186999272</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8275194171204551</v>
+        <v>0.8346438116004949</v>
       </c>
       <c r="O14" t="n">
-        <v>4.329492817556477</v>
+        <v>4.39120619674625</v>
       </c>
       <c r="P14" t="n">
-        <v>4.335907849498072</v>
+        <v>4.418051540750579</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9750988932962109</v>
+        <v>0.9758866962106585</v>
       </c>
       <c r="R14" t="n">
-        <v>0.00939733038287162</v>
+        <v>0.009247482748847456</v>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
@@ -1947,38 +1947,38 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>0.8897260454809109</v>
+        <v>0.8962303159519627</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01651086770166907</v>
+        <v>0.01601653880184001</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>0.9614806109789685</v>
+        <v>0.9614806109789515</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0009625122855061652</v>
+        <v>0.0009625122855063774</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
-        <v>0.9849724804964495</v>
+        <v>0.9849845292746786</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.005298007302351099</v>
+        <v>0.005295882955898474</v>
       </c>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>0.7299024075255995</v>
+        <v>0.725763918075617</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.01174396094047176</v>
+        <v>0.01183359057656408</v>
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>0.4806231746466632</v>
+        <v>0.4757257212978004</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.001422817456791014</v>
+        <v>0.001429509931492915</v>
       </c>
       <c r="AN14" t="inlineStr"/>
     </row>
@@ -2020,28 +2020,28 @@
         <v>0.02024626170970604</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5359698083557878</v>
+        <v>0.512220023929174</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5467394642119179</v>
+        <v>0.5472466657528773</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2456022085799998</v>
+        <v>0.2054544340532677</v>
       </c>
       <c r="N15" t="n">
-        <v>0.03342822512588114</v>
+        <v>0.02732880500144134</v>
       </c>
       <c r="O15" t="n">
-        <v>4.259694900513283</v>
+        <v>4.082594718855475</v>
       </c>
       <c r="P15" t="n">
-        <v>4.33994462759292</v>
+        <v>4.343708182579936</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.9794039101164713</v>
+        <v>0.9796688837151163</v>
       </c>
       <c r="R15" t="n">
-        <v>0.00758430903823341</v>
+        <v>0.007535364136179344</v>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
@@ -2051,38 +2051,38 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>0.9473022963183706</v>
+        <v>0.9488242111984214</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01130371085120413</v>
+        <v>0.01113928888121617</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>-1.742894624875848</v>
+        <v>-1.700885672526133</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.004333755939171458</v>
+        <v>0.00430044094977637</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="n">
-        <v>0.9237164109941166</v>
+        <v>0.9243393103573231</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.01011344490481206</v>
+        <v>0.01007206922145105</v>
       </c>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>0.8435386362261248</v>
+        <v>0.8326849008110861</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.004426929376334709</v>
+        <v>0.004577903203204117</v>
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
-        <v>0.9999986510870518</v>
+        <v>0.9999999465617552</v>
       </c>
       <c r="AM15" t="n">
-        <v>4.297850118533509e-06</v>
+        <v>8.554318119230041e-07</v>
       </c>
       <c r="AN15" t="inlineStr"/>
     </row>
@@ -2124,10 +2124,10 @@
         <v>0.01569855494294647</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5751444245764759</v>
+        <v>0.5547407510209782</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5874316999305738</v>
+        <v>0.5733753977865961</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.551455588325581</v>
+        <v>4.399547914881412</v>
       </c>
       <c r="P16" t="n">
-        <v>4.642881917668832</v>
+        <v>4.53828267416197</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.975122638547116</v>
+        <v>0.9757558264078261</v>
       </c>
       <c r="R16" t="n">
-        <v>0.009593223199481242</v>
+        <v>0.009470351170750822</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
@@ -2155,31 +2155,31 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>0.9948607139476633</v>
+        <v>0.9946929737023286</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.005284643225081933</v>
+        <v>0.005370193034839947</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>0.957976977481104</v>
+        <v>0.9590837394407519</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.004225098766462982</v>
+        <v>0.004169089230149025</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="n">
-        <v>0.9105516800513709</v>
+        <v>0.909418027163619</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.003591081248007135</v>
+        <v>0.003613765977076533</v>
       </c>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="n">
-        <v>0.8343470396335655</v>
+        <v>0.8395852168630731</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01844238572074455</v>
+        <v>0.01814845648655414</v>
       </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
@@ -2226,28 +2226,28 @@
         <v>0.07189096045701066</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5112182132599017</v>
+        <v>0.5024881191354954</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5287327068144865</v>
+        <v>0.5288586751569063</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4454190081494447</v>
+        <v>0.4340558664594968</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1586950397383495</v>
+        <v>0.1543382506437194</v>
       </c>
       <c r="O17" t="n">
-        <v>4.075120312358837</v>
+        <v>4.009971608901167</v>
       </c>
       <c r="P17" t="n">
-        <v>4.205736711259693</v>
+        <v>4.20666188061859</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9878100294134849</v>
+        <v>0.9881534027509168</v>
       </c>
       <c r="R17" t="n">
-        <v>0.005125053133220133</v>
+        <v>0.005052354965176604</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
@@ -2257,38 +2257,38 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>0.9709410180494122</v>
+        <v>0.9717219102085268</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.008575757968547813</v>
+        <v>0.008459746560558453</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>0.6376777806545382</v>
+        <v>0.6387246672313837</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.001861632856731224</v>
+        <v>0.001858941428806582</v>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="n">
-        <v>0.9929520867339228</v>
+        <v>0.992996618002341</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.002270418921658675</v>
+        <v>0.002263234891360768</v>
       </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
-        <v>-0.8459176166170412</v>
+        <v>-0.7835307476540299</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.006991816216421011</v>
+        <v>0.006872648732564511</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>0.9969939195161235</v>
+        <v>0.9972964487803031</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0005303304434419691</v>
+        <v>0.0005029369656487576</v>
       </c>
       <c r="AN17" t="inlineStr"/>
     </row>
@@ -2330,28 +2330,28 @@
         <v>0.03009288922194302</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5342617001777857</v>
+        <v>0.5490011313733419</v>
       </c>
       <c r="L18" t="n">
-        <v>0.534785322311127</v>
+        <v>0.5506707167572154</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2066086790791819</v>
+        <v>0.2144891651553351</v>
       </c>
       <c r="N18" t="n">
-        <v>0.03341697081850464</v>
+        <v>0.03642154007914782</v>
       </c>
       <c r="O18" t="n">
-        <v>4.246963527162229</v>
+        <v>4.356795527549973</v>
       </c>
       <c r="P18" t="n">
-        <v>4.250866430211788</v>
+        <v>4.369232563220775</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9844374197665723</v>
+        <v>0.9844596409725355</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006451777545722705</v>
+        <v>0.006447169778601816</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
@@ -2361,38 +2361,38 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>0.9256519656283986</v>
+        <v>0.925781813178142</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.0140025545483555</v>
+        <v>0.01399032159579558</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>0.8386582677868116</v>
+        <v>0.8262208064774124</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.001106321924178101</v>
+        <v>0.001148172259881364</v>
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.9973801157000624</v>
+        <v>0.9973241852381616</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.001536287343048318</v>
+        <v>0.001552599418118485</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="n">
-        <v>0.9703733125192392</v>
+        <v>0.9707421190050074</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.002895685478244862</v>
+        <v>0.00287760563031676</v>
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>0.9939117578427222</v>
+        <v>0.993566815617775</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.0002941296118067318</v>
+        <v>0.0003023470880712413</v>
       </c>
       <c r="AN18" t="inlineStr"/>
     </row>
@@ -2434,10 +2434,10 @@
         <v>0.01254934055241822</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5813650193172442</v>
+        <v>0.4773251588100098</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5870200882868084</v>
+        <v>0.557407236502968</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2446,16 +2446,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.597747250805167</v>
+        <v>3.82203959903637</v>
       </c>
       <c r="P19" t="n">
-        <v>4.660679921074324</v>
+        <v>4.419352345783507</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.986656482780438</v>
+        <v>0.9870541844013571</v>
       </c>
       <c r="R19" t="n">
-        <v>0.008138780003914483</v>
+        <v>0.008016574953401417</v>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
@@ -2465,38 +2465,38 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>0.6677641661662665</v>
+        <v>0.684894949120765</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.008582413441954023</v>
+        <v>0.008358221540882463</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>-0.03155798034056234</v>
+        <v>0.0339622334556906</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.003025895198384228</v>
+        <v>0.002928222768507439</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="n">
-        <v>0.7281412330183729</v>
+        <v>0.7305985674293305</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.01471638387524143</v>
+        <v>0.01464972211562931</v>
       </c>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="n">
-        <v>0.7610779460886306</v>
+        <v>0.7876202587310586</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.005639242197273458</v>
+        <v>0.005316785888196324</v>
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>0.9986159682653917</v>
+        <v>0.9987782105249791</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.000108768549580096</v>
+        <v>0.000102194730566972</v>
       </c>
       <c r="AN19" t="inlineStr"/>
     </row>
@@ -2538,28 +2538,28 @@
         <v>0.005481236733903614</v>
       </c>
       <c r="K20" t="n">
-        <v>0.574355127123015</v>
+        <v>0.5783758603000023</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5695122258681898</v>
+        <v>0.5737878378029928</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4062272361709381</v>
+        <v>0.4211378052355061</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1262615534836229</v>
+        <v>0.1374112956337796</v>
       </c>
       <c r="O20" t="n">
-        <v>4.545581196261954</v>
+        <v>4.575504098150747</v>
       </c>
       <c r="P20" t="n">
-        <v>4.509533253526445</v>
+        <v>4.541358413194546</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9759804519983738</v>
+        <v>0.9755804995114662</v>
       </c>
       <c r="R20" t="n">
-        <v>0.009098967650586504</v>
+        <v>0.009174408923704153</v>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
@@ -2569,38 +2569,38 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>0.8703038125402149</v>
+        <v>0.8647795136952487</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.01049136665598626</v>
+        <v>0.01071247217864532</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>0.6834186441708962</v>
+        <v>0.6825498641508045</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.003839294161081819</v>
+        <v>0.003844558553258426</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="n">
-        <v>0.9744291341576417</v>
+        <v>0.9741405335941882</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.004267048567844605</v>
+        <v>0.004291060609633838</v>
       </c>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
-        <v>0.7994023026178239</v>
+        <v>0.7979500153190703</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.01644733801744716</v>
+        <v>0.01650676836801308</v>
       </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>0.5255268678482636</v>
+        <v>0.5253865720811438</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.0006515184003031693</v>
+        <v>0.0006516147161024418</v>
       </c>
       <c r="AN20" t="inlineStr"/>
     </row>
@@ -2642,10 +2642,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5351911822574889</v>
+        <v>0.5119505968393867</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5529481507233011</v>
+        <v>0.5214040378706312</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2654,16 +2654,16 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.25389152450637</v>
+        <v>4.080584583903153</v>
       </c>
       <c r="P21" t="n">
-        <v>4.386184553673481</v>
+        <v>4.151092398028675</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.9812066993839685</v>
+        <v>0.9807245874358685</v>
       </c>
       <c r="R21" t="n">
-        <v>0.008921589401371274</v>
+        <v>0.009035299282911835</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
@@ -2673,38 +2673,38 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>0.9305211289508095</v>
+        <v>0.9293877291295994</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.01035414305198907</v>
+        <v>0.01043825431261878</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>0.9962220958117336</v>
+        <v>0.9960348199549983</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.00202890601960426</v>
+        <v>0.00207858561234625</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="n">
-        <v>0.5085856355751177</v>
+        <v>0.5037533632643423</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.01535439601547208</v>
+        <v>0.01542970426672279</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="n">
-        <v>0.8248039860214601</v>
+        <v>0.8043675129155022</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.007132796745293699</v>
+        <v>0.0075373420832216</v>
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>0.9861889728701395</v>
+        <v>0.9830011533144901</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.0001215847286627412</v>
+        <v>0.0001348887621392687</v>
       </c>
       <c r="AN21" t="inlineStr"/>
     </row>
@@ -2746,28 +2746,28 @@
         <v>0.02704531936448205</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5490391750829117</v>
+        <v>0.5268307831677946</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5545651530916513</v>
+        <v>0.5502395706595578</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2723648788345177</v>
+        <v>0.2371734845628231</v>
       </c>
       <c r="N22" t="n">
-        <v>0.07697426123460036</v>
+        <v>0.06531715824998359</v>
       </c>
       <c r="O22" t="n">
-        <v>4.357078932018656</v>
+        <v>4.191566915241262</v>
       </c>
       <c r="P22" t="n">
-        <v>4.398239473401946</v>
+        <v>4.366007210331949</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.9814971254077901</v>
+        <v>0.981778520680347</v>
       </c>
       <c r="R22" t="n">
-        <v>0.006876153077600934</v>
+        <v>0.006823665825279303</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
@@ -2777,38 +2777,38 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>0.8885745902457906</v>
+        <v>0.892625612258153</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.009841045409044614</v>
+        <v>0.009660496913106801</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>0.9072050582643829</v>
+        <v>0.9076380112991456</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.00168842564143216</v>
+        <v>0.001684482195522065</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="n">
-        <v>0.3369618258536772</v>
+        <v>0.3418877129747621</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.01123894509393277</v>
+        <v>0.01119711870660374</v>
       </c>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="n">
-        <v>0.9648980072452806</v>
+        <v>0.9604867993236423</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.002682702006537262</v>
+        <v>0.002846280209049821</v>
       </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="n">
-        <v>0.8209941686896018</v>
+        <v>0.8225078020850068</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.00178876297009017</v>
+        <v>0.001781184224621996</v>
       </c>
       <c r="AN22" t="inlineStr"/>
     </row>
@@ -2850,28 +2850,28 @@
         <v>0.0237900385797033</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5152447668645552</v>
+        <v>0.484531289021057</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5284163059789408</v>
+        <v>0.5341169703775777</v>
       </c>
       <c r="M23" t="n">
-        <v>0.359756821032886</v>
+        <v>0.3059299700505546</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1115600279407888</v>
+        <v>0.100233206885056</v>
       </c>
       <c r="O23" t="n">
-        <v>4.105159995358824</v>
+        <v>3.875883377277486</v>
       </c>
       <c r="P23" t="n">
-        <v>4.203384894277518</v>
+        <v>4.245845263686942</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9802563570435707</v>
+        <v>0.9807992217311796</v>
       </c>
       <c r="R23" t="n">
-        <v>0.01051967198822108</v>
+        <v>0.01037404124332526</v>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -2881,38 +2881,38 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>0.8888426216888146</v>
+        <v>0.8918270714684264</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.02337342485896986</v>
+        <v>0.02305751497639328</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>-0.9835698289004924</v>
+        <v>-0.9802205738419052</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.001344957892539373</v>
+        <v>0.001343821933000081</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="n">
-        <v>0.9842178083935216</v>
+        <v>0.9853473260644688</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.002115944726354964</v>
+        <v>0.002038821034385091</v>
       </c>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="n">
-        <v>0.7694268447252266</v>
+        <v>0.8569640178500566</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.0007796007203253022</v>
+        <v>0.0006140313026391147</v>
       </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="n">
-        <v>0.9950889791945202</v>
+        <v>0.9947026274492846</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.0003264857731671716</v>
+        <v>0.0003390850424057322</v>
       </c>
       <c r="AN23" t="inlineStr"/>
     </row>
@@ -2954,10 +2954,10 @@
         <v>0.01655830938827357</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5248228924400306</v>
+        <v>0.5381273422429782</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5346619123675868</v>
+        <v>0.5469554563350643</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2966,16 +2966,16 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.176595398310353</v>
+        <v>4.275774819085798</v>
       </c>
       <c r="P24" t="n">
-        <v>4.249943635766656</v>
+        <v>4.341554147160157</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.9926767711312096</v>
+        <v>0.9926953288581162</v>
       </c>
       <c r="R24" t="n">
-        <v>0.005082038447477863</v>
+        <v>0.005075595189499516</v>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2985,31 +2985,31 @@
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>0.9990711816414876</v>
+        <v>0.9989979145197011</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.002445614290197801</v>
+        <v>0.002540241183442363</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>0.9612024084671005</v>
+        <v>0.9608443827013903</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.003109934748062506</v>
+        <v>0.003124251098636244</v>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="n">
-        <v>0.8432798990979502</v>
+        <v>0.8446192709595116</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.009755977409476171</v>
+        <v>0.009714199361370081</v>
       </c>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="n">
-        <v>0.9762159677482655</v>
+        <v>0.9769001235953902</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.001041959106340037</v>
+        <v>0.001026863601820317</v>
       </c>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         <v>0.05553965571423582</v>
       </c>
       <c r="K25" t="n">
-        <v>0.546176191779207</v>
+        <v>0.5494012369207484</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5474373258942006</v>
+        <v>0.5531651098141975</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3068,65 +3068,65 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.335750152080124</v>
+        <v>4.359776070804065</v>
       </c>
       <c r="P25" t="n">
-        <v>4.345145644667552</v>
+        <v>4.387811859846882</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.9827387291373857</v>
+        <v>0.9827869502360601</v>
       </c>
       <c r="R25" t="n">
-        <v>0.02178914927046165</v>
+        <v>0.02175869289332351</v>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
-        <v>-0.3178696900896567</v>
+        <v>-0.3143661111299618</v>
       </c>
       <c r="U25" t="n">
-        <v>0.04226582086109543</v>
+        <v>0.04220960126964817</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
-        <v>0.2715419016375845</v>
+        <v>0.2705704395949385</v>
       </c>
       <c r="X25" t="n">
-        <v>0.001082974965634676</v>
+        <v>0.001083696845556093</v>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>0.9025866658831153</v>
+        <v>0.9037293283445984</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.01075964932178874</v>
+        <v>0.01069635760359922</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>0.516909168050367</v>
+        <v>0.5155857894256859</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.003406138054026074</v>
+        <v>0.003410800249187533</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="n">
-        <v>0.9999935732209662</v>
+        <v>0.9999642980004979</v>
       </c>
       <c r="AG25" t="n">
-        <v>4.152746277530777e-05</v>
+        <v>9.787797672631068e-05</v>
       </c>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="n">
-        <v>0.99834042675764</v>
+        <v>0.9912692940008837</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.0002544449168657389</v>
+        <v>0.000583606673247077</v>
       </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="n">
-        <v>-0.06041086027544185</v>
+        <v>-0.06019105087399779</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.003409952638309039</v>
+        <v>0.003409599200541214</v>
       </c>
       <c r="AN25" t="inlineStr"/>
     </row>
@@ -3168,10 +3168,10 @@
         <v>0.05246774739927379</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5471977775578866</v>
+        <v>0.540731726273736</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5532293772499586</v>
+        <v>0.5490181805573094</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3180,65 +3180,65 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.343361074649197</v>
+        <v>4.295183238249074</v>
       </c>
       <c r="P26" t="n">
-        <v>4.388289853205311</v>
+        <v>4.35691974105193</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.979314812173351</v>
+        <v>0.9795222297738044</v>
       </c>
       <c r="R26" t="n">
-        <v>0.02210635105936981</v>
+        <v>0.02199523776444483</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
-        <v>0.2427630145943427</v>
+        <v>0.2503683661072617</v>
       </c>
       <c r="U26" t="n">
-        <v>0.04273358774231388</v>
+        <v>0.04251844761102798</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
-        <v>-0.6665875550631879</v>
+        <v>-0.6471722246888199</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0009049905024329322</v>
+        <v>0.0008997036024602547</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>0.9504715364084975</v>
+        <v>0.9509637374357274</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.01201517225632442</v>
+        <v>0.01195532135634414</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>-0.4571320571760833</v>
+        <v>-0.4457842790344297</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.004138979097333071</v>
+        <v>0.004122830932079933</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="n">
-        <v>0.9169771163994712</v>
+        <v>0.9173165762320066</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.003856845859956554</v>
+        <v>0.003848952943997378</v>
       </c>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="n">
-        <v>0.9916811813196229</v>
+        <v>0.9927408269512144</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.000775873208618261</v>
+        <v>0.0007247754950350273</v>
       </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="n">
-        <v>0.5370226430074407</v>
+        <v>0.5346525047973455</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.000942865176822287</v>
+        <v>0.0009452755193291395</v>
       </c>
       <c r="AN26" t="inlineStr"/>
     </row>
@@ -3280,10 +3280,10 @@
         <v>0.07321928484019485</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5184276146984496</v>
+        <v>0.5300735358050577</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5227981113404304</v>
+        <v>0.5351292280837466</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3292,65 +3292,65 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.128901529664978</v>
+        <v>4.215743336360242</v>
       </c>
       <c r="P27" t="n">
-        <v>4.161495752880196</v>
+        <v>4.253428619002744</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.9962385935324101</v>
+        <v>0.9962122268506304</v>
       </c>
       <c r="R27" t="n">
-        <v>0.009954129110999511</v>
+        <v>0.009988956378272563</v>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
-        <v>0.9038462785322294</v>
+        <v>0.9032455835895219</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0162781251649524</v>
+        <v>0.0163288926400523</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
-        <v>0.3568215206527713</v>
+        <v>0.3403901770992426</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0008987475938432298</v>
+        <v>0.0009101553906670243</v>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
-        <v>0.896409747478216</v>
+        <v>0.8956302996488192</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.01364799694266148</v>
+        <v>0.01369924677302828</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>0.8036552957432164</v>
+        <v>0.795753143896083</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.001620347645801288</v>
+        <v>0.001652632528219481</v>
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="n">
-        <v>0.8796028119280882</v>
+        <v>0.878561005675181</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.009693025851397544</v>
+        <v>0.009734872774329884</v>
       </c>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
-        <v>0.7165622915505249</v>
+        <v>0.7015923908315007</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.002868232465646778</v>
+        <v>0.002943001475169708</v>
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="n">
-        <v>0.4329737498948468</v>
+        <v>0.434080415220143</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.00490305564950791</v>
+        <v>0.004898268664987468</v>
       </c>
       <c r="AN27" t="inlineStr"/>
     </row>
@@ -3392,28 +3392,28 @@
         <v>0.02087465183044777</v>
       </c>
       <c r="K28" t="n">
-        <v>0.5215366498630084</v>
+        <v>0.5203824890675836</v>
       </c>
       <c r="L28" t="n">
-        <v>0.5227658022949631</v>
+        <v>0.5468676968391812</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2146253974333584</v>
+        <v>0.2358816670151607</v>
       </c>
       <c r="N28" t="n">
-        <v>0.02753274191369269</v>
+        <v>0.04142854948115181</v>
       </c>
       <c r="O28" t="n">
-        <v>4.152089315711887</v>
+        <v>4.143481723210112</v>
       </c>
       <c r="P28" t="n">
-        <v>4.161255495901893</v>
+        <v>4.340893939552014</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9512915469829644</v>
+        <v>0.9515815760435493</v>
       </c>
       <c r="R28" t="n">
-        <v>0.02298295271013748</v>
+        <v>0.02291442583235275</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
@@ -3425,38 +3425,38 @@
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>0.6696732244720467</v>
+        <v>0.6722847004638964</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.04709472336136226</v>
+        <v>0.04690819476408412</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>0.945840182629432</v>
+        <v>0.9522477831395815</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.002783400101384704</v>
+        <v>0.002613568048843253</v>
       </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="n">
-        <v>0.5260321673783743</v>
+        <v>0.5243685243442856</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.01150853097547389</v>
+        <v>0.01152871094829263</v>
       </c>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="n">
-        <v>0.396872229317448</v>
+        <v>0.3925752358161078</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.01687585012636792</v>
+        <v>0.01693585956432243</v>
       </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="n">
-        <v>0.9902782133427275</v>
+        <v>0.9901335997416376</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.0003413474834718591</v>
+        <v>0.0003438769191753161</v>
       </c>
       <c r="AN28" t="inlineStr"/>
     </row>
@@ -3498,10 +3498,10 @@
         <v>0.03864752444133265</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5137115865110338</v>
+        <v>0.5450393411938402</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5154247351720747</v>
+        <v>0.5378951225118166</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3510,16 +3510,16 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.093722495858296</v>
+        <v>4.327280143443206</v>
       </c>
       <c r="P29" t="n">
-        <v>4.106500720371598</v>
+        <v>4.274042576065238</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9365634869260727</v>
+        <v>0.9370092198966595</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01625315658438449</v>
+        <v>0.01619595499649923</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
@@ -3531,38 +3531,38 @@
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>0.7217448756772677</v>
+        <v>0.7199198589712297</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.03437425002626893</v>
+        <v>0.03448679252226174</v>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>0.9306142453337927</v>
+        <v>0.9343812983619562</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.009123769463589835</v>
+        <v>0.008872642059008218</v>
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="n">
-        <v>0.5427167746793323</v>
+        <v>0.6184579859230938</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.009557872598296295</v>
+        <v>0.008730513457351945</v>
       </c>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="n">
-        <v>0.9578486310945015</v>
+        <v>0.9545880790724479</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.005334488199129581</v>
+        <v>0.005536965959767819</v>
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>0.9375347331216408</v>
+        <v>0.9388067148510899</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.001491590586131032</v>
+        <v>0.001476325829841406</v>
       </c>
       <c r="AN29" t="inlineStr"/>
     </row>
@@ -3604,28 +3604,28 @@
         <v>0.0191674492264043</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5256560026576934</v>
+        <v>0.5803769440286095</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5162950458297986</v>
+        <v>0.5467235057226325</v>
       </c>
       <c r="M30" t="n">
-        <v>0.09584112791169885</v>
+        <v>0.1656685183293913</v>
       </c>
       <c r="N30" t="n">
-        <v>0.003635779676298114</v>
+        <v>0.009265298389339413</v>
       </c>
       <c r="O30" t="n">
-        <v>4.182807504896132</v>
+        <v>4.590394956480194</v>
       </c>
       <c r="P30" t="n">
-        <v>4.112993355631942</v>
+        <v>4.339807576284242</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9732307277513563</v>
+        <v>0.9734941725865006</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01348603154086628</v>
+        <v>0.01341950732385387</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
@@ -3637,38 +3637,38 @@
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>0.867976867808312</v>
+        <v>0.8671532172930863</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.02474964455141944</v>
+        <v>0.02482672711248347</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>0.9979704002760172</v>
+        <v>0.997541705724161</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.0002030194235282269</v>
+        <v>0.0002234340345439503</v>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="n">
-        <v>-0.05851006375124679</v>
+        <v>0.01505622351020164</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.01391361480131597</v>
+        <v>0.01342141175353233</v>
       </c>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="n">
-        <v>0.8763947052509893</v>
+        <v>0.8736855960878586</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.0073585584901133</v>
+        <v>0.007438761718713984</v>
       </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="n">
-        <v>0.50306056094756</v>
+        <v>0.5113721296791657</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.00189588980937774</v>
+        <v>0.001879968085850792</v>
       </c>
       <c r="AN30" t="inlineStr"/>
     </row>
@@ -3710,10 +3710,10 @@
         <v>0.02030227596285282</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5492159660579294</v>
+        <v>0.5411091241769229</v>
       </c>
       <c r="L31" t="n">
-        <v>0.5548683045678015</v>
+        <v>0.5556445995349577</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.35839592105136</v>
+        <v>4.297995521688784</v>
       </c>
       <c r="P31" t="n">
-        <v>4.400497349139041</v>
+        <v>4.406273731714898</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9845130816922074</v>
+        <v>0.9845846215736355</v>
       </c>
       <c r="R31" t="n">
-        <v>0.008127165808253836</v>
+        <v>0.008108372867425035</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
@@ -3743,38 +3743,38 @@
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
-        <v>0.9389312232340536</v>
+        <v>0.9403393012386818</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.01319917546374068</v>
+        <v>0.01304611971851409</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>0.8918662357371373</v>
+        <v>0.8908991023708824</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.0080057491002262</v>
+        <v>0.008041470559999596</v>
       </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="n">
-        <v>-0.02547675039257369</v>
+        <v>-0.04007470500952648</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.009207840512719495</v>
+        <v>0.00927314704035594</v>
       </c>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
-        <v>0.9733931947205273</v>
+        <v>0.9703497265043083</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.002559564919299102</v>
+        <v>0.002701992476453797</v>
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="n">
-        <v>0.05857907364202219</v>
+        <v>0.05262509718589548</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.004078133638813569</v>
+        <v>0.004091009304045872</v>
       </c>
       <c r="AN31" t="inlineStr"/>
     </row>
@@ -3816,10 +3816,10 @@
         <v>0.02773752553385222</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5246702789488129</v>
+        <v>0.5785259936431176</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5154133601425148</v>
+        <v>0.5570048359248688</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3828,16 +3828,16 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.175457408489923</v>
+        <v>4.576621334530718</v>
       </c>
       <c r="P32" t="n">
-        <v>4.106415121301283</v>
+        <v>4.416392399057208</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9802556012802348</v>
+        <v>0.9813117562949464</v>
       </c>
       <c r="R32" t="n">
-        <v>0.01353056408015836</v>
+        <v>0.01316370649800837</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
@@ -3849,38 +3849,38 @@
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>0.8420104094751262</v>
+        <v>0.8830149249119658</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.01133625921117785</v>
+        <v>0.009754853694145426</v>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>0.2197806636491788</v>
+        <v>0.2196324728205126</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.01753338943787072</v>
+        <v>0.01753505445950276</v>
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="n">
-        <v>-0.3406033005926725</v>
+        <v>-0.2312443221242326</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.01472455336441108</v>
+        <v>0.01411120524233461</v>
       </c>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="n">
-        <v>0.3365535540866608</v>
+        <v>0.3378479862451139</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.01687695183224104</v>
+        <v>0.01686047971490034</v>
       </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="n">
-        <v>0.08750968120625413</v>
+        <v>0.0827074752067728</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.004855447425927944</v>
+        <v>0.004868207156664338</v>
       </c>
       <c r="AN32" t="inlineStr"/>
     </row>
@@ -3920,28 +3920,28 @@
         <v>0.02495281852103528</v>
       </c>
       <c r="K33" t="n">
-        <v>0.5234358631328813</v>
+        <v>0.5508868290868433</v>
       </c>
       <c r="L33" t="n">
-        <v>0.5218939702136494</v>
+        <v>0.5458029700241758</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2433363612025115</v>
+        <v>0.30045665397837</v>
       </c>
       <c r="N33" t="n">
-        <v>0.01277002314642459</v>
+        <v>0.01884087476792937</v>
       </c>
       <c r="O33" t="n">
-        <v>4.166252496298712</v>
+        <v>4.370842435405677</v>
       </c>
       <c r="P33" t="n">
-        <v>4.154754038748912</v>
+        <v>4.332969072833048</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.9666886615911263</v>
+        <v>0.9676863728354042</v>
       </c>
       <c r="R33" t="n">
-        <v>0.005790245039185479</v>
+        <v>0.005702873743655971</v>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
@@ -3951,38 +3951,38 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
-        <v>0.9185130287642053</v>
+        <v>0.9209140137953842</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.01153512055009549</v>
+        <v>0.01136391082119986</v>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>0.5354341398257849</v>
+        <v>0.5598075583597079</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.004374059661800538</v>
+        <v>0.004257771468192942</v>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="n">
-        <v>0.933730061419687</v>
+        <v>0.9333973606963083</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.003070618745477956</v>
+        <v>0.003078316942466647</v>
       </c>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="n">
-        <v>0.7636231578030872</v>
+        <v>0.7698562698815211</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.002306931424245182</v>
+        <v>0.00227631204009091</v>
       </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
-        <v>0.2914288368876401</v>
+        <v>0.2950358869805424</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.0008322571493136954</v>
+        <v>0.0008301361037336391</v>
       </c>
       <c r="AN33" t="inlineStr"/>
     </row>
@@ -4024,10 +4024,10 @@
         <v>0.008784365836720525</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5179999681685502</v>
+        <v>0.536901696262555</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5226926153685167</v>
+        <v>0.5432389027487502</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.125711815458049</v>
+        <v>4.266640352725299</v>
       </c>
       <c r="P34" t="n">
-        <v>4.160709122843012</v>
+        <v>4.313865019699602</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.9437303344346608</v>
+        <v>0.9392370431768626</v>
       </c>
       <c r="R34" t="n">
-        <v>0.01654204816445072</v>
+        <v>0.01718982928280536</v>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
@@ -4057,38 +4057,38 @@
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>0.9103728914185104</v>
+        <v>0.9025777770358581</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.03583861983970351</v>
+        <v>0.03736462267539677</v>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>0.9956350035562451</v>
+        <v>0.9954666026972713</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.001562847182316779</v>
+        <v>0.001592709087179328</v>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="n">
-        <v>0.6868423332197944</v>
+        <v>0.7077091980568507</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.004308087539485898</v>
+        <v>0.004162081399060013</v>
       </c>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="n">
-        <v>0.4910170618572209</v>
+        <v>0.5015557242603633</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.007919376951724129</v>
+        <v>0.00783696143241468</v>
       </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="n">
-        <v>0.2782269776724356</v>
+        <v>0.2670092201505117</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.0008258918345748553</v>
+        <v>0.0008322850727627393</v>
       </c>
       <c r="AN34" t="inlineStr"/>
     </row>
@@ -4130,10 +4130,10 @@
         <v>0.033117285160876</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5047782193068076</v>
+        <v>0.5002346248069625</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5047603985694951</v>
+        <v>0.5375970958928967</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4142,16 +4142,16 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.027064102812506</v>
+        <v>3.9931505467131</v>
       </c>
       <c r="P35" t="n">
-        <v>4.026931042096406</v>
+        <v>4.271817773745477</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9954471077236299</v>
+        <v>0.9962031555067061</v>
       </c>
       <c r="R35" t="n">
-        <v>0.006721987021724298</v>
+        <v>0.00613854420043662</v>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>0.9655258578814498</v>
+        <v>0.9758020481878399</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.01013190658057474</v>
+        <v>0.00848855460540931</v>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -4173,24 +4173,24 @@
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="n">
-        <v>0.6437992543016026</v>
+        <v>0.64945627498078</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.008913149906159113</v>
+        <v>0.008842089311811454</v>
       </c>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="n">
-        <v>0.6995764681874671</v>
+        <v>0.6948344030196475</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.002214974567840757</v>
+        <v>0.002232387366728052</v>
       </c>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="n">
-        <v>0.5636275771746777</v>
+        <v>0.5727487813570584</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.002242951385482504</v>
+        <v>0.002219386128153858</v>
       </c>
       <c r="AN35" t="inlineStr"/>
     </row>
@@ -4232,10 +4232,10 @@
         <v>0.02290841461070009</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5291426829145613</v>
+        <v>0.5508842687946176</v>
       </c>
       <c r="L36" t="n">
-        <v>0.5286557860396734</v>
+        <v>0.5490979189898959</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4244,16 +4244,16 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.208803672383319</v>
+        <v>4.370823363997192</v>
       </c>
       <c r="P36" t="n">
-        <v>4.205173662037383</v>
+        <v>4.357516428485859</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9839701669244788</v>
+        <v>0.9839315696536894</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01147266173959638</v>
+        <v>0.01148646560125316</v>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
@@ -4265,38 +4265,38 @@
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
-        <v>0.817723976418594</v>
+        <v>0.8166610429078107</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.01855906841856205</v>
+        <v>0.01861310289764294</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>0.3705482319500039</v>
+        <v>0.3723614624476508</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.008138674206086631</v>
+        <v>0.008126943414296529</v>
       </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="n">
-        <v>0.06420798879367828</v>
+        <v>0.06702911052602845</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.01349658276513005</v>
+        <v>0.01347622341055103</v>
       </c>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="n">
-        <v>0.7347136685789963</v>
+        <v>0.7326810460920691</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.006033980829770504</v>
+        <v>0.00605705288442605</v>
       </c>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="n">
-        <v>0.14635170221074</v>
+        <v>0.1524810339639457</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.004085770458337526</v>
+        <v>0.004071075789554511</v>
       </c>
       <c r="AN36" t="inlineStr"/>
     </row>
@@ -4338,10 +4338,10 @@
         <v>0.007462828179086988</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5448562437145308</v>
+        <v>0.5416254005209055</v>
       </c>
       <c r="L37" t="n">
-        <v>0.5498883332052865</v>
+        <v>0.5505442080965769</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4350,61 +4350,61 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4.325915956550759</v>
+        <v>4.301842628273871</v>
       </c>
       <c r="P37" t="n">
-        <v>4.363403740894099</v>
+        <v>4.368288287673698</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.990296608537576</v>
+        <v>0.9904183339057777</v>
       </c>
       <c r="R37" t="n">
-        <v>0.006563727542686192</v>
+        <v>0.006522427874597541</v>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="n">
-        <v>-1.524683709658958</v>
+        <v>-1.532500512853302</v>
       </c>
       <c r="X37" t="n">
-        <v>0.0006797541525909888</v>
+        <v>0.0006808056502324749</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
-        <v>0.9745784974441917</v>
+        <v>0.9759297077302049</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.007569902348256348</v>
+        <v>0.007365976870870116</v>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>-0.7418751389149945</v>
+        <v>-0.7305957074055771</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.008356455871203709</v>
+        <v>0.008329356008159492</v>
       </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="n">
-        <v>0.9059626047732871</v>
+        <v>0.9057722058075757</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.009979341087240204</v>
+        <v>0.009989438641628256</v>
       </c>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="n">
-        <v>0.9659062198024937</v>
+        <v>0.9607746496072406</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.001656590247050169</v>
+        <v>0.001776891613454449</v>
       </c>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="n">
-        <v>0.9998821209654625</v>
+        <v>0.9999955925352465</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.068744836987045e-05</v>
+        <v>2.066570228598871e-06</v>
       </c>
       <c r="AN37" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>0.003185097564105027</v>
       </c>
       <c r="K38" t="n">
-        <v>0.540912009343728</v>
+        <v>0.5410877791334675</v>
       </c>
       <c r="L38" t="n">
-        <v>0.5469205628049896</v>
+        <v>0.5459534785704414</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4458,61 +4458,61 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.296526671931293</v>
+        <v>4.297836464385832</v>
       </c>
       <c r="P38" t="n">
-        <v>4.341294306558273</v>
+        <v>4.334089179456488</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9428325660011811</v>
+        <v>0.9430380972433829</v>
       </c>
       <c r="R38" t="n">
-        <v>0.01341604592867179</v>
+        <v>0.0133919071904237</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
-        <v>0.2594209483904801</v>
+        <v>0.2639470867320597</v>
       </c>
       <c r="X38" t="n">
-        <v>0.001127983700122156</v>
+        <v>0.001124531513097592</v>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>0.7451969187800127</v>
+        <v>0.7469339915377098</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.02434632169428359</v>
+        <v>0.02426319150403365</v>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>-0.545267829990691</v>
+        <v>-0.5464580451682217</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.01804255156000626</v>
+        <v>0.01804949870042787</v>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="n">
-        <v>0.991168406693346</v>
+        <v>0.9907604013767453</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.002181442096618998</v>
+        <v>0.002231262732024745</v>
       </c>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="n">
-        <v>-2.304964116336112</v>
+        <v>-2.316352245161167</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.006005350560149638</v>
+        <v>0.006015688175171676</v>
       </c>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="n">
-        <v>0.9999879117301999</v>
+        <v>0.9999993534681905</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.393476724578854e-06</v>
+        <v>3.222645951117273e-07</v>
       </c>
       <c r="AN38" t="inlineStr"/>
     </row>
@@ -4554,10 +4554,10 @@
         <v>0.03277409385829239</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5277031214589124</v>
+        <v>0.5532307663355256</v>
       </c>
       <c r="L39" t="n">
-        <v>0.5262642480452384</v>
+        <v>0.5491049323283788</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4566,16 +4566,16 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.198070974628081</v>
+        <v>4.388301465052076</v>
       </c>
       <c r="P39" t="n">
-        <v>4.187342706575164</v>
+        <v>4.357568293928008</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.9820155687657246</v>
+        <v>0.9819945676145284</v>
       </c>
       <c r="R39" t="n">
-        <v>0.008976421545433658</v>
+        <v>0.008981661082384249</v>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
@@ -4585,38 +4585,38 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>0.8615733922404776</v>
+        <v>0.8614104763354866</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.01245262617987344</v>
+        <v>0.0124599518462974</v>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>0.2501341581817347</v>
+        <v>0.2315287535118379</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.001288321907383524</v>
+        <v>0.001304206671885018</v>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="n">
-        <v>-0.05102372831820112</v>
+        <v>-0.05242748113915696</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.01468426495895124</v>
+        <v>0.0146940678776024</v>
       </c>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="n">
-        <v>0.7811804882406734</v>
+        <v>0.781611202634598</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.005076142584020242</v>
+        <v>0.005071144298890516</v>
       </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="n">
-        <v>-0.1176510596055118</v>
+        <v>-0.1198831906614264</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.002181326609182442</v>
+        <v>0.002183503754813192</v>
       </c>
       <c r="AN39" t="inlineStr"/>
     </row>
@@ -4658,28 +4658,28 @@
         <v>0.003165060709665684</v>
       </c>
       <c r="K40" t="n">
-        <v>0.5774219930435192</v>
+        <v>0.5283164027424528</v>
       </c>
       <c r="L40" t="n">
-        <v>0.5848994472824949</v>
+        <v>0.5692409188383837</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5654808253351944</v>
+        <v>0.522701138985566</v>
       </c>
       <c r="N40" t="n">
-        <v>0.1188566283133557</v>
+        <v>0.1104856991032153</v>
       </c>
       <c r="O40" t="n">
-        <v>4.568405641987668</v>
+        <v>4.202643391765502</v>
       </c>
       <c r="P40" t="n">
-        <v>4.624044155330719</v>
+        <v>4.507508523809872</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.9915652689925698</v>
+        <v>0.9916978149582863</v>
       </c>
       <c r="R40" t="n">
-        <v>0.00551665319719768</v>
+        <v>0.005473136365717831</v>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
@@ -4689,38 +4689,38 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
-        <v>0.9663461414084645</v>
+        <v>0.9670261955693887</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.01107080331690243</v>
+        <v>0.0109583768475607</v>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
-        <v>0.6904932432457745</v>
+        <v>0.7153572480560326</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.001265661302204762</v>
+        <v>0.001213759100701683</v>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="n">
-        <v>0.9821299790916059</v>
+        <v>0.9821727339140446</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.003357730472798638</v>
+        <v>0.003353711307356606</v>
       </c>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="n">
-        <v>0.9992504584484263</v>
+        <v>0.9990123328687575</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.001229488718741174</v>
+        <v>0.001411341110100427</v>
       </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="n">
-        <v>0.9999989679470341</v>
+        <v>0.9999999999897455</v>
       </c>
       <c r="AM40" t="n">
-        <v>6.176930585866982e-07</v>
+        <v>1.94705706972353e-09</v>
       </c>
       <c r="AN40" t="inlineStr"/>
     </row>
@@ -4762,28 +4762,28 @@
         <v>0.01422966781757511</v>
       </c>
       <c r="K41" t="n">
-        <v>0.5798983691005819</v>
+        <v>0.5561311174839206</v>
       </c>
       <c r="L41" t="n">
-        <v>0.5834942783595261</v>
+        <v>0.5675786677022348</v>
       </c>
       <c r="M41" t="n">
-        <v>0.116011044374727</v>
+        <v>0.09510322729313825</v>
       </c>
       <c r="N41" t="n">
-        <v>0.01293868914391235</v>
+        <v>0.009607910224360803</v>
       </c>
       <c r="O41" t="n">
-        <v>4.586833780976132</v>
+        <v>4.409902885576174</v>
       </c>
       <c r="P41" t="n">
-        <v>4.613590058470473</v>
+        <v>4.495138427495989</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.994097110898541</v>
+        <v>0.9942326924938512</v>
       </c>
       <c r="R41" t="n">
-        <v>0.005954527677307655</v>
+        <v>0.005885746597548107</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
@@ -4793,38 +4793,38 @@
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>0.8665988956660102</v>
+        <v>0.8699122566411659</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.01063621076000406</v>
+        <v>0.01050329133840707</v>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>0.7749882292897026</v>
+        <v>0.7634550602741808</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.001182973418839182</v>
+        <v>0.001212911736693704</v>
       </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="n">
-        <v>0.9823212331700997</v>
+        <v>0.9823332189033043</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.003565060012253145</v>
+        <v>0.003563851299466245</v>
       </c>
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="n">
-        <v>0.9537568898951335</v>
+        <v>0.954982546630979</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.006932887914437144</v>
+        <v>0.006840394089492075</v>
       </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="n">
-        <v>0.8139890661597812</v>
+        <v>0.8188063758434938</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.001406771528391638</v>
+        <v>0.001388435755810789</v>
       </c>
       <c r="AN41" t="inlineStr"/>
     </row>
@@ -4866,28 +4866,28 @@
         <v>0.01067227249555984</v>
       </c>
       <c r="K42" t="n">
-        <v>0.5715750579492677</v>
+        <v>0.5695103219420882</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5749328599619349</v>
+        <v>0.567741715497726</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4070472770800015</v>
+        <v>0.3991687508264905</v>
       </c>
       <c r="N42" t="n">
-        <v>0.06471339467210176</v>
+        <v>0.06191300225348243</v>
       </c>
       <c r="O42" t="n">
-        <v>4.524889107463629</v>
+        <v>4.509519969177892</v>
       </c>
       <c r="P42" t="n">
-        <v>4.549880412920261</v>
+        <v>4.496354142500471</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.9620336643302453</v>
+        <v>0.9618113939159544</v>
       </c>
       <c r="R42" t="n">
-        <v>0.01290323730918828</v>
+        <v>0.01294095259659222</v>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
@@ -4897,31 +4897,31 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>0.8588034611204007</v>
+        <v>0.8583697096695226</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.02062073970729805</v>
+        <v>0.0206523885608478</v>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>0.9997863621673407</v>
+        <v>0.9998279033187278</v>
       </c>
       <c r="AD42" t="n">
-        <v>7.812130339682059e-05</v>
+        <v>7.011592156942258e-05</v>
       </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="n">
-        <v>0.6901485132120334</v>
+        <v>0.6869359442877778</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.01624590351881728</v>
+        <v>0.01632990586074336</v>
       </c>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="n">
-        <v>0.966202880955161</v>
+        <v>0.9660122728424613</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.005685207685249477</v>
+        <v>0.005701216788251034</v>
       </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
@@ -4968,28 +4968,28 @@
         <v>0.0240059836138475</v>
       </c>
       <c r="K43" t="n">
-        <v>0.5149621556576743</v>
+        <v>0.4953620074672234</v>
       </c>
       <c r="L43" t="n">
-        <v>0.5277867653881738</v>
+        <v>0.5435126257415349</v>
       </c>
       <c r="M43" t="n">
-        <v>0.4000689730996849</v>
+        <v>0.3683045390121662</v>
       </c>
       <c r="N43" t="n">
-        <v>0.07226202377716107</v>
+        <v>0.07179043718877728</v>
       </c>
       <c r="O43" t="n">
-        <v>4.103051778684014</v>
+        <v>3.956773080980899</v>
       </c>
       <c r="P43" t="n">
-        <v>4.198693171128466</v>
+        <v>4.315885400832582</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.9256020629865613</v>
+        <v>0.9294625116452134</v>
       </c>
       <c r="R43" t="n">
-        <v>0.01666600787355307</v>
+        <v>0.01622785549969679</v>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
@@ -4999,38 +4999,38 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>0.8504050459786245</v>
+        <v>0.8591416301352739</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.03326309023468825</v>
+        <v>0.03227717007729149</v>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>0.5845248355187043</v>
+        <v>0.5715983214402245</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.003044078681885044</v>
+        <v>0.003091070578040153</v>
       </c>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="n">
-        <v>0.7371630383810936</v>
+        <v>0.7441255299772154</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.01624699019305853</v>
+        <v>0.01603035637342281</v>
       </c>
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="n">
-        <v>0.7147435972775064</v>
+        <v>0.7376034787767961</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.002994000382936507</v>
+        <v>0.002871528873232446</v>
       </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="n">
-        <v>0.9904529454842311</v>
+        <v>0.991892510691032</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.0003882996237200478</v>
+        <v>0.0003578289390546378</v>
       </c>
       <c r="AN43" t="inlineStr"/>
     </row>
@@ -5072,10 +5072,10 @@
         <v>0.02192364384915694</v>
       </c>
       <c r="K44" t="n">
-        <v>0.5457327389361865</v>
+        <v>0.5286870787682787</v>
       </c>
       <c r="L44" t="n">
-        <v>0.5768348026250045</v>
+        <v>0.5600074997541628</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5084,16 +5084,16 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.33244628845221</v>
+        <v>4.205406969984286</v>
       </c>
       <c r="P44" t="n">
-        <v>4.564016717324882</v>
+        <v>4.438748696822004</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.9535533506493198</v>
+        <v>0.95302310452405</v>
       </c>
       <c r="R44" t="n">
-        <v>0.007340553793944856</v>
+        <v>0.007382335648650627</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
@@ -5103,38 +5103,38 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>0.9564774780883339</v>
+        <v>0.9556761552670739</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.009355203020702363</v>
+        <v>0.009440932723754175</v>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>0.8092811316243541</v>
+        <v>0.8126900677434666</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.004843377820810989</v>
+        <v>0.004799897038070332</v>
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="n">
-        <v>0.9019754780492765</v>
+        <v>0.8998961627984626</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.01095041690744184</v>
+        <v>0.01106594864011849</v>
       </c>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="n">
-        <v>0.9218653904937562</v>
+        <v>0.9233222961529891</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.006072489103649121</v>
+        <v>0.006015608589755103</v>
       </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="n">
-        <v>0.6313700271707015</v>
+        <v>0.6252075221395293</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.001285987315094204</v>
+        <v>0.00129669189296649</v>
       </c>
       <c r="AN44" t="inlineStr"/>
     </row>
@@ -5176,10 +5176,10 @@
         <v>0.02487778863857871</v>
       </c>
       <c r="K45" t="n">
-        <v>0.534591615256344</v>
+        <v>0.5400703130547023</v>
       </c>
       <c r="L45" t="n">
-        <v>0.5477299127261217</v>
+        <v>0.5560424067601982</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5188,16 +5188,16 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.249422615389083</v>
+        <v>4.290254436529441</v>
       </c>
       <c r="P45" t="n">
-        <v>4.347324171597083</v>
+        <v>4.409240661505166</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.9689158210965371</v>
+        <v>0.9689003003205184</v>
       </c>
       <c r="R45" t="n">
-        <v>0.008610528234223395</v>
+        <v>0.0086126776460247</v>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
@@ -5207,38 +5207,38 @@
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="n">
-        <v>0.9762063133828901</v>
+        <v>0.9761786969789389</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.0131934775192567</v>
+        <v>0.01320113187623589</v>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>0.922799914561855</v>
+        <v>0.9228403531276196</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.007287011336767298</v>
+        <v>0.007285102563709765</v>
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="n">
-        <v>0.8734330617593351</v>
+        <v>0.8734203387177651</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.008454297378518105</v>
+        <v>0.008454722298625272</v>
       </c>
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="n">
-        <v>0.9225952721221818</v>
+        <v>0.9225908945229462</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.008466729278960713</v>
+        <v>0.008466968692137505</v>
       </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="n">
-        <v>0.9804490793265342</v>
+        <v>0.9804677110250209</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.0006139627357223216</v>
+        <v>0.0006136701179116748</v>
       </c>
       <c r="AN45" t="inlineStr"/>
     </row>
@@ -5280,10 +5280,10 @@
         <v>0.04354702384994095</v>
       </c>
       <c r="K46" t="n">
-        <v>0.5306468072560714</v>
+        <v>0.4692195827002179</v>
       </c>
       <c r="L46" t="n">
-        <v>0.5746731523761059</v>
+        <v>0.56319358864237</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5292,16 +5292,16 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4.220017038479095</v>
+        <v>3.761450846446995</v>
       </c>
       <c r="P46" t="n">
-        <v>4.547935087036819</v>
+        <v>4.462444238329396</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9677847421026257</v>
+        <v>0.9695306941104365</v>
       </c>
       <c r="R46" t="n">
-        <v>0.008557699023027636</v>
+        <v>0.008322570492744614</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
@@ -5311,38 +5311,38 @@
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
-        <v>0.9824825443662556</v>
+        <v>0.9840113589995604</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.01020584497525098</v>
+        <v>0.009750328092818736</v>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>0.9204160001375665</v>
+        <v>0.9224336542903625</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.01047117642148282</v>
+        <v>0.01033758898922709</v>
       </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="n">
-        <v>0.9836807424446214</v>
+        <v>0.9848925210034284</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.002091118985687701</v>
+        <v>0.002011984109332633</v>
       </c>
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="n">
-        <v>0.8658714761208417</v>
+        <v>0.8728316232390262</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.01212794854304989</v>
+        <v>0.01180908740359581</v>
       </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="n">
-        <v>0.9878502006923368</v>
+        <v>0.9880876414415648</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.0009520194639804986</v>
+        <v>0.0009426710156491396</v>
       </c>
       <c r="AN46" t="inlineStr"/>
     </row>
@@ -5384,10 +5384,10 @@
         <v>0.01548193654302897</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5362846783319638</v>
+        <v>0.5376530400040005</v>
       </c>
       <c r="L47" t="n">
-        <v>0.5492302964256942</v>
+        <v>0.55386159540626</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5396,16 +5396,16 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.262041686410713</v>
+        <v>4.272240003116125</v>
       </c>
       <c r="P47" t="n">
-        <v>4.358499538739855</v>
+        <v>4.392994941751244</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.9442435661395094</v>
+        <v>0.9451092518699958</v>
       </c>
       <c r="R47" t="n">
-        <v>0.008873757836498755</v>
+        <v>0.008804600464171093</v>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
@@ -5415,38 +5415,38 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="n">
-        <v>0.9388010457126807</v>
+        <v>0.940644718982248</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.01363056122682955</v>
+        <v>0.01342367472314932</v>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>0.8034696057270717</v>
+        <v>0.8033244109864681</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.006926755960562583</v>
+        <v>0.00692931419805967</v>
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="n">
-        <v>0.8472217428334066</v>
+        <v>0.847695687677937</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.0116543004856974</v>
+        <v>0.01163620960645925</v>
       </c>
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="n">
-        <v>0.9010697874179765</v>
+        <v>0.9016049470413948</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.004877825252754163</v>
+        <v>0.004864614147289625</v>
       </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="n">
-        <v>0.9096346914701681</v>
+        <v>0.9099581517169765</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.0005743206432334187</v>
+        <v>0.0005732918389398196</v>
       </c>
       <c r="AN47" t="inlineStr"/>
     </row>
@@ -5488,10 +5488,10 @@
         <v>0.04054047652094685</v>
       </c>
       <c r="K48" t="n">
-        <v>0.5133086615075061</v>
+        <v>0.4047097120777118</v>
       </c>
       <c r="L48" t="n">
-        <v>0.5304241650804626</v>
+        <v>0.5459567870506425</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5500,16 +5500,16 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4.090716553477905</v>
+        <v>3.278188650913639</v>
       </c>
       <c r="P48" t="n">
-        <v>4.218355529141682</v>
+        <v>4.334035035067895</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.9636543047177719</v>
+        <v>0.9639931396374642</v>
       </c>
       <c r="R48" t="n">
-        <v>0.009830026639216628</v>
+        <v>0.009784098841558167</v>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
@@ -5519,38 +5519,38 @@
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>0.9508658427437623</v>
+        <v>0.9507073691867312</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.01620828195268155</v>
+        <v>0.01623439938749992</v>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>0.8763418849191106</v>
+        <v>0.885564897739694</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.005940221760702119</v>
+        <v>0.005714404488955672</v>
       </c>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="n">
-        <v>0.9507766138532817</v>
+        <v>0.9510188166467399</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.01286607049429841</v>
+        <v>0.01283437782524244</v>
       </c>
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="n">
-        <v>0.7132509990905755</v>
+        <v>0.7409315243339216</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.004425150112169619</v>
+        <v>0.004206145926056573</v>
       </c>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="n">
-        <v>0.9994202483595795</v>
+        <v>0.9996682151621836</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.0001864315829211262</v>
+        <v>0.0001410349541343809</v>
       </c>
       <c r="AN48" t="inlineStr"/>
     </row>
@@ -5592,28 +5592,28 @@
         <v>0.02297528417150188</v>
       </c>
       <c r="K49" t="n">
-        <v>0.5430493439742232</v>
+        <v>0.507334054451019</v>
       </c>
       <c r="L49" t="n">
-        <v>0.5551717902926681</v>
+        <v>0.5559303586706785</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1959086541064013</v>
+        <v>0.1424750500673412</v>
       </c>
       <c r="N49" t="n">
-        <v>0.01031374940239459</v>
+        <v>0.007061884483731409</v>
       </c>
       <c r="O49" t="n">
-        <v>4.312452942874997</v>
+        <v>4.046137816931933</v>
       </c>
       <c r="P49" t="n">
-        <v>4.402757055788375</v>
+        <v>4.408391981495804</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.920756724333003</v>
+        <v>0.9239242745457639</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01334309222119501</v>
+        <v>0.01307369440207055</v>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
@@ -5623,38 +5623,38 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>0.9277392209818692</v>
+        <v>0.9320841862665314</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.01813235180953891</v>
+        <v>0.01757876140134717</v>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>0.9177242786321178</v>
+        <v>0.9208852584045786</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.002750715804419393</v>
+        <v>0.002697357934196381</v>
       </c>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="n">
-        <v>0.4357777175651032</v>
+        <v>0.4430907100250938</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.01386756496318391</v>
+        <v>0.01377740177948114</v>
       </c>
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="n">
-        <v>0.2545286660840321</v>
+        <v>0.2814832788216017</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.01897036098110735</v>
+        <v>0.01862424005392624</v>
       </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="n">
-        <v>0.8757606712778323</v>
+        <v>0.8771289558488665</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.001287624469072878</v>
+        <v>0.001280514343327963</v>
       </c>
       <c r="AN49" t="inlineStr"/>
     </row>
@@ -5696,10 +5696,10 @@
         <v>0.02365077480082941</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5532153165827609</v>
+        <v>0.5409958952894118</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5851082596758951</v>
+        <v>0.5605201676033635</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -5708,16 +5708,16 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4.388186391172322</v>
+        <v>4.297151770118208</v>
       </c>
       <c r="P50" t="n">
-        <v>4.625587228345159</v>
+        <v>4.442562212890054</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.9579546499562428</v>
+        <v>0.9608045769180966</v>
       </c>
       <c r="R50" t="n">
-        <v>0.0109594947982313</v>
+        <v>0.01058154850218405</v>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
@@ -5727,31 +5727,31 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
-        <v>0.9775691242814226</v>
+        <v>0.9819033004737431</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.01259988117814589</v>
+        <v>0.01131730506638015</v>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>0.9379724386735047</v>
+        <v>0.9374170034323297</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.005306798584481242</v>
+        <v>0.005330505898001532</v>
       </c>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="n">
-        <v>0.94867769317901</v>
+        <v>0.9482343494354788</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.00231454428559842</v>
+        <v>0.002324519793881028</v>
       </c>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="n">
-        <v>0.8024407405620921</v>
+        <v>0.8050630900901391</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.01783797926667442</v>
+        <v>0.01771919545651057</v>
       </c>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
@@ -5798,10 +5798,10 @@
         <v>0.05173441476315732</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5293227205179547</v>
+        <v>0.4812086802605804</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5583707580630578</v>
+        <v>0.5582457840330085</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -5810,16 +5810,16 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>4.210145903626906</v>
+        <v>3.851059526098111</v>
       </c>
       <c r="P51" t="n">
-        <v>4.42657732043377</v>
+        <v>4.425622904874372</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.9282979959973066</v>
+        <v>0.9284299964927997</v>
       </c>
       <c r="R51" t="n">
-        <v>0.01075423064377406</v>
+        <v>0.01074432703134815</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
@@ -5829,38 +5829,38 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
-        <v>0.9299460486816002</v>
+        <v>0.9295092822420135</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.01564785368538375</v>
+        <v>0.01569655784531013</v>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>0.7955981168623248</v>
+        <v>0.7965003248261033</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.01443591286388576</v>
+        <v>0.01440401834558218</v>
       </c>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="n">
-        <v>-0.8408767479385451</v>
+        <v>-0.8078403432370145</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.003403678605510174</v>
+        <v>0.003372999102247724</v>
       </c>
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="n">
-        <v>0.8902798997025974</v>
+        <v>0.8916714400390217</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.01063498913798302</v>
+        <v>0.01056733408254436</v>
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="n">
-        <v>0.9952095412905826</v>
+        <v>0.9956322801226107</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.0005731112544184649</v>
+        <v>0.0005472399253436916</v>
       </c>
       <c r="AN51" t="inlineStr"/>
     </row>
@@ -5902,10 +5902,10 @@
         <v>0.004631983561397277</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5458032169079876</v>
+        <v>0.5429836066241071</v>
       </c>
       <c r="L52" t="n">
-        <v>0.5562802672787837</v>
+        <v>0.5519809004860716</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -5914,16 +5914,16 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4.33297137534801</v>
+        <v>4.311963123218198</v>
       </c>
       <c r="P52" t="n">
-        <v>4.411009900256763</v>
+        <v>4.378988121467831</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.9654227421943514</v>
+        <v>0.9652852496903884</v>
       </c>
       <c r="R52" t="n">
-        <v>0.008979425245246357</v>
+        <v>0.008997260360846616</v>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
@@ -5933,38 +5933,38 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
-        <v>0.9775886454272612</v>
+        <v>0.9775778295623077</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.006855349610060666</v>
+        <v>0.006857003628598683</v>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>0.9195096840870256</v>
+        <v>0.9189528216211351</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.00200698872328012</v>
+        <v>0.002013919310586962</v>
       </c>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="n">
-        <v>0.7877828467702369</v>
+        <v>0.7873706895020927</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.01654210160623573</v>
+        <v>0.01655815742488062</v>
       </c>
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="n">
-        <v>0.7146591608453062</v>
+        <v>0.7108994128057953</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.008806593314211067</v>
+        <v>0.008864422778274969</v>
       </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="n">
-        <v>0.0001582846317169651</v>
+        <v>0.001044304216321068</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.0009640307621501654</v>
+        <v>0.0009636035248012068</v>
       </c>
       <c r="AN52" t="inlineStr"/>
     </row>
@@ -6006,28 +6006,28 @@
         <v>0.00319007047444387</v>
       </c>
       <c r="K53" t="n">
-        <v>0.5542601478318625</v>
+        <v>0.5670780971791589</v>
       </c>
       <c r="L53" t="n">
-        <v>0.5498204637936478</v>
+        <v>0.5591499193549173</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1121626273224042</v>
+        <v>0.1240744627952637</v>
       </c>
       <c r="N53" t="n">
-        <v>0.004322913227953993</v>
+        <v>0.004988707459151543</v>
       </c>
       <c r="O53" t="n">
-        <v>4.395968424017083</v>
+        <v>4.491413962140649</v>
       </c>
       <c r="P53" t="n">
-        <v>4.362898707479979</v>
+        <v>4.432383425697124</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.9852527361471984</v>
+        <v>0.9852417438817525</v>
       </c>
       <c r="R53" t="n">
-        <v>0.005221180603083967</v>
+        <v>0.005223126113549885</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
@@ -6037,38 +6037,38 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="n">
-        <v>0.9775079440002391</v>
+        <v>0.9776580948010445</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.008691783916341218</v>
+        <v>0.008662723351526966</v>
       </c>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>0.7222597674370607</v>
+        <v>0.7157641763372806</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.005410022763735653</v>
+        <v>0.005472920023092795</v>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="n">
-        <v>0.9852419251616968</v>
+        <v>0.9851775095484872</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.00299925065879608</v>
+        <v>0.003005789052673199</v>
       </c>
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="n">
-        <v>0.9815349721876085</v>
+        <v>0.9816799404673644</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.003957200640875131</v>
+        <v>0.00394163611045416</v>
       </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="n">
-        <v>0.8772443649568704</v>
+        <v>0.8771047225238296</v>
       </c>
       <c r="AM53" t="n">
-        <v>0.0001551659269262512</v>
+        <v>0.0001552541574540863</v>
       </c>
       <c r="AN53" t="inlineStr"/>
     </row>
@@ -6110,28 +6110,28 @@
         <v>0.02695043454293275</v>
       </c>
       <c r="K54" t="n">
-        <v>0.5344032669168637</v>
+        <v>0.5192367329134363</v>
       </c>
       <c r="L54" t="n">
-        <v>0.5640535399283015</v>
+        <v>0.5515678024324538</v>
       </c>
       <c r="M54" t="n">
-        <v>0.3252762272693893</v>
+        <v>0.3229157324759777</v>
       </c>
       <c r="N54" t="n">
-        <v>0.0399936933870431</v>
+        <v>0.03857309580623619</v>
       </c>
       <c r="O54" t="n">
-        <v>4.248018727268365</v>
+        <v>4.134936389104962</v>
       </c>
       <c r="P54" t="n">
-        <v>4.468877127658842</v>
+        <v>4.375886144305886</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.9338286641326593</v>
+        <v>0.9340780364024328</v>
       </c>
       <c r="R54" t="n">
-        <v>0.009340847140505558</v>
+        <v>0.00932322964076867</v>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
@@ -6141,38 +6141,38 @@
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>0.9120830664146515</v>
+        <v>0.9127659723197946</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.01527661506148939</v>
+        <v>0.01521716787538714</v>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>0.3436196968000098</v>
+        <v>0.3683017101695465</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.004672181164048123</v>
+        <v>0.004583494923799544</v>
       </c>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="n">
-        <v>0.8089684499168038</v>
+        <v>0.8070285197022052</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.01296191467163652</v>
+        <v>0.01302756271362885</v>
       </c>
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="n">
-        <v>0.9282376039062078</v>
+        <v>0.9328120890658789</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.003432620611278483</v>
+        <v>0.003321413215073124</v>
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="n">
-        <v>0.8549814280612259</v>
+        <v>0.8510080464395345</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.001121947293362742</v>
+        <v>0.001137213614732013</v>
       </c>
       <c r="AN54" t="inlineStr"/>
     </row>
@@ -6214,28 +6214,28 @@
         <v>0.00266683139341308</v>
       </c>
       <c r="K55" t="n">
-        <v>0.5474997588324574</v>
+        <v>0.5563410684470536</v>
       </c>
       <c r="L55" t="n">
-        <v>0.5482104719584124</v>
+        <v>0.5566633662362249</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2290172180051231</v>
+        <v>0.2315986820760616</v>
       </c>
       <c r="N55" t="n">
-        <v>0.02903035930288557</v>
+        <v>0.02992057583063879</v>
       </c>
       <c r="O55" t="n">
-        <v>4.345610810250299</v>
+        <v>4.411466481943051</v>
       </c>
       <c r="P55" t="n">
-        <v>4.350905443918853</v>
+        <v>4.41386670503176</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.865345112980063</v>
+        <v>0.8656895894651874</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01479749854301311</v>
+        <v>0.01477855881258635</v>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
@@ -6245,38 +6245,38 @@
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="n">
-        <v>0.7560239936917391</v>
+        <v>0.7588511292980465</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.02384290425552666</v>
+        <v>0.02370435879225456</v>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
-        <v>0.1932714838493415</v>
+        <v>0.1885740618111673</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.003932652109920881</v>
+        <v>0.003944085022411729</v>
       </c>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="n">
-        <v>0.5611454676614281</v>
+        <v>0.5591732286465172</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.0212201025598737</v>
+        <v>0.02126773132531239</v>
       </c>
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="n">
-        <v>0.7050559317081784</v>
+        <v>0.6969689764574305</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.007756833677620211</v>
+        <v>0.007862455357550723</v>
       </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="n">
-        <v>0.7818411400781091</v>
+        <v>0.7697483982478852</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.0006471154013600438</v>
+        <v>0.0006648086147663551</v>
       </c>
       <c r="AN55" t="inlineStr"/>
     </row>
@@ -6318,10 +6318,10 @@
         <v>0.03893815066809572</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5336789504017783</v>
+        <v>0.5097180810386136</v>
       </c>
       <c r="L56" t="n">
-        <v>0.5483711655041982</v>
+        <v>0.5518535577083454</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -6330,16 +6330,16 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>4.242619804626787</v>
+        <v>4.063927352245716</v>
       </c>
       <c r="P56" t="n">
-        <v>4.352100318077322</v>
+        <v>4.378024103527062</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.8242670219004026</v>
+        <v>0.8290942444541722</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01229988857148968</v>
+        <v>0.01212977896087996</v>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
@@ -6349,38 +6349,38 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>0.7196027677003406</v>
+        <v>0.7283256784225867</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.01848776660585475</v>
+        <v>0.01819792556061479</v>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
-        <v>-0.2139204721596895</v>
+        <v>-0.1642604336165421</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.009656550822694223</v>
+        <v>0.009456969361349826</v>
       </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="n">
-        <v>0.6232084159368971</v>
+        <v>0.6280877513406949</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.01622894053033722</v>
+        <v>0.01612351822136859</v>
       </c>
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="n">
-        <v>0.7348469815186315</v>
+        <v>0.7483831336531044</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.007486526698408037</v>
+        <v>0.00729292864910951</v>
       </c>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="n">
-        <v>0.9126349647852501</v>
+        <v>0.915257761023231</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.001401147297138398</v>
+        <v>0.001379955025367335</v>
       </c>
       <c r="AN56" t="inlineStr"/>
     </row>
@@ -6422,10 +6422,10 @@
         <v>0.02444228773888892</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5416026416533484</v>
+        <v>0.5362984060044483</v>
       </c>
       <c r="L57" t="n">
-        <v>0.5546963790150543</v>
+        <v>0.554455161301568</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -6434,16 +6434,16 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4.301673038976071</v>
+        <v>4.26214400069415</v>
       </c>
       <c r="P57" t="n">
-        <v>4.399214048441006</v>
+        <v>4.397413072186263</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.9059462298041834</v>
+        <v>0.9075211627563269</v>
       </c>
       <c r="R57" t="n">
-        <v>0.009325716035934436</v>
+        <v>0.009247306723752669</v>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
@@ -6453,38 +6453,38 @@
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
-        <v>0.8140214676226617</v>
+        <v>0.817918593012726</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.01632283342963049</v>
+        <v>0.01615090791475431</v>
       </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>0.6143887314377203</v>
+        <v>0.6169303172194858</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.008952304261603374</v>
+        <v>0.008922752914418243</v>
       </c>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="n">
-        <v>0.7454058531746608</v>
+        <v>0.7460658066096132</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.007746089106169566</v>
+        <v>0.007736042969368808</v>
       </c>
       <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="n">
-        <v>0.9215997188427121</v>
+        <v>0.9245547766948449</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.005152726803217192</v>
+        <v>0.00505468598589359</v>
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="n">
-        <v>0.6569838767558028</v>
+        <v>0.6597688663710393</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.001309108552155662</v>
+        <v>0.001303783315303731</v>
       </c>
       <c r="AN57" t="inlineStr"/>
     </row>
@@ -6526,28 +6526,28 @@
         <v>0.02625641629885448</v>
       </c>
       <c r="K58" t="n">
-        <v>0.5437601033099886</v>
+        <v>0.5115706784830822</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5821784744279264</v>
+        <v>0.5658850689946624</v>
       </c>
       <c r="M58" t="n">
-        <v>0.6358212716719776</v>
+        <v>0.6267182989987903</v>
       </c>
       <c r="N58" t="n">
-        <v>0.09424317843169754</v>
+        <v>0.08247842331091572</v>
       </c>
       <c r="O58" t="n">
-        <v>4.317748846014766</v>
+        <v>4.077750057352576</v>
       </c>
       <c r="P58" t="n">
-        <v>4.752538114922851</v>
+        <v>4.482453740644113</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.9911560287779473</v>
+        <v>0.9901554915404083</v>
       </c>
       <c r="R58" t="n">
-        <v>0.00395452125453791</v>
+        <v>0.004172220686021936</v>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
@@ -6557,38 +6557,38 @@
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
-        <v>0.9874591654783621</v>
+        <v>0.9873814863589049</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.006497725786079674</v>
+        <v>0.006517818485245936</v>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>0.9652773692445734</v>
+        <v>0.9785044102272578</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.001714992956239681</v>
+        <v>0.001349368949458598</v>
       </c>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="n">
-        <v>0.9790955914131713</v>
+        <v>0.9789336013243369</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.00555536964268686</v>
+        <v>0.005576852627025074</v>
       </c>
       <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="n">
-        <v>0.9978133890518522</v>
+        <v>0.9834196429093729</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.001199648425624015</v>
+        <v>0.003303430461131876</v>
       </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="n">
-        <v>0.9419402923964625</v>
+        <v>0.9425643257586086</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.0008533828683159153</v>
+        <v>0.0008487843429751338</v>
       </c>
       <c r="AN58" t="inlineStr"/>
     </row>
@@ -6630,10 +6630,10 @@
         <v>0.02080322163891103</v>
       </c>
       <c r="K59" t="n">
-        <v>0.5318362786808796</v>
+        <v>0.5293059348727757</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5522015830235472</v>
+        <v>0.5537011020857625</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>4.228884151391346</v>
+        <v>4.210020762317669</v>
       </c>
       <c r="P59" t="n">
-        <v>4.380628629632027</v>
+        <v>4.391793516466226</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.7824327653299111</v>
+        <v>0.7893019037545375</v>
       </c>
       <c r="R59" t="n">
-        <v>0.01996519928968916</v>
+        <v>0.01964749602167767</v>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
@@ -6661,38 +6661,38 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="n">
-        <v>0.7324247911474242</v>
+        <v>0.7511808006713493</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.03242759479864647</v>
+        <v>0.03127042221855022</v>
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
-        <v>0.4673994583749578</v>
+        <v>0.456024180753672</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.02255329314555998</v>
+        <v>0.02279286721567782</v>
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="n">
-        <v>0.1419712598525847</v>
+        <v>0.1390582692687956</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.01074618996479988</v>
+        <v>0.01076441605967704</v>
       </c>
       <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="n">
-        <v>-1.018723166284632</v>
+        <v>-1.015799239317717</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.01762406767912647</v>
+        <v>0.01761129966795367</v>
       </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="n">
-        <v>-0.6676998393311022</v>
+        <v>-0.662332675334125</v>
       </c>
       <c r="AM59" t="n">
-        <v>0.002599541677346572</v>
+        <v>0.00259535524947564</v>
       </c>
       <c r="AN59" t="inlineStr"/>
     </row>
@@ -6734,10 +6734,10 @@
         <v>0.0151609171982884</v>
       </c>
       <c r="K60" t="n">
-        <v>0.525362947003733</v>
+        <v>0.520091897588902</v>
       </c>
       <c r="L60" t="n">
-        <v>0.539655723525681</v>
+        <v>0.5419720878153651</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -6746,16 +6746,16 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4.180622353107697</v>
+        <v>4.141314459674549</v>
       </c>
       <c r="P60" t="n">
-        <v>4.287158916417223</v>
+        <v>4.304414026823678</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.8221347114998343</v>
+        <v>0.8246015048840531</v>
       </c>
       <c r="R60" t="n">
-        <v>0.02623119911056224</v>
+        <v>0.02604866526239791</v>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
@@ -6765,38 +6765,38 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="n">
-        <v>0.3323109987312934</v>
+        <v>0.34159354583436</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.05724703921997685</v>
+        <v>0.0568477079221997</v>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>-1.759004463168659</v>
+        <v>-1.724682159987728</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.008803385065024382</v>
+        <v>0.008748456186128822</v>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="n">
-        <v>0.6517873767234297</v>
+        <v>0.6533379756932023</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.006507808907720355</v>
+        <v>0.006493303028177932</v>
       </c>
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="n">
-        <v>-7.701239102907756</v>
+        <v>-7.498498238228663</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.006563358872323581</v>
+        <v>0.006486444317226213</v>
       </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="n">
-        <v>0.9398996491455879</v>
+        <v>0.9388936035041684</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.0004761190679149376</v>
+        <v>0.0004800875104764872</v>
       </c>
       <c r="AN60" t="inlineStr"/>
     </row>
@@ -6838,28 +6838,28 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K61" t="n">
-        <v>0.511350727992935</v>
+        <v>0.4963841461331371</v>
       </c>
       <c r="L61" t="n">
-        <v>0.5275557427314554</v>
+        <v>0.5417894463426931</v>
       </c>
       <c r="M61" t="n">
-        <v>0.1643066192249723</v>
+        <v>0.1204125434549804</v>
       </c>
       <c r="N61" t="n">
-        <v>0.007297154168668496</v>
+        <v>0.005130341714084428</v>
       </c>
       <c r="O61" t="n">
-        <v>4.076109010387499</v>
+        <v>3.964404756002983</v>
       </c>
       <c r="P61" t="n">
-        <v>4.19696817131211</v>
+        <v>4.303049516459621</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.973727816910127</v>
+        <v>0.973359555994064</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01155614628252248</v>
+        <v>0.01163685650571532</v>
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
@@ -6871,38 +6871,38 @@
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="n">
-        <v>0.9519202126483097</v>
+        <v>0.9512193711693016</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.0244375500810057</v>
+        <v>0.0246150143285852</v>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>0.1041420982587036</v>
+        <v>0.1004408317049967</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.005130782413625964</v>
+        <v>0.005141370487281874</v>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="n">
-        <v>0.6671695147499788</v>
+        <v>0.6638897331901619</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.005845308991986154</v>
+        <v>0.005874038839727621</v>
       </c>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="n">
-        <v>0.9052540095287053</v>
+        <v>0.9015481007833585</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.002460460775096952</v>
+        <v>0.002508118635099341</v>
       </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="n">
-        <v>0.3292133564062483</v>
+        <v>0.3338899037005356</v>
       </c>
       <c r="AM61" t="n">
-        <v>0.002231114614959896</v>
+        <v>0.002223323641177635</v>
       </c>
       <c r="AN61" t="inlineStr"/>
     </row>
@@ -6944,28 +6944,28 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K62" t="n">
-        <v>0.5144396822390431</v>
+        <v>0.5450073111588626</v>
       </c>
       <c r="L62" t="n">
-        <v>0.5177837968715534</v>
+        <v>0.5421749813290176</v>
       </c>
       <c r="M62" t="n">
-        <v>0.7725986251625739</v>
+        <v>0.7880158723096803</v>
       </c>
       <c r="N62" t="n">
-        <v>0.2344962987902775</v>
+        <v>0.2493507376162362</v>
       </c>
       <c r="O62" t="n">
-        <v>4.099154174190237</v>
+        <v>4.327041501018048</v>
       </c>
       <c r="P62" t="n">
-        <v>4.124098890966609</v>
+        <v>4.30593748337531</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.9870137523793598</v>
+        <v>0.986584021353077</v>
       </c>
       <c r="R62" t="n">
-        <v>0.007515529894221146</v>
+        <v>0.007638866953173154</v>
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
@@ -6977,38 +6977,38 @@
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="n">
-        <v>0.9824370439696873</v>
+        <v>0.9818252866463979</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.01382293089723202</v>
+        <v>0.01406161214788852</v>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
-        <v>-0.4124450722887252</v>
+        <v>-0.4102785677597443</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.003956430290641875</v>
+        <v>0.003953394804954631</v>
       </c>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="n">
-        <v>0.6184832408835603</v>
+        <v>0.6031113765094324</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.008269892792555463</v>
+        <v>0.0084348505995414</v>
       </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="n">
-        <v>0.9794062295888272</v>
+        <v>0.9795773164699276</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.002130461356511972</v>
+        <v>0.002121593282107927</v>
       </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>0.8625767458246675</v>
+        <v>0.8627701935028548</v>
       </c>
       <c r="AM62" t="n">
-        <v>0.001857147115990963</v>
+        <v>0.001855839523183129</v>
       </c>
       <c r="AN62" t="inlineStr"/>
     </row>
@@ -7050,28 +7050,28 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K63" t="n">
-        <v>0.511350727992935</v>
+        <v>0.5050331926392826</v>
       </c>
       <c r="L63" t="n">
-        <v>0.5287262843637369</v>
+        <v>0.5420051715105731</v>
       </c>
       <c r="M63" t="n">
-        <v>0.3973889742625994</v>
+        <v>0.3926051668648807</v>
       </c>
       <c r="N63" t="n">
-        <v>0.06303992147063657</v>
+        <v>0.0671576182304284</v>
       </c>
       <c r="O63" t="n">
-        <v>4.076109010387499</v>
+        <v>4.028967021104511</v>
       </c>
       <c r="P63" t="n">
-        <v>4.205694208592687</v>
+        <v>4.304657828588299</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.9927703178294861</v>
+        <v>0.993146461752922</v>
       </c>
       <c r="R63" t="n">
-        <v>0.006218904440748968</v>
+        <v>0.00605496589397783</v>
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
@@ -7083,38 +7083,38 @@
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="n">
-        <v>0.9857974779259574</v>
+        <v>0.9866640677774584</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.01312267838331806</v>
+        <v>0.01271602691257459</v>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
-        <v>0.6803438714736528</v>
+        <v>0.6671581015502692</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.002468800897135918</v>
+        <v>0.002519205200372174</v>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="n">
-        <v>0.9898053724225728</v>
+        <v>0.9894548928536367</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.001122923394629912</v>
+        <v>0.001142062695144151</v>
       </c>
       <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="n">
-        <v>0.8608348240070633</v>
+        <v>0.8586571035976174</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0.003326954813260527</v>
+        <v>0.003352884622953562</v>
       </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="n">
-        <v>0.3567099094512781</v>
+        <v>0.3617325033325532</v>
       </c>
       <c r="AM63" t="n">
-        <v>0.001852232138005888</v>
+        <v>0.00184498716418021</v>
       </c>
       <c r="AN63" t="inlineStr"/>
     </row>
@@ -7156,28 +7156,28 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K64" t="n">
-        <v>0.5144396822390431</v>
+        <v>0.4864960531109634</v>
       </c>
       <c r="L64" t="n">
-        <v>0.5224276624773413</v>
+        <v>0.5426643651982641</v>
       </c>
       <c r="M64" t="n">
-        <v>0.4727228909102524</v>
+        <v>0.4253990809188536</v>
       </c>
       <c r="N64" t="n">
-        <v>0.03409831558367884</v>
+        <v>0.03264464345778306</v>
       </c>
       <c r="O64" t="n">
-        <v>4.099154174190237</v>
+        <v>3.890560537641748</v>
       </c>
       <c r="P64" t="n">
-        <v>4.158733623545192</v>
+        <v>4.309571782714835</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.9700915473120666</v>
+        <v>0.9685932789461209</v>
       </c>
       <c r="R64" t="n">
-        <v>0.01158717598216024</v>
+        <v>0.01187386013204562</v>
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
@@ -7189,38 +7189,38 @@
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="n">
-        <v>0.950455941808288</v>
+        <v>0.9475401721383335</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.02350737361693347</v>
+        <v>0.02418921373398097</v>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
-        <v>0.2594827973358051</v>
+        <v>0.2368240865817285</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.004647280579274818</v>
+        <v>0.004717844749262385</v>
       </c>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="n">
-        <v>0.406105159627723</v>
+        <v>0.4041267257454908</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.009377616662827543</v>
+        <v>0.009393223440010902</v>
       </c>
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="n">
-        <v>0.9755240806944683</v>
+        <v>0.9747398387252907</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.0022578890012738</v>
+        <v>0.002293776722581101</v>
       </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="n">
-        <v>0.8403174254535619</v>
+        <v>0.8406716469126118</v>
       </c>
       <c r="AM64" t="n">
-        <v>0.002258774015405541</v>
+        <v>0.002256267322241268</v>
       </c>
       <c r="AN64" t="inlineStr"/>
     </row>
@@ -7262,28 +7262,28 @@
         <v>0.01715393264003622</v>
       </c>
       <c r="K65" t="n">
-        <v>0.511350727992935</v>
+        <v>0.4897404220545651</v>
       </c>
       <c r="L65" t="n">
-        <v>0.5303192543846083</v>
+        <v>0.5433803602594763</v>
       </c>
       <c r="M65" t="n">
-        <v>0.3047370258184154</v>
+        <v>0.259123631540967</v>
       </c>
       <c r="N65" t="n">
-        <v>0.027486445441136</v>
+        <v>0.02483611279084425</v>
       </c>
       <c r="O65" t="n">
-        <v>4.076109010387499</v>
+        <v>3.914793425256979</v>
       </c>
       <c r="P65" t="n">
-        <v>4.217570670219068</v>
+        <v>4.314898845667633</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.9779077313875328</v>
+        <v>0.9778646832476886</v>
       </c>
       <c r="R65" t="n">
-        <v>0.010706140635103</v>
+        <v>0.01071656634449585</v>
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
@@ -7295,38 +7295,38 @@
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="n">
-        <v>0.962972813677307</v>
+        <v>0.9629137010605526</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.02199863625984467</v>
+        <v>0.02201618928625144</v>
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>0.6568092959992452</v>
+        <v>0.6561159865697148</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.003966897327744389</v>
+        <v>0.003970902243478991</v>
       </c>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="n">
-        <v>0.6670631540901317</v>
+        <v>0.6662999847298431</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.008121496479117593</v>
+        <v>0.008130799338731775</v>
       </c>
       <c r="AH65" t="inlineStr"/>
       <c r="AI65" t="n">
-        <v>0.9368660463108107</v>
+        <v>0.9346055395823537</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.002167874522001878</v>
+        <v>0.002206343502215114</v>
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="n">
-        <v>0.5755806179917831</v>
+        <v>0.576669543402839</v>
       </c>
       <c r="AM65" t="n">
-        <v>0.001861645706000432</v>
+        <v>0.001859255976223689</v>
       </c>
       <c r="AN65" t="inlineStr"/>
     </row>
@@ -7368,28 +7368,28 @@
         <v>0.03097209188130944</v>
       </c>
       <c r="K66" t="n">
-        <v>0.5144396822390431</v>
+        <v>0.5058386519967449</v>
       </c>
       <c r="L66" t="n">
-        <v>0.523609997496202</v>
+        <v>0.5430289830034628</v>
       </c>
       <c r="M66" t="n">
-        <v>0.3940770192007441</v>
+        <v>0.3699568244870225</v>
       </c>
       <c r="N66" t="n">
-        <v>0.0278654959789714</v>
+        <v>0.0271495297562646</v>
       </c>
       <c r="O66" t="n">
-        <v>4.099154174190237</v>
+        <v>4.034978182807103</v>
       </c>
       <c r="P66" t="n">
-        <v>4.167550175975615</v>
+        <v>4.31229429669068</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.975848903255676</v>
+        <v>0.9753032211695043</v>
       </c>
       <c r="R66" t="n">
-        <v>0.01051143411307453</v>
+        <v>0.01062952113692031</v>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
@@ -7401,38 +7401,38 @@
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="n">
-        <v>0.9596489592751504</v>
+        <v>0.9586240957633888</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.02114502465381636</v>
+        <v>0.02141186885153401</v>
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>0.5200562688179975</v>
+        <v>0.5091594646722968</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.004270608973092558</v>
+        <v>0.00431881754532872</v>
       </c>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="n">
-        <v>0.679720363875698</v>
+        <v>0.6771872170638409</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.008646520421889807</v>
+        <v>0.008680646487265974</v>
       </c>
       <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="n">
-        <v>0.9544835924576348</v>
+        <v>0.9538088809542411</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0.002967204895546064</v>
+        <v>0.002989116143492937</v>
       </c>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="n">
-        <v>0.8558176924078512</v>
+        <v>0.8562093144269013</v>
       </c>
       <c r="AM66" t="n">
-        <v>0.002101917772435564</v>
+        <v>0.002099061260383179</v>
       </c>
       <c r="AN66" t="inlineStr"/>
     </row>
@@ -7474,10 +7474,10 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.5363853847768683</v>
+        <v>0.5593926976864663</v>
       </c>
       <c r="L67" t="n">
-        <v>0.5389165975484288</v>
+        <v>0.5512002886797739</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -7486,61 +7486,61 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>4.262792264471607</v>
+        <v>4.434191938319421</v>
       </c>
       <c r="P67" t="n">
-        <v>4.281656357094274</v>
+        <v>4.373176826468922</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.8938501908716237</v>
+        <v>0.9016017879882344</v>
       </c>
       <c r="R67" t="n">
-        <v>0.02356521893211269</v>
+        <v>0.02268848376272927</v>
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="n">
-        <v>0.7930789923882897</v>
+        <v>0.7840801696326886</v>
       </c>
       <c r="X67" t="n">
-        <v>0.0007907044530710683</v>
+        <v>0.0008077150173946896</v>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>0.7105199667418028</v>
+        <v>0.7336310103394725</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.05543939947565078</v>
+        <v>0.05318033173531437</v>
       </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
-        <v>0.7511674317275493</v>
+        <v>0.7404052560833239</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.00273284666674002</v>
+        <v>0.002791319834743385</v>
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="n">
-        <v>0.6473722752445826</v>
+        <v>0.6497400710206538</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.01302492600908484</v>
+        <v>0.01298112300062097</v>
       </c>
       <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="n">
-        <v>0.8122955231177984</v>
+        <v>0.8056547580162973</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.00897245283465628</v>
+        <v>0.009129790771392391</v>
       </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="n">
-        <v>0.6853069859011143</v>
+        <v>0.6647114106311883</v>
       </c>
       <c r="AM67" t="n">
-        <v>0.0001497127871956984</v>
+        <v>0.000154534243857436</v>
       </c>
       <c r="AN67" t="inlineStr"/>
     </row>
@@ -7582,10 +7582,10 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.5363853847768683</v>
+        <v>0.5709449617807177</v>
       </c>
       <c r="L68" t="n">
-        <v>0.5297471523212122</v>
+        <v>0.5513570683522704</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -7594,61 +7594,61 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>4.262792264471607</v>
+        <v>4.520199018951153</v>
       </c>
       <c r="P68" t="n">
-        <v>4.213309631801003</v>
+        <v>4.374341569472314</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.7871056652562435</v>
+        <v>0.786817436540392</v>
       </c>
       <c r="R68" t="n">
-        <v>0.03077967619079638</v>
+        <v>0.0308005048001323</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
-        <v>0.5362386777269366</v>
+        <v>0.5373321545204689</v>
       </c>
       <c r="X68" t="n">
-        <v>0.001113684600831411</v>
+        <v>0.001112370878778731</v>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>0.4232174203305504</v>
+        <v>0.4243442330989456</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.07387633074846606</v>
+        <v>0.07380413240840066</v>
       </c>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
-        <v>0.5178908718650947</v>
+        <v>0.5179732162829653</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.003705593374142564</v>
+        <v>0.003705276902267366</v>
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="n">
-        <v>0.7444400601802357</v>
+        <v>0.7400229691060459</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.007433921869821379</v>
+        <v>0.007497890498027606</v>
       </c>
       <c r="AH68" t="inlineStr"/>
       <c r="AI68" t="n">
-        <v>0.6940291167964876</v>
+        <v>0.6598640180531672</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.01247355336462033</v>
+        <v>0.01315153447838448</v>
       </c>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="n">
-        <v>0.1358580616806645</v>
+        <v>0.07980018132295041</v>
       </c>
       <c r="AM68" t="n">
-        <v>0.000826174448611449</v>
+        <v>0.0008525508457932999</v>
       </c>
       <c r="AN68" t="inlineStr"/>
     </row>
@@ -7690,28 +7690,28 @@
         <v>0.04611530568392795</v>
       </c>
       <c r="K69" t="n">
-        <v>0.5364024716033315</v>
+        <v>0.551076722083462</v>
       </c>
       <c r="L69" t="n">
-        <v>0.5369868915513369</v>
+        <v>0.5516659031529068</v>
       </c>
       <c r="M69" t="n">
-        <v>0.2404224575989623</v>
+        <v>0.2531780513365061</v>
       </c>
       <c r="N69" t="n">
-        <v>0.03182621315212187</v>
+        <v>0.03555068735324171</v>
       </c>
       <c r="O69" t="n">
-        <v>4.262919614482086</v>
+        <v>4.372256927767693</v>
       </c>
       <c r="P69" t="n">
-        <v>4.267275300149816</v>
+        <v>4.376645601003035</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.9704638355070102</v>
+        <v>0.9706578517667198</v>
       </c>
       <c r="R69" t="n">
-        <v>0.01007264680104021</v>
+        <v>0.01003950984602801</v>
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
@@ -7721,38 +7721,38 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
-        <v>0.9470874709873641</v>
+        <v>0.9481006358183436</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.01274359567105553</v>
+        <v>0.01262099929794639</v>
       </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
-        <v>0.6792455843985173</v>
+        <v>0.6860762449492538</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.003596596441665123</v>
+        <v>0.003558094502644299</v>
       </c>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="n">
-        <v>0.8519102597244683</v>
+        <v>0.8522691986763569</v>
       </c>
       <c r="AG69" t="n">
-        <v>0.01558320053393528</v>
+        <v>0.01556430384638484</v>
       </c>
       <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="n">
-        <v>0.9222937239393145</v>
+        <v>0.9214912320744859</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.008457971770504603</v>
+        <v>0.008501533371077206</v>
       </c>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="n">
-        <v>0.5379256222837439</v>
+        <v>0.5404852662213813</v>
       </c>
       <c r="AM69" t="n">
-        <v>0.004193197580545257</v>
+        <v>0.004181567420456924</v>
       </c>
       <c r="AN69" t="inlineStr"/>
     </row>
@@ -7794,10 +7794,10 @@
         <v>0.03389921553245138</v>
       </c>
       <c r="K70" t="n">
-        <v>0.5481989593924306</v>
+        <v>0.5503708566416453</v>
       </c>
       <c r="L70" t="n">
-        <v>0.5511909743090966</v>
+        <v>0.5571388279955621</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -7806,16 +7806,16 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>4.3508196972905</v>
+        <v>4.366998961487805</v>
       </c>
       <c r="P70" t="n">
-        <v>4.373107845075807</v>
+        <v>4.417406803997117</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.9577167159245279</v>
+        <v>0.9577440876459358</v>
       </c>
       <c r="R70" t="n">
-        <v>0.0100910667170145</v>
+        <v>0.01008780000550043</v>
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
@@ -7825,38 +7825,38 @@
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
-        <v>0.8859224981354885</v>
+        <v>0.8854756377355057</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.01508131466268258</v>
+        <v>0.01511082379202798</v>
       </c>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
-        <v>0.9254726862436822</v>
+        <v>0.9253918248346422</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.003166708927624993</v>
+        <v>0.003168426386055833</v>
       </c>
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="n">
-        <v>0.9428528437063111</v>
+        <v>0.9431770989989549</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.01085497252243279</v>
+        <v>0.01082413293580442</v>
       </c>
       <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="n">
-        <v>0.8099224002261393</v>
+        <v>0.8105629049318468</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.01221107077450313</v>
+        <v>0.0121904795837367</v>
       </c>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="n">
-        <v>0.7677324838809731</v>
+        <v>0.7706955991884092</v>
       </c>
       <c r="AM70" t="n">
-        <v>0.002175629133457512</v>
+        <v>0.002161706969927251</v>
       </c>
       <c r="AN70" t="inlineStr"/>
     </row>
@@ -7898,28 +7898,28 @@
         <v>0.02861063360823382</v>
       </c>
       <c r="K71" t="n">
-        <v>0.5599138393455446</v>
+        <v>0.5607074877638749</v>
       </c>
       <c r="L71" t="n">
-        <v>0.5622049658679787</v>
+        <v>0.5617693768775038</v>
       </c>
       <c r="M71" t="n">
-        <v>0.09550902688441698</v>
+        <v>0.0977182329233427</v>
       </c>
       <c r="N71" t="n">
-        <v>0.00527443978750755</v>
+        <v>0.005487302083923218</v>
       </c>
       <c r="O71" t="n">
-        <v>4.438072623193317</v>
+        <v>4.443982390835941</v>
       </c>
       <c r="P71" t="n">
-        <v>4.455132421585007</v>
+        <v>4.451889222000164</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.9608430329340657</v>
+        <v>0.9608701726475205</v>
       </c>
       <c r="R71" t="n">
-        <v>0.01080462554076457</v>
+        <v>0.01080088054605496</v>
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
@@ -7929,38 +7929,38 @@
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>0.9409942495602059</v>
+        <v>0.9410713149500289</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.01445695520314052</v>
+        <v>0.01444751125149274</v>
       </c>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
-        <v>0.763523111195119</v>
+        <v>0.7637962374064738</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.004307598296459629</v>
+        <v>0.004305109981599602</v>
       </c>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="n">
-        <v>0.9058656788503383</v>
+        <v>0.9059491140440447</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.009785397991283147</v>
+        <v>0.009781060425771194</v>
       </c>
       <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="n">
-        <v>0.8454793953925853</v>
+        <v>0.8454917558703836</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.01611130986912981</v>
+        <v>0.01611066546487351</v>
       </c>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="n">
-        <v>0.9467714649090566</v>
+        <v>0.9470678978140651</v>
       </c>
       <c r="AM71" t="n">
-        <v>0.0009013262475426636</v>
+        <v>0.0008988129735431207</v>
       </c>
       <c r="AN71" t="inlineStr"/>
     </row>
@@ -8002,28 +8002,28 @@
         <v>0.03450948851818413</v>
       </c>
       <c r="K72" t="n">
-        <v>0.5746653235323204</v>
+        <v>0.567038931825131</v>
       </c>
       <c r="L72" t="n">
-        <v>0.5761621360947605</v>
+        <v>0.5683049613018839</v>
       </c>
       <c r="M72" t="n">
-        <v>0.03396306033048613</v>
+        <v>0.02889630540394161</v>
       </c>
       <c r="N72" t="n">
-        <v>0.0009433033684369807</v>
+        <v>0.0007371817192045827</v>
       </c>
       <c r="O72" t="n">
-        <v>4.547889869855799</v>
+        <v>4.491122394156444</v>
       </c>
       <c r="P72" t="n">
-        <v>4.559029664778897</v>
+        <v>4.500547146409128</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.9586648738786917</v>
+        <v>0.9585553851690581</v>
       </c>
       <c r="R72" t="n">
-        <v>0.01161019349291535</v>
+        <v>0.01162555989621234</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -8033,38 +8033,38 @@
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>0.8577203806386557</v>
+        <v>0.857734449441842</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.01575390341218081</v>
+        <v>0.01575312450917711</v>
       </c>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
-        <v>0.8508102087670661</v>
+        <v>0.848894879494377</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.004254537300673404</v>
+        <v>0.004281760518148211</v>
       </c>
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="n">
-        <v>0.950769114686869</v>
+        <v>0.9507772774019115</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.006953265553137719</v>
+        <v>0.006952689086984144</v>
       </c>
       <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="n">
-        <v>0.8653367437505864</v>
+        <v>0.8647401787236401</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.0189029657997846</v>
+        <v>0.01894479007669282</v>
       </c>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="n">
-        <v>0.9025300453390618</v>
+        <v>0.9024114055544867</v>
       </c>
       <c r="AM72" t="n">
-        <v>0.001423512020057512</v>
+        <v>0.001424378101301547</v>
       </c>
       <c r="AN72" t="inlineStr"/>
     </row>
@@ -8106,10 +8106,10 @@
         <v>0.01985208116188355</v>
       </c>
       <c r="K73" t="n">
-        <v>0.5344803546979763</v>
+        <v>0.559424568274783</v>
       </c>
       <c r="L73" t="n">
-        <v>0.5301017193244142</v>
+        <v>0.5542545518429339</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -8118,16 +8118,16 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4.248593316158351</v>
+        <v>4.434429264975574</v>
       </c>
       <c r="P73" t="n">
-        <v>4.215952651098378</v>
+        <v>4.395925882920462</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.9946573091834153</v>
+        <v>0.9946561456582593</v>
       </c>
       <c r="R73" t="n">
-        <v>0.004861073151948811</v>
+        <v>0.004861602442636507</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -8137,38 +8137,38 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
-        <v>0.9546121604691518</v>
+        <v>0.9546487435590537</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.007314794319917047</v>
+        <v>0.007311845823971833</v>
       </c>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
-        <v>0.3242131489493414</v>
+        <v>0.3039560404521018</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.001643315281973885</v>
+        <v>0.001667763096576236</v>
       </c>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="n">
-        <v>0.9722420968345759</v>
+        <v>0.9721216431086848</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.005589939534414202</v>
+        <v>0.005602055005699502</v>
       </c>
       <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="n">
-        <v>0.8215680996015584</v>
+        <v>0.8216020872551331</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.005164768484466956</v>
+        <v>0.005164276569283708</v>
       </c>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="n">
-        <v>0.2274670930124254</v>
+        <v>0.2548639667643721</v>
       </c>
       <c r="AM73" t="n">
-        <v>0.002005293591417014</v>
+        <v>0.001969415060487452</v>
       </c>
       <c r="AN73" t="inlineStr"/>
     </row>
@@ -8210,28 +8210,28 @@
         <v>0.03595872786204279</v>
       </c>
       <c r="K74" t="n">
-        <v>0.5589968659270829</v>
+        <v>0.5539023547937509</v>
       </c>
       <c r="L74" t="n">
-        <v>0.5628820082102249</v>
+        <v>0.5600553730725266</v>
       </c>
       <c r="M74" t="n">
-        <v>0.004523646036259654</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>9.047292072519308e-05</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>4.431244325415121</v>
+        <v>4.393303571076886</v>
       </c>
       <c r="P74" t="n">
-        <v>4.460173328345116</v>
+        <v>4.439125499388008</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.9677309539763639</v>
+        <v>0.9676665578531954</v>
       </c>
       <c r="R74" t="n">
-        <v>0.008509586179370513</v>
+        <v>0.008518072814554984</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -8241,38 +8241,38 @@
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="n">
-        <v>0.7921299699481166</v>
+        <v>0.7906503234297318</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.01089278324511172</v>
+        <v>0.01093148264024884</v>
       </c>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
-        <v>0.8335583982445667</v>
+        <v>0.8362112174981582</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.001355746166108913</v>
+        <v>0.00134489853037209</v>
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="n">
-        <v>0.882042091334617</v>
+        <v>0.8820519164274934</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.01352381373464016</v>
+        <v>0.01352325050198177</v>
       </c>
       <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="n">
-        <v>0.8656572321066995</v>
+        <v>0.8658459153406076</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.007410923638675252</v>
+        <v>0.007405717521567467</v>
       </c>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="n">
-        <v>0.7301938535532755</v>
+        <v>0.7302212470244285</v>
       </c>
       <c r="AM74" t="n">
-        <v>0.001938861294998995</v>
+        <v>0.001938762866016105</v>
       </c>
       <c r="AN74" t="inlineStr"/>
     </row>
@@ -8314,10 +8314,10 @@
         <v>0.05396179716059933</v>
       </c>
       <c r="K75" t="n">
-        <v>0.5349426521273756</v>
+        <v>0.5371232694513625</v>
       </c>
       <c r="L75" t="n">
-        <v>0.5413772776291564</v>
+        <v>0.5502296926302926</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -8326,16 +8326,16 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>4.252039103170227</v>
+        <v>4.268291721388134</v>
       </c>
       <c r="P75" t="n">
-        <v>4.299992914838684</v>
+        <v>4.365943769511382</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.9676287084065744</v>
+        <v>0.9676649476119463</v>
       </c>
       <c r="R75" t="n">
-        <v>0.007105495843128927</v>
+        <v>0.007101517478086479</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -8345,38 +8345,38 @@
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>0.8878174341871221</v>
+        <v>0.8871496550952456</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.01196835557650719</v>
+        <v>0.01200392420158328</v>
       </c>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
-        <v>0.8404662438353948</v>
+        <v>0.8451492726607359</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.002410055786531198</v>
+        <v>0.002374419361649531</v>
       </c>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="n">
-        <v>0.9218240777938458</v>
+        <v>0.9222494765015478</v>
       </c>
       <c r="AG75" t="n">
-        <v>0.007338187549231866</v>
+        <v>0.007318194732568614</v>
       </c>
       <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="n">
-        <v>0.8636514196420016</v>
+        <v>0.8654124041024618</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.007004236752120719</v>
+        <v>0.006958858806779673</v>
       </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="n">
-        <v>0.9872474183398596</v>
+        <v>0.9882558302454952</v>
       </c>
       <c r="AM75" t="n">
-        <v>0.0006943506291843446</v>
+        <v>0.0006663324087990279</v>
       </c>
       <c r="AN75" t="inlineStr"/>
     </row>
@@ -8418,28 +8418,28 @@
         <v>0.03136066852465918</v>
       </c>
       <c r="K76" t="n">
-        <v>0.5346548357892247</v>
+        <v>0.5601812859072123</v>
       </c>
       <c r="L76" t="n">
-        <v>0.5300814593897085</v>
+        <v>0.5542270421319764</v>
       </c>
       <c r="M76" t="n">
-        <v>0.01737952908113416</v>
+        <v>0.0317967981228201</v>
       </c>
       <c r="N76" t="n">
-        <v>0.0004253783814230983</v>
+        <v>0.001097192311935573</v>
       </c>
       <c r="O76" t="n">
-        <v>4.249893838573551</v>
+        <v>4.440064137367118</v>
       </c>
       <c r="P76" t="n">
-        <v>4.215801585584356</v>
+        <v>4.395720827941094</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.9927063952910966</v>
+        <v>0.9927200006677219</v>
       </c>
       <c r="R76" t="n">
-        <v>0.005358970361255332</v>
+        <v>0.005353969758232399</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -8449,38 +8449,38 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="n">
-        <v>0.9145938065215979</v>
+        <v>0.914825167941657</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.008314678801162444</v>
+        <v>0.008303409123960276</v>
       </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
-        <v>0.9202508395993567</v>
+        <v>0.9190752618506144</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.0007785897160244444</v>
+        <v>0.0007843072954074451</v>
       </c>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="n">
-        <v>0.9595988646800295</v>
+        <v>0.9596394167327328</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.00848510712679533</v>
+        <v>0.008480847656170387</v>
       </c>
       <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="n">
-        <v>0.9883664164483551</v>
+        <v>0.9882871061576899</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.0009065145176326545</v>
+        <v>0.0009095992855558673</v>
       </c>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="n">
-        <v>0.6815633846033107</v>
+        <v>0.6886002130920674</v>
       </c>
       <c r="AM76" t="n">
-        <v>0.001016818384862664</v>
+        <v>0.001005520770240395</v>
       </c>
       <c r="AN76" t="inlineStr"/>
     </row>
@@ -8522,28 +8522,28 @@
         <v>0.02805201336700053</v>
       </c>
       <c r="K77" t="n">
-        <v>0.5641779213995787</v>
+        <v>0.5411801492891922</v>
       </c>
       <c r="L77" t="n">
-        <v>0.5768997019835649</v>
+        <v>0.5509761206511651</v>
       </c>
       <c r="M77" t="n">
-        <v>0.101484807413155</v>
+        <v>0.07522527212345076</v>
       </c>
       <c r="N77" t="n">
-        <v>0.007418649492630054</v>
+        <v>0.004190561813070513</v>
       </c>
       <c r="O77" t="n">
-        <v>4.469822402045478</v>
+        <v>4.29852478003157</v>
       </c>
       <c r="P77" t="n">
-        <v>4.564512749974802</v>
+        <v>4.371503445291739</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.9772123799273464</v>
+        <v>0.9763471268795081</v>
       </c>
       <c r="R77" t="n">
-        <v>0.009052270669250888</v>
+        <v>0.009222528314083349</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -8553,38 +8553,38 @@
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>0.8220483513669413</v>
+        <v>0.8168364612673467</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.00768566240814275</v>
+        <v>0.007797399915782872</v>
       </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
-        <v>-3.855089779392717</v>
+        <v>-3.599334688359904</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.002154784495603091</v>
+        <v>0.002097262136702771</v>
       </c>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="n">
-        <v>0.9107431708256462</v>
+        <v>0.9033801265902224</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.01295119011792225</v>
+        <v>0.01347479551908767</v>
       </c>
       <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="n">
-        <v>0.2031653775210075</v>
+        <v>0.2022002169169386</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.01333058697612641</v>
+        <v>0.01333865782505892</v>
       </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="n">
-        <v>0.8894801402889401</v>
+        <v>0.8856566600326781</v>
       </c>
       <c r="AM77" t="n">
-        <v>0.0007534214450302884</v>
+        <v>0.0007663431009781172</v>
       </c>
       <c r="AN77" t="inlineStr"/>
     </row>
@@ -8626,28 +8626,28 @@
         <v>0.01052672116974796</v>
       </c>
       <c r="K78" t="n">
-        <v>0.5807095945396936</v>
+        <v>0.5620493770299488</v>
       </c>
       <c r="L78" t="n">
-        <v>0.5852554319468414</v>
+        <v>0.5617286666631309</v>
       </c>
       <c r="M78" t="n">
-        <v>0.1700437686371762</v>
+        <v>0.1609547940455152</v>
       </c>
       <c r="N78" t="n">
-        <v>0.01711021231977296</v>
+        <v>0.01512461808946006</v>
       </c>
       <c r="O78" t="n">
-        <v>4.592870244659815</v>
+        <v>4.453974155675245</v>
       </c>
       <c r="P78" t="n">
-        <v>4.626692599605751</v>
+        <v>4.451586136153072</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.982350716148363</v>
+        <v>0.9822834841454851</v>
       </c>
       <c r="R78" t="n">
-        <v>0.009647070578454563</v>
+        <v>0.009665427566204674</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -8657,38 +8657,38 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="n">
-        <v>0.3450575126657476</v>
+        <v>0.3422108380902777</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.009810696822512659</v>
+        <v>0.009831994555338473</v>
       </c>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
-        <v>0.1255077325643539</v>
+        <v>0.1436898764006889</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.001093817573228961</v>
+        <v>0.00108238670420082</v>
       </c>
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="n">
-        <v>0.8873680706857859</v>
+        <v>0.8862268703883346</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.01380148834105679</v>
+        <v>0.01387123129782569</v>
       </c>
       <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="n">
-        <v>-0.5730367306035871</v>
+        <v>-0.567516176031176</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.01321318094990031</v>
+        <v>0.01318997481721795</v>
       </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="n">
-        <v>-0.2910560924390135</v>
+        <v>-0.3194356206241811</v>
       </c>
       <c r="AM78" t="n">
-        <v>0.001677621369236373</v>
+        <v>0.001695959574249089</v>
       </c>
       <c r="AN78" t="inlineStr"/>
     </row>
@@ -8730,10 +8730,10 @@
         <v>3.234988232153624e-17</v>
       </c>
       <c r="K79" t="n">
-        <v>0.5515163866565659</v>
+        <v>0.5610550899029443</v>
       </c>
       <c r="L79" t="n">
-        <v>0.5597358919004219</v>
+        <v>0.5628967104249973</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -8742,58 +8742,58 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>4.375531902801428</v>
+        <v>4.446570697558703</v>
       </c>
       <c r="P79" t="n">
-        <v>4.436745638812805</v>
+        <v>4.460283018455883</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.9810915793406919</v>
+        <v>0.982243384299494</v>
       </c>
       <c r="R79" t="n">
-        <v>0.02022731371680062</v>
+        <v>0.01960156198295226</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="n">
-        <v>0.917683960597017</v>
+        <v>0.9236410073665533</v>
       </c>
       <c r="U79" t="n">
-        <v>0.04456378051768834</v>
+        <v>0.04292100560411066</v>
       </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="n">
-        <v>0.6982275188905437</v>
+        <v>0.6981942464365025</v>
       </c>
       <c r="X79" t="n">
-        <v>0.001546068265304778</v>
+        <v>0.001546153495189306</v>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
-        <v>0.9863612624336334</v>
+        <v>0.9839019855367579</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.009126954050928308</v>
+        <v>0.009915735517281758</v>
       </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
-        <v>0.8740663970732334</v>
+        <v>0.874554951078451</v>
       </c>
       <c r="AD79" t="n">
-        <v>0.00268213465456372</v>
+        <v>0.002676926985810397</v>
       </c>
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="n">
-        <v>0.9897139566822728</v>
+        <v>0.988746861923252</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.003254008125341544</v>
+        <v>0.003403543318451284</v>
       </c>
       <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="n">
-        <v>0.8978384099379954</v>
+        <v>0.895514667962212</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.008541232315438943</v>
+        <v>0.008637824505324111</v>
       </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
@@ -8838,70 +8838,70 @@
         <v>7.592549229303372e-17</v>
       </c>
       <c r="K80" t="n">
-        <v>0.5606867247544488</v>
+        <v>0.5736197870707861</v>
       </c>
       <c r="L80" t="n">
-        <v>0.5630026861770286</v>
+        <v>0.5623591394170167</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>0.02403048939813879</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>0.0004806097879627758</v>
       </c>
       <c r="O80" t="n">
-        <v>4.443827784785064</v>
+        <v>4.540108243019789</v>
       </c>
       <c r="P80" t="n">
-        <v>4.461072072876458</v>
+        <v>4.456279041148765</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.9950575792360774</v>
+        <v>0.9956478964383095</v>
       </c>
       <c r="R80" t="n">
-        <v>0.009716953321653975</v>
+        <v>0.009118215861198689</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="n">
-        <v>0.9836332853566682</v>
+        <v>0.9860382557411835</v>
       </c>
       <c r="U80" t="n">
-        <v>0.02031538894866413</v>
+        <v>0.01876351616049722</v>
       </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="n">
-        <v>0.9832320561902002</v>
+        <v>0.9831985104016491</v>
       </c>
       <c r="X80" t="n">
-        <v>0.0003463800407259961</v>
+        <v>0.0003467263499106868</v>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>0.987128533635359</v>
+        <v>0.9868830554320623</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.007284075370561012</v>
+        <v>0.007353206449812684</v>
       </c>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
-        <v>0.984920746264807</v>
+        <v>0.9849980239359901</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.001021721369137113</v>
+        <v>0.001019099964008648</v>
       </c>
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="n">
-        <v>0.9894531725476404</v>
+        <v>0.9891682159533975</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.005447227910761254</v>
+        <v>0.00552032468929934</v>
       </c>
       <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="n">
-        <v>0.9870430955305496</v>
+        <v>0.9863948862715952</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.003729204003768846</v>
+        <v>0.003821348107016561</v>
       </c>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
@@ -8946,66 +8946,66 @@
         <v>9.901399624920571e-18</v>
       </c>
       <c r="K81" t="n">
-        <v>0.5754981068107931</v>
+        <v>0.58328369577433</v>
       </c>
       <c r="L81" t="n">
-        <v>0.5743491971556541</v>
+        <v>0.5692071072888926</v>
       </c>
       <c r="M81" t="n">
-        <v>0.2922075727616273</v>
+        <v>0.3055147787262624</v>
       </c>
       <c r="N81" t="n">
-        <v>0.04136741539768771</v>
+        <v>0.04150523718463438</v>
       </c>
       <c r="O81" t="n">
-        <v>4.554087837697824</v>
+        <v>4.612023486339785</v>
       </c>
       <c r="P81" t="n">
-        <v>4.545537055193345</v>
+        <v>4.507262339291565</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.9911891535193372</v>
+        <v>0.9911866101913818</v>
       </c>
       <c r="R81" t="n">
-        <v>0.01275631371774209</v>
+        <v>0.01275815469570156</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="n">
-        <v>0.9733545140706205</v>
+        <v>0.9734507136147083</v>
       </c>
       <c r="U81" t="n">
-        <v>0.02446241267550627</v>
+        <v>0.02441821380386815</v>
       </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>0.9777013079218474</v>
+        <v>0.9774051182660005</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.009841601322405368</v>
+        <v>0.009906747844501801</v>
       </c>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
-        <v>0.9762968117301813</v>
+        <v>0.9752122397824157</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.0009348854930458877</v>
+        <v>0.0009560347556745789</v>
       </c>
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="n">
-        <v>0.9661821842293723</v>
+        <v>0.9660126718879699</v>
       </c>
       <c r="AG81" t="n">
-        <v>0.00589977726463643</v>
+        <v>0.005914545145569408</v>
       </c>
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="n">
-        <v>0.9648676124138046</v>
+        <v>0.9644875473940431</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0.009092280526573373</v>
+        <v>0.009141328745771291</v>
       </c>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
@@ -9050,66 +9050,66 @@
         <v>1.336850539002381e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.5754874687447049</v>
+        <v>0.5822582513598026</v>
       </c>
       <c r="L82" t="n">
-        <v>0.5741509984982603</v>
+        <v>0.5830713692718481</v>
       </c>
       <c r="M82" t="n">
-        <v>0.483158667679818</v>
+        <v>0.5111293151775895</v>
       </c>
       <c r="N82" t="n">
-        <v>0.1332078799512766</v>
+        <v>0.1383307409555058</v>
       </c>
       <c r="O82" t="n">
-        <v>4.554008665274212</v>
+        <v>4.604393606839464</v>
       </c>
       <c r="P82" t="n">
-        <v>4.544061883568968</v>
+        <v>4.610443667869723</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.9616798147797319</v>
+        <v>0.963308714175231</v>
       </c>
       <c r="R82" t="n">
-        <v>0.02640698766941131</v>
+        <v>0.02583964416135188</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="n">
-        <v>0.8932666556085175</v>
+        <v>0.8993020125474719</v>
       </c>
       <c r="U82" t="n">
-        <v>0.05100655637683447</v>
+        <v>0.04954346078878032</v>
       </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>0.8928891879385397</v>
+        <v>0.8932479277357017</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.02191388134809261</v>
+        <v>0.02187715314737478</v>
       </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
-        <v>-0.5991756268224644</v>
+        <v>-0.6067829403559379</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.003711524611871798</v>
+        <v>0.003720342040132102</v>
       </c>
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="n">
-        <v>0.7411156938295489</v>
+        <v>0.7402802853326962</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.01830512245911502</v>
+        <v>0.01833463359107143</v>
       </c>
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="n">
-        <v>0.979975500164452</v>
+        <v>0.9802022669412829</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.007476969741346064</v>
+        <v>0.007434512852158392</v>
       </c>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
@@ -9152,66 +9152,66 @@
         <v>0.002282733977536599</v>
       </c>
       <c r="K83" t="n">
-        <v>0.570498636937081</v>
+        <v>0.5876714572894921</v>
       </c>
       <c r="L83" t="n">
-        <v>0.5662011928415824</v>
+        <v>0.5692117569781444</v>
       </c>
       <c r="M83" t="n">
-        <v>0.2957332180206774</v>
+        <v>0.07981456649599261</v>
       </c>
       <c r="N83" t="n">
-        <v>0.006726699870354715</v>
+        <v>0.002585205517971454</v>
       </c>
       <c r="O83" t="n">
-        <v>4.516876761044007</v>
+        <v>4.644667992207475</v>
       </c>
       <c r="P83" t="n">
-        <v>4.484885022066504</v>
+        <v>4.507289777567745</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.9766404940914197</v>
+        <v>0.9773624851312184</v>
       </c>
       <c r="R83" t="n">
-        <v>0.01829846262545317</v>
+        <v>0.01801346049152716</v>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="n">
-        <v>0.9257323866947215</v>
+        <v>0.9289935652030937</v>
       </c>
       <c r="U83" t="n">
-        <v>0.03531897740202598</v>
+        <v>0.03453482350741809</v>
       </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="n">
-        <v>0.9554564304261555</v>
+        <v>0.9554906605334325</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.01017720663378364</v>
+        <v>0.01017329547634024</v>
       </c>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
-        <v>0.6712699585152895</v>
+        <v>0.6753332431721435</v>
       </c>
       <c r="AD83" t="n">
-        <v>0.006408124960713961</v>
+        <v>0.006368397836927414</v>
       </c>
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="n">
-        <v>0.9253247647570578</v>
+        <v>0.9250070261678919</v>
       </c>
       <c r="AG83" t="n">
-        <v>0.01049011386966141</v>
+        <v>0.01051240757884076</v>
       </c>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="n">
-        <v>0.8762026581094186</v>
+        <v>0.8739360413416268</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.0131170277949463</v>
+        <v>0.01323656355511342</v>
       </c>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
@@ -9254,66 +9254,66 @@
         <v>0.001579598306755124</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5613395544464862</v>
+        <v>0.5796778824583331</v>
       </c>
       <c r="L84" t="n">
-        <v>0.5554563956272078</v>
+        <v>0.563378885391299</v>
       </c>
       <c r="M84" t="n">
-        <v>0.471346403715812</v>
+        <v>0.4887897418573557</v>
       </c>
       <c r="N84" t="n">
-        <v>0.06116193299676035</v>
+        <v>0.06502288007868076</v>
       </c>
       <c r="O84" t="n">
-        <v>4.44868884650036</v>
+        <v>4.58519307493649</v>
       </c>
       <c r="P84" t="n">
-        <v>4.404877002124129</v>
+        <v>4.463870603773183</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.9980807493872891</v>
+        <v>0.9980618652316851</v>
       </c>
       <c r="R84" t="n">
-        <v>0.005144658934719338</v>
+        <v>0.005169906999916839</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="n">
-        <v>0.9973799448422898</v>
+        <v>0.9972558346115841</v>
       </c>
       <c r="U84" t="n">
-        <v>0.00684602351160612</v>
+        <v>0.00700629324243527</v>
       </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="n">
-        <v>0.9955976382919735</v>
+        <v>0.9957378997957589</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.00452662424180725</v>
+        <v>0.004453930251991188</v>
       </c>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
-        <v>0.9821126793913358</v>
+        <v>0.9849722483041821</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.001210863368324516</v>
+        <v>0.001109863325018791</v>
       </c>
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="n">
-        <v>0.9656705975524613</v>
+        <v>0.9656581688568103</v>
       </c>
       <c r="AG84" t="n">
-        <v>0.007636163686613108</v>
+        <v>0.007637545868635714</v>
       </c>
       <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="n">
-        <v>0.9949862084950726</v>
+        <v>0.9950362094096518</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.002280795229620106</v>
+        <v>0.002269393917902525</v>
       </c>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
@@ -9356,66 +9356,66 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.5587195126399009</v>
+        <v>0.5746033622443787</v>
       </c>
       <c r="L85" t="n">
-        <v>0.5588588245930418</v>
+        <v>0.5683264924564659</v>
       </c>
       <c r="M85" t="n">
-        <v>0.1124804050600758</v>
+        <v>0.1499511902499464</v>
       </c>
       <c r="N85" t="n">
-        <v>0.003981221874916435</v>
+        <v>0.005244004775718696</v>
       </c>
       <c r="O85" t="n">
-        <v>4.429178952661008</v>
+        <v>4.54742871756644</v>
       </c>
       <c r="P85" t="n">
-        <v>4.430216359617308</v>
+        <v>4.500705163438571</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.9914422549453106</v>
+        <v>0.9935362787147766</v>
       </c>
       <c r="R85" t="n">
-        <v>0.01156128054940215</v>
+        <v>0.0100477212629602</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="n">
-        <v>0.9705503150716309</v>
+        <v>0.9807012436553757</v>
       </c>
       <c r="U85" t="n">
-        <v>0.0220314258508642</v>
+        <v>0.0178347464801778</v>
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="n">
-        <v>0.9846490602232969</v>
+        <v>0.9849304295659268</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.009547971889324951</v>
+        <v>0.009460064208359369</v>
       </c>
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
-        <v>0.760661052242488</v>
+        <v>0.7662515113579828</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.007644940697759106</v>
+        <v>0.007555128198113705</v>
       </c>
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="n">
-        <v>0.9706246573087978</v>
+        <v>0.9692067255052649</v>
       </c>
       <c r="AG85" t="n">
-        <v>0.005535669047119192</v>
+        <v>0.005667696465736062</v>
       </c>
       <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="n">
-        <v>0.9967108366888473</v>
+        <v>0.9901688672941981</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.001637008679564139</v>
+        <v>0.002830153835848248</v>
       </c>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
@@ -9458,66 +9458,66 @@
         <v>0.001282293415705915</v>
       </c>
       <c r="K86" t="n">
-        <v>0.5641723537032975</v>
+        <v>0.5894067212606844</v>
       </c>
       <c r="L86" t="n">
-        <v>0.5565471426668797</v>
+        <v>0.5676365455263553</v>
       </c>
       <c r="M86" t="n">
-        <v>0.2082888901432743</v>
+        <v>0.164012961575661</v>
       </c>
       <c r="N86" t="n">
-        <v>0.005544616762431973</v>
+        <v>0.005908826605035044</v>
       </c>
       <c r="O86" t="n">
-        <v>4.469780948890098</v>
+        <v>4.65757690113081</v>
       </c>
       <c r="P86" t="n">
-        <v>4.412999639060022</v>
+        <v>4.495557844070868</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.9943109733483647</v>
+        <v>0.99596761356452</v>
       </c>
       <c r="R86" t="n">
-        <v>0.008995802874146409</v>
+        <v>0.007573593973731987</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="n">
-        <v>0.9866793716763271</v>
+        <v>0.9929286106879106</v>
       </c>
       <c r="U86" t="n">
-        <v>0.01604286381796461</v>
+        <v>0.01168885349986235</v>
       </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="n">
-        <v>0.9955569550904998</v>
+        <v>0.9954974462410984</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.003877288685638122</v>
+        <v>0.003903167956676739</v>
       </c>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
-        <v>0.6127356151679801</v>
+        <v>0.6317332072218212</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.009314961110054865</v>
+        <v>0.009083611398404412</v>
       </c>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="n">
-        <v>0.9911290386568266</v>
+        <v>0.9900788421902922</v>
       </c>
       <c r="AG86" t="n">
-        <v>0.004815361841081511</v>
+        <v>0.005092426417373469</v>
       </c>
       <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="n">
-        <v>0.9789252913502577</v>
+        <v>0.9749218023384573</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.004717975156419354</v>
+        <v>0.005146630869014135</v>
       </c>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
@@ -9560,66 +9560,66 @@
         <v>1.327388309752159e-16</v>
       </c>
       <c r="K87" t="n">
-        <v>0.5810708420402754</v>
+        <v>0.5852585427094423</v>
       </c>
       <c r="L87" t="n">
-        <v>0.5705287853586947</v>
+        <v>0.5859857945326804</v>
       </c>
       <c r="M87" t="n">
-        <v>0.7615104027509046</v>
+        <v>0.7690944556535395</v>
       </c>
       <c r="N87" t="n">
-        <v>0.2012504147084422</v>
+        <v>0.2037190790581341</v>
       </c>
       <c r="O87" t="n">
-        <v>4.595558295125066</v>
+        <v>4.675916314716923</v>
       </c>
       <c r="P87" t="n">
-        <v>4.517098298482443</v>
+        <v>4.634914678866079</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.9615623298411046</v>
+        <v>0.9654542854591001</v>
       </c>
       <c r="R87" t="n">
-        <v>0.02197895212442644</v>
+        <v>0.02083653717399546</v>
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="n">
-        <v>0.8989766282044465</v>
+        <v>0.9138792276411978</v>
       </c>
       <c r="U87" t="n">
-        <v>0.04121270445040497</v>
+        <v>0.03805170690026567</v>
       </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="n">
-        <v>0.8861032693803607</v>
+        <v>0.8841444013148053</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.01886232952221586</v>
+        <v>0.01902384117889745</v>
       </c>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
-        <v>0.9255473295446355</v>
+        <v>0.9259497523490778</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.003198357166042252</v>
+        <v>0.003189701762696498</v>
       </c>
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="n">
-        <v>0.7475974437931036</v>
+        <v>0.745779150959581</v>
       </c>
       <c r="AG87" t="n">
-        <v>0.01775070798155601</v>
+        <v>0.01781453076027997</v>
       </c>
       <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="n">
-        <v>0.9858641352478882</v>
+        <v>0.9867903147446578</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.005981645000333304</v>
+        <v>0.00578236735679459</v>
       </c>
       <c r="AK87" t="inlineStr"/>
       <c r="AL87" t="inlineStr"/>
@@ -9662,66 +9662,66 @@
         <v>1.912261794240524e-16</v>
       </c>
       <c r="K88" t="n">
-        <v>0.5819485907991109</v>
+        <v>0.590586229268512</v>
       </c>
       <c r="L88" t="n">
-        <v>0.5780673756851117</v>
+        <v>0.5714000476581824</v>
       </c>
       <c r="M88" t="n">
-        <v>0.7352523758330665</v>
+        <v>0.7351866714466452</v>
       </c>
       <c r="N88" t="n">
-        <v>0.08187920143855786</v>
+        <v>0.08236529828281203</v>
       </c>
       <c r="O88" t="n">
-        <v>4.602089508487431</v>
+        <v>4.666351041259506</v>
       </c>
       <c r="P88" t="n">
-        <v>4.573208274084705</v>
+        <v>4.523585173738249</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.9875845355750781</v>
+        <v>0.9878274091918079</v>
       </c>
       <c r="R88" t="n">
-        <v>0.01306384894798392</v>
+        <v>0.01293543913470825</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="n">
-        <v>0.9626411832406975</v>
+        <v>0.9644307692616069</v>
       </c>
       <c r="U88" t="n">
-        <v>0.02436081841961832</v>
+        <v>0.02377018461083583</v>
       </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="n">
-        <v>0.967073704369789</v>
+        <v>0.9660910220376986</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.01026679732373331</v>
+        <v>0.01041887678790007</v>
       </c>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
-        <v>-0.02116167155352056</v>
+        <v>-0.02401621413803712</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.006303487591916437</v>
+        <v>0.006312291788673499</v>
       </c>
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="n">
-        <v>0.9787062191016869</v>
+        <v>0.977555910915916</v>
       </c>
       <c r="AG88" t="n">
-        <v>0.004349462715633973</v>
+        <v>0.004465398413132405</v>
       </c>
       <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="n">
-        <v>0.9538171056280776</v>
+        <v>0.9502231692949223</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.009788379006880331</v>
+        <v>0.01016210841659788</v>
       </c>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
@@ -9764,66 +9764,66 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.5774046468347739</v>
+        <v>0.5779806317272085</v>
       </c>
       <c r="L89" t="n">
-        <v>0.5824754213300122</v>
+        <v>0.5697550295019791</v>
       </c>
       <c r="M89" t="n">
-        <v>0.5722630313168107</v>
+        <v>0.5626937765709654</v>
       </c>
       <c r="N89" t="n">
-        <v>0.07109788655413651</v>
+        <v>0.06639920394480998</v>
       </c>
       <c r="O89" t="n">
-        <v>4.568276553466714</v>
+        <v>4.572562927515825</v>
       </c>
       <c r="P89" t="n">
-        <v>4.606008832177676</v>
+        <v>4.511340762019881</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.9966616333482017</v>
+        <v>0.9966650542560334</v>
       </c>
       <c r="R89" t="n">
-        <v>0.006837510103119388</v>
+        <v>0.006834005921347447</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="n">
-        <v>0.9949259974393911</v>
+        <v>0.9949552893220264</v>
       </c>
       <c r="U89" t="n">
-        <v>0.009734593451490466</v>
+        <v>0.009706454197730939</v>
       </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
-        <v>0.9975663020806397</v>
+        <v>0.9975449749781534</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.003759515187666083</v>
+        <v>0.003775952041262557</v>
       </c>
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
-        <v>0.9182673935933386</v>
+        <v>0.9174350813537422</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.002770592879012623</v>
+        <v>0.002784664113660759</v>
       </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="n">
-        <v>0.9931165791343617</v>
+        <v>0.9931407185205504</v>
       </c>
       <c r="AG89" t="n">
-        <v>0.00201573676697352</v>
+        <v>0.002012199181207847</v>
       </c>
       <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="n">
-        <v>0.9453741462725874</v>
+        <v>0.9453163248355907</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.01063588634408253</v>
+        <v>0.01064151389529388</v>
       </c>
       <c r="AK89" t="inlineStr"/>
       <c r="AL89" t="inlineStr"/>
@@ -9866,66 +9866,66 @@
         <v>0.03004752976171331</v>
       </c>
       <c r="K90" t="n">
-        <v>0.5245953145928745</v>
+        <v>0.5729495712298517</v>
       </c>
       <c r="L90" t="n">
-        <v>0.4397615814187343</v>
+        <v>0.5382134011256914</v>
       </c>
       <c r="M90" t="n">
-        <v>0.6658097890400982</v>
+        <v>0.6654125091509961</v>
       </c>
       <c r="N90" t="n">
-        <v>0.1282164748251007</v>
+        <v>0.1308745974910419</v>
       </c>
       <c r="O90" t="n">
-        <v>4.174898420666395</v>
+        <v>4.535119873192954</v>
       </c>
       <c r="P90" t="n">
-        <v>3.540212064046116</v>
+        <v>4.276387088985127</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.9888197130630613</v>
+        <v>0.9895602482751137</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01398190227870671</v>
+        <v>0.01351091845765313</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="n">
-        <v>0.9793871642484947</v>
+        <v>0.9806794056833744</v>
       </c>
       <c r="U90" t="n">
-        <v>0.02325170253351274</v>
+        <v>0.02251106944082309</v>
       </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="n">
-        <v>0.986677443604175</v>
+        <v>0.9877028042845071</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.0149107279065413</v>
+        <v>0.0143254444219854</v>
       </c>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>0.8370143710158326</v>
+        <v>0.8339382169405896</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.004599615000052214</v>
+        <v>0.004642818150404649</v>
       </c>
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="n">
-        <v>0.9950257095338867</v>
+        <v>0.9949739767678161</v>
       </c>
       <c r="AG90" t="n">
-        <v>0.0005371996305271803</v>
+        <v>0.0005399858509917179</v>
       </c>
       <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="n">
-        <v>0.980940412403664</v>
+        <v>0.9843548440065371</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.004525195903723297</v>
+        <v>0.004099874704513088</v>
       </c>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>

--- a/tables/N-Retention/Local_perf_matrix_protection_False_vo_False_CUE_False.xlsx
+++ b/tables/N-Retention/Local_perf_matrix_protection_False_vo_False_CUE_False.xlsx
@@ -653,43 +653,43 @@
         <v>70.85714285714286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.432164952517398</v>
+        <v>0.4321649524844555</v>
       </c>
       <c r="G2" t="n">
         <v>0.04480286738351254</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2627803891781534</v>
+        <v>0.2627803892434106</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2428872347095719</v>
+        <v>0.2428872346838566</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01736455621136393</v>
+        <v>0.01736455620476475</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5642466039963522</v>
+        <v>0.5642466029735214</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5600604317922732</v>
+        <v>0.5600604318943019</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3115413050704156</v>
+        <v>0.3115410997810887</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04316546565134319</v>
+        <v>0.04316540680981906</v>
       </c>
       <c r="O2" t="n">
-        <v>4.470333763738433</v>
+        <v>4.470333756123172</v>
       </c>
       <c r="P2" t="n">
-        <v>4.439163888185504</v>
+        <v>4.439163888945531</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9928303656964881</v>
+        <v>0.9928303723875366</v>
       </c>
       <c r="R2" t="n">
-        <v>0.005204895081949752</v>
+        <v>0.005204892653987823</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
@@ -699,38 +699,38 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>0.9900361442677965</v>
+        <v>0.9900361634791055</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007238785599476895</v>
+        <v>0.007238778620024508</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>0.9996418919322152</v>
+        <v>0.9996418839777994</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0001245155083495076</v>
+        <v>0.0001245168912318092</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>0.9967185295930294</v>
+        <v>0.9967185351181548</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.002417010965324996</v>
+        <v>0.002417008931553043</v>
       </c>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>0.9626874346096489</v>
+        <v>0.9626874387684075</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.008219521528311862</v>
+        <v>0.008219521068602277</v>
       </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>0.9324701748037454</v>
+        <v>0.9324701456137027</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0007819999628291574</v>
+        <v>0.0007820001267523491</v>
       </c>
       <c r="AN2" t="inlineStr"/>
     </row>
@@ -757,43 +757,43 @@
         <v>82.71186440677965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4230480283044928</v>
+        <v>0.4230480283479805</v>
       </c>
       <c r="G3" t="n">
         <v>0.03838147280770231</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3417824749441816</v>
+        <v>0.341782474747073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1733633998846752</v>
+        <v>0.1733633999809309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02342462405894816</v>
+        <v>0.02342462411631339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5500633872661924</v>
+        <v>0.5500633869103069</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5568990549743057</v>
+        <v>0.556899055006427</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9969047014159728</v>
+        <v>0.9969047015221654</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9935845596183941</v>
+        <v>0.9935845596496604</v>
       </c>
       <c r="O3" t="n">
-        <v>4.364708589435769</v>
+        <v>4.364708586784724</v>
       </c>
       <c r="P3" t="n">
-        <v>4.415621198484515</v>
+        <v>4.415621198723657</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9879759116995286</v>
+        <v>0.9879759087523498</v>
       </c>
       <c r="R3" t="n">
-        <v>0.006668003938890086</v>
+        <v>0.006668004755180406</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
@@ -803,38 +803,38 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9787807615872389</v>
+        <v>0.9787807503866783</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00936035754344834</v>
+        <v>0.009360360015471384</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>-1.057186228100539</v>
+        <v>-1.057186228100401</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.003512210996364732</v>
+        <v>0.003512210996364615</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>0.9640213864734405</v>
+        <v>0.9640213842506832</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.009199604886482747</v>
+        <v>0.009199605163658661</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>0.9621069258529816</v>
+        <v>0.9621069263929314</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.004720955755810866</v>
+        <v>0.004720955725389911</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>0.7158513143953831</v>
+        <v>0.7158513327676689</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.002174954349716137</v>
+        <v>0.002174954283268422</v>
       </c>
       <c r="AN3" t="inlineStr"/>
     </row>
@@ -861,43 +861,43 @@
         <v>38.828125</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5026131523004256</v>
+        <v>0.5026131523545405</v>
       </c>
       <c r="G4" t="n">
         <v>0.08176040369199321</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1418117772088146</v>
+        <v>0.1418117771640022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2720282171617107</v>
+        <v>0.2720282171735377</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001786449637055907</v>
+        <v>0.00178644961592619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5593743245998097</v>
+        <v>0.5593743721000277</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5642265507449217</v>
+        <v>0.5642265405673528</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3976351111137273</v>
+        <v>0.397631635088232</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0476639932013033</v>
+        <v>0.04766308868379831</v>
       </c>
       <c r="O4" t="n">
-        <v>4.434055121667282</v>
+        <v>4.434055475381553</v>
       </c>
       <c r="P4" t="n">
-        <v>4.470183147467676</v>
+        <v>4.470183071708111</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9300663600145919</v>
+        <v>0.9300665913753172</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01729924446944472</v>
+        <v>0.01729921585569803</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -907,38 +907,38 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>0.9108761258733526</v>
+        <v>0.9108767494391047</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0262866128401436</v>
+        <v>0.02628652088452381</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0.9985733007969231</v>
+        <v>0.9985729042160666</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0004700826471958413</v>
+        <v>0.0004701479773036281</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>0.4286801650323083</v>
+        <v>0.4286797555305465</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.02460067643119307</v>
+        <v>0.0246006852437392</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0.9444163706116997</v>
+        <v>0.9444165260489731</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.009779266826449634</v>
+        <v>0.009779253153289943</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>0.8207175031984019</v>
+        <v>0.8207172182587823</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.002145693995884795</v>
+        <v>0.00214569570200861</v>
       </c>
       <c r="AN4" t="inlineStr"/>
     </row>
@@ -965,43 +965,43 @@
         <v>67.8082191780822</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4142260612899763</v>
+        <v>0.414226061397911</v>
       </c>
       <c r="G5" t="n">
         <v>0.04681738015071348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2912830177383198</v>
+        <v>0.2912830175544637</v>
       </c>
       <c r="I5" t="n">
-        <v>0.217379291417003</v>
+        <v>0.2173792914645093</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03029424940398749</v>
+        <v>0.03029424943240262</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5455450639454225</v>
+        <v>0.5455450650049486</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5561727268014236</v>
+        <v>0.5561727271627208</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2956961141435077</v>
+        <v>0.2956966961406499</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04353140792920152</v>
+        <v>0.04353158141289994</v>
       </c>
       <c r="O5" t="n">
-        <v>4.3310480335764</v>
+        <v>4.331048041470329</v>
       </c>
       <c r="P5" t="n">
-        <v>4.410210185213942</v>
+        <v>4.410210187905775</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9972489848169036</v>
+        <v>0.997248987162516</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003104446883283346</v>
+        <v>0.003104445559866058</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -1011,38 +1011,38 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>0.9944887057469326</v>
+        <v>0.9944887130289525</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.005317340013197305</v>
+        <v>0.005317336501845178</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>0.9999540343022505</v>
+        <v>0.9999540182586588</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.178034729557198e-05</v>
+        <v>4.178763804046472e-05</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>0.9974327082621375</v>
+        <v>0.9974327076645415</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.002355330690529882</v>
+        <v>0.002355330962411819</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>0.9903471913824016</v>
+        <v>0.9903471938849905</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.00326663257940252</v>
+        <v>0.003266632156637755</v>
       </c>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>0.9778428152075118</v>
+        <v>0.9778428120058936</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0006940334913633781</v>
+        <v>0.0006940335428087446</v>
       </c>
       <c r="AN5" t="inlineStr"/>
     </row>
@@ -1069,43 +1069,43 @@
         <v>77.65625</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3890909284533883</v>
+        <v>0.3890909284112034</v>
       </c>
       <c r="G6" t="n">
         <v>0.0408802018459966</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3036991224550851</v>
+        <v>0.3036991225960292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2478250703308909</v>
+        <v>0.2478250702399798</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01850467691463906</v>
+        <v>0.01850467690679097</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5529797707778151</v>
+        <v>0.5529797710670845</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5586029469598892</v>
+        <v>0.5586029472738887</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3222223782457707</v>
+        <v>0.3222223832830547</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07547153673851013</v>
+        <v>0.07547153677898635</v>
       </c>
       <c r="O6" t="n">
-        <v>4.386431974980576</v>
+        <v>4.386431977135151</v>
       </c>
       <c r="P6" t="n">
-        <v>4.428309714956633</v>
+        <v>4.428309717294939</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9802776578016524</v>
+        <v>0.9802776559615053</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008489646803062814</v>
+        <v>0.008489647198551387</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -1115,38 +1115,38 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>0.9747679560460246</v>
+        <v>0.9747679471769917</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009162615230539909</v>
+        <v>0.009162616837946176</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>0.9999912811409317</v>
+        <v>0.9999912816349914</v>
       </c>
       <c r="AD6" t="n">
-        <v>7.886450777379478e-06</v>
+        <v>7.886227328849374e-06</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
-        <v>0.9839624732715443</v>
+        <v>0.9839624730482868</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.005194122491021331</v>
+        <v>0.005194122532070962</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>0.7876673446288028</v>
+        <v>0.7876673429215924</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01497005299893108</v>
+        <v>0.0149700530506273</v>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
-        <v>0.7639236147119302</v>
+        <v>0.7639236320881846</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001144927372073617</v>
+        <v>0.001144927332439893</v>
       </c>
       <c r="AN6" t="inlineStr"/>
     </row>
@@ -1173,43 +1173,43 @@
         <v>66.19718309859155</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4886958146778536</v>
+        <v>0.4886958146760266</v>
       </c>
       <c r="G7" t="n">
         <v>0.04795677136102667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2566075839924613</v>
+        <v>0.2566075840123206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1893475641758934</v>
+        <v>0.1893475641544703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01739226579276497</v>
+        <v>0.01739226579615577</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5559179333411531</v>
+        <v>0.5559179311700849</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5558627807473355</v>
+        <v>0.5558627826002295</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5709597665635073</v>
+        <v>0.5709593662952288</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1535577457270393</v>
+        <v>0.1535576077473842</v>
       </c>
       <c r="O7" t="n">
-        <v>4.408315197949928</v>
+        <v>4.408315181780848</v>
       </c>
       <c r="P7" t="n">
-        <v>4.407904079674585</v>
+        <v>4.40790409347598</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9723637397464224</v>
+        <v>0.9723638432019049</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01010067768112661</v>
+        <v>0.01010065877540157</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -1219,38 +1219,38 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>0.9402764797245806</v>
+        <v>0.9402767619699109</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01854189574058069</v>
+        <v>0.01854185192709032</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>0.9999993816223586</v>
+        <v>0.999999380674235</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.392609260420041e-06</v>
+        <v>3.395209112678491e-06</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="n">
-        <v>0.933763054346792</v>
+        <v>0.9337630455458668</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.01025995565312062</v>
+        <v>0.01025995633757883</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>0.9749701057516975</v>
+        <v>0.9749703711333617</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.004166132057610829</v>
+        <v>0.004166109970271364</v>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
-        <v>0.6524941662225709</v>
+        <v>0.6524937194506388</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.003112121446456149</v>
+        <v>0.003112123446875657</v>
       </c>
       <c r="AN7" t="inlineStr"/>
     </row>
@@ -1277,43 +1277,43 @@
         <v>66.66666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3735503885622976</v>
+        <v>0.3735503886646729</v>
       </c>
       <c r="G8" t="n">
         <v>0.04761904761904761</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3017797553926043</v>
+        <v>0.3017797550644881</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2489905948482005</v>
+        <v>0.2489905949934041</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02806021357785015</v>
+        <v>0.02806021365838738</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5696724953710857</v>
+        <v>0.5696724962253498</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5582304145031345</v>
+        <v>0.5582304146831525</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5656129037576733</v>
+        <v>0.5656128990819769</v>
       </c>
       <c r="N8" t="n">
-        <v>0.123469185332697</v>
+        <v>0.1234691903029068</v>
       </c>
       <c r="O8" t="n">
-        <v>4.510727168591731</v>
+        <v>4.510727174950752</v>
       </c>
       <c r="P8" t="n">
-        <v>4.42553379663859</v>
+        <v>4.42553379797898</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9912273778190596</v>
+        <v>0.9912273751636429</v>
       </c>
       <c r="R8" t="n">
-        <v>0.005045829682511346</v>
+        <v>0.005045830445555134</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -1323,38 +1323,38 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>0.9879209337806626</v>
+        <v>0.9879209264559969</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.007333686055246319</v>
+        <v>0.007333688281434303</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>0.9999499565778071</v>
+        <v>0.9999499581142124</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.643341202094378e-05</v>
+        <v>4.643269922909492e-05</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
-        <v>0.9842187517718755</v>
+        <v>0.9842187509684986</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.00622055601322734</v>
+        <v>0.006220556162368995</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>0.9857714815979933</v>
+        <v>0.9857714806850832</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.005050819101523772</v>
+        <v>0.005050819267430024</v>
       </c>
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>0.9381952946474335</v>
+        <v>0.9381953104748361</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0009081341428959874</v>
+        <v>0.0009081340302936232</v>
       </c>
       <c r="AN8" t="inlineStr"/>
     </row>
@@ -1381,43 +1381,43 @@
         <v>69.85074626865672</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4184346509008527</v>
+        <v>0.4184346509642805</v>
       </c>
       <c r="G9" t="n">
         <v>0.0454483787817121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2664295170187482</v>
+        <v>0.2664295168783421</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2311091971008347</v>
+        <v>0.2311091971723147</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03857825619785213</v>
+        <v>0.03857825620335059</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5453351465816443</v>
+        <v>0.5453351445704828</v>
       </c>
       <c r="L9" t="n">
-        <v>0.556554213922496</v>
+        <v>0.556554214392348</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4828014850071219</v>
+        <v>0.4828015347804492</v>
       </c>
       <c r="N9" t="n">
-        <v>0.09699572675597476</v>
+        <v>0.09699574348497687</v>
       </c>
       <c r="O9" t="n">
-        <v>4.329484052021317</v>
+        <v>4.329484037037172</v>
       </c>
       <c r="P9" t="n">
-        <v>4.413051445738119</v>
+        <v>4.413051449236411</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.995969469611047</v>
+        <v>0.9959694679327736</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003433545180892337</v>
+        <v>0.003433545895857898</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -1427,38 +1427,38 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>0.9939044813677833</v>
+        <v>0.9939044759698787</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.005635335178453466</v>
+        <v>0.005635337674605239</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>0.9999854215510335</v>
+        <v>0.9999854217362116</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.186671038014954e-05</v>
+        <v>2.186657150226392e-05</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="n">
-        <v>0.9996751176891397</v>
+        <v>0.999675117453126</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.000729341718533743</v>
+        <v>0.0007293419830441178</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>0.9842085349449278</v>
+        <v>0.9842085388220352</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.004741469022100936</v>
+        <v>0.004741468441360786</v>
       </c>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>0.9932051596523748</v>
+        <v>0.9932051623035093</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0004956099315675032</v>
+        <v>0.0004956098348329761</v>
       </c>
       <c r="AN9" t="inlineStr"/>
     </row>
@@ -1485,43 +1485,43 @@
         <v>52.61363636363636</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5306916825504616</v>
+        <v>0.5306916826579526</v>
       </c>
       <c r="G10" t="n">
         <v>0.0603380301004491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2597511503162143</v>
+        <v>0.2597511501438604</v>
       </c>
       <c r="I10" t="n">
-        <v>0.115376694226804</v>
+        <v>0.1153766942703101</v>
       </c>
       <c r="J10" t="n">
-        <v>0.033842442806071</v>
+        <v>0.03384244282742767</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5415086286978176</v>
+        <v>0.5415086242441041</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5458309682770885</v>
+        <v>0.5458309681582216</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3986701795954545</v>
+        <v>0.3986693308833529</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05992434306972079</v>
+        <v>0.05992408086412205</v>
       </c>
       <c r="O10" t="n">
-        <v>4.300972493242484</v>
+        <v>4.300972460055188</v>
       </c>
       <c r="P10" t="n">
-        <v>4.333177849306642</v>
+        <v>4.333177848421946</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9854271349723449</v>
+        <v>0.9854271516410955</v>
       </c>
       <c r="R10" t="n">
-        <v>0.00766836505128327</v>
+        <v>0.007668360666224821</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1531,38 +1531,38 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>0.9823762407769263</v>
+        <v>0.9823762825534307</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01174249440687682</v>
+        <v>0.01174248049258632</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0.9999433595113485</v>
+        <v>0.999943337996626</v>
       </c>
       <c r="AD10" t="n">
-        <v>6.290533449707162e-05</v>
+        <v>6.291728056556956e-05</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
-        <v>0.9257446684795817</v>
+        <v>0.9257446563147202</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.01114224498330956</v>
+        <v>0.01114224588484107</v>
       </c>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>0.9679127369888821</v>
+        <v>0.9679127758320558</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.002834103281497369</v>
+        <v>0.002834101569392761</v>
       </c>
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
-        <v>0.8842271591027899</v>
+        <v>0.8842271181255406</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.002085008629297619</v>
+        <v>0.002085008999651352</v>
       </c>
       <c r="AN10" t="inlineStr"/>
     </row>
@@ -1589,43 +1589,43 @@
         <v>61.69014084507042</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6976459379986636</v>
+        <v>0.6976459379735106</v>
       </c>
       <c r="G11" t="n">
         <v>0.05146046241936653</v>
       </c>
       <c r="H11" t="n">
-        <v>0.128689928922737</v>
+        <v>0.1286899289623047</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09261029160041566</v>
+        <v>0.09261029157801856</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02959337905881725</v>
+        <v>0.02959337906679948</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5232073771356348</v>
+        <v>0.5232073761328682</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5438853471604912</v>
+        <v>0.5438853478683552</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5083450037344445</v>
+        <v>0.5083450846411486</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1033850603426523</v>
+        <v>0.1033850884406853</v>
       </c>
       <c r="O11" t="n">
-        <v>4.164548646870926</v>
+        <v>4.164548639393129</v>
       </c>
       <c r="P11" t="n">
-        <v>4.318675838034389</v>
+        <v>4.318675843307981</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9732819856645946</v>
+        <v>0.9732819999437231</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01216028186135488</v>
+        <v>0.0121602786114371</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
@@ -1635,38 +1635,38 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>0.957795624283472</v>
+        <v>0.9577956482339773</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.02568557427021327</v>
+        <v>0.02568556697974183</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>0.9999970036279392</v>
+        <v>0.9999970036839783</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.219255070018111e-05</v>
+        <v>1.219243668525542e-05</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="n">
-        <v>0.9509628516722497</v>
+        <v>0.9509628482739071</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.003925377814322443</v>
+        <v>0.003925377953367668</v>
       </c>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>0.8869736977496876</v>
+        <v>0.8869736625577558</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.003777833654889559</v>
+        <v>0.003777834239402491</v>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
-        <v>0.9642268614891987</v>
+        <v>0.9642268524732052</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.000801257522120928</v>
+        <v>0.0008012576227092733</v>
       </c>
       <c r="AN11" t="inlineStr"/>
     </row>
@@ -1693,43 +1693,43 @@
         <v>1182.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6580079528637066</v>
+        <v>0.658007952809377</v>
       </c>
       <c r="G12" t="n">
         <v>0.002684653847444545</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3185832282923884</v>
+        <v>0.3185832283714021</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0207241649964606</v>
+        <v>0.02072416497177636</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4987727432373008</v>
+        <v>0.4987727401542309</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5383950290610813</v>
+        <v>0.5383950271070885</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7487064795573467</v>
+        <v>0.7487062799563868</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3185967204065523</v>
+        <v>0.3185965870276693</v>
       </c>
       <c r="O12" t="n">
-        <v>3.982237472851483</v>
+        <v>3.982237449835301</v>
       </c>
       <c r="P12" t="n">
-        <v>4.277758912669679</v>
+        <v>4.277758898097615</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.947437558166937</v>
+        <v>0.9474376259860798</v>
       </c>
       <c r="R12" t="n">
-        <v>0.02495169623840094</v>
+        <v>0.02495168014193404</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
@@ -1739,38 +1739,38 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>0.7052580634734094</v>
+        <v>0.7052584277138321</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.05366558510878599</v>
+        <v>0.05366555194985159</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>0.9999879060034488</v>
+        <v>0.9999879082591087</v>
       </c>
       <c r="AD12" t="n">
-        <v>8.166876649055178e-06</v>
+        <v>8.166115008565789e-06</v>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="n">
-        <v>0.9833717895763443</v>
+        <v>0.9833719252687614</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.004876029252967263</v>
+        <v>0.004876009358303346</v>
       </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>0.9158445769773014</v>
+        <v>0.9158443242517715</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.001260363860230257</v>
+        <v>0.001260365758103294</v>
       </c>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
-        <v>0.9884096156565162</v>
+        <v>0.9884097036550118</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0002177833934109597</v>
+        <v>0.0002177825662481627</v>
       </c>
       <c r="AN12" t="inlineStr"/>
     </row>
@@ -1797,43 +1797,43 @@
         <v>37.30769230769231</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3764292995365501</v>
+        <v>0.3764292995885038</v>
       </c>
       <c r="G13" t="n">
         <v>0.08509245622647683</v>
       </c>
       <c r="H13" t="n">
-        <v>0.20530781079537</v>
+        <v>0.2053078106416003</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2773838130683605</v>
+        <v>0.2773838131849478</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05578662037324268</v>
+        <v>0.0557866203584713</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5485841142950727</v>
+        <v>0.5485841172716791</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5653524252994078</v>
+        <v>0.5653524257977128</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4766883541347894</v>
+        <v>0.476688399670569</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1744981835547542</v>
+        <v>0.1744982265446134</v>
       </c>
       <c r="O13" t="n">
-        <v>4.353688955519708</v>
+        <v>4.353688977694136</v>
       </c>
       <c r="P13" t="n">
-        <v>4.478562639926059</v>
+        <v>4.478562643637238</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9959027740660206</v>
+        <v>0.9959027738819872</v>
       </c>
       <c r="R13" t="n">
-        <v>0.00366300644198031</v>
+        <v>0.003663006526103782</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
@@ -1843,38 +1843,38 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>0.2511616036557029</v>
+        <v>0.2511615406114125</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.006822677036309507</v>
+        <v>0.006822677286926848</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>0.9296560921948005</v>
+        <v>0.9296563603688166</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0002031160696128928</v>
+        <v>0.0002031156824400321</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="n">
-        <v>0.6914577501947159</v>
+        <v>0.6914577526212038</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.003972090851091277</v>
+        <v>0.003972090822050012</v>
       </c>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
-        <v>0.9993451484223673</v>
+        <v>0.9993451485154167</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.001033844723912316</v>
+        <v>0.001033844653118174</v>
       </c>
       <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
-        <v>0.9645555570890871</v>
+        <v>0.9645555550037814</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.001910906132687272</v>
+        <v>0.001910906183986788</v>
       </c>
       <c r="AN13" t="inlineStr"/>
     </row>
@@ -1901,43 +1901,43 @@
         <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4685666630154797</v>
+        <v>0.4685666629631464</v>
       </c>
       <c r="G14" t="n">
         <v>0.07215007215007214</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2791093997172449</v>
+        <v>0.2791093997308827</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1713546933726054</v>
+        <v>0.1713546934252931</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008819171744597891</v>
+        <v>0.008819171730605837</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5536207568821497</v>
+        <v>0.5536207624284061</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5572253833098649</v>
+        <v>0.5572253843877273</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9005092186999272</v>
+        <v>0.900509202619883</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8346438116004949</v>
+        <v>0.8346437986895111</v>
       </c>
       <c r="O14" t="n">
-        <v>4.39120619674625</v>
+        <v>4.391206238055635</v>
       </c>
       <c r="P14" t="n">
-        <v>4.418051540750579</v>
+        <v>4.418051548778996</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9758866962106585</v>
+        <v>0.975886719568404</v>
       </c>
       <c r="R14" t="n">
-        <v>0.009247482748847456</v>
+        <v>0.009247478268539817</v>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
@@ -1947,38 +1947,38 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>0.8962303159519627</v>
+        <v>0.8962304824333043</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01601653880184001</v>
+        <v>0.01601652594982509</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
-        <v>0.9614806109789515</v>
+        <v>0.9614806109789699</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0009625122855063774</v>
+        <v>0.0009625122855061491</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="n">
-        <v>0.9849845292746786</v>
+        <v>0.984984541585973</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.005295882955898474</v>
+        <v>0.005295880782968431</v>
       </c>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
-        <v>0.725763918075617</v>
+        <v>0.7257638803368389</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.01183359057656408</v>
+        <v>0.01183359142691135</v>
       </c>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
-        <v>0.4757257212978004</v>
+        <v>0.4757256496697012</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.001429509931492915</v>
+        <v>0.001429510023723444</v>
       </c>
       <c r="AN14" t="inlineStr"/>
     </row>
@@ -2005,43 +2005,43 @@
         <v>37.66666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4676168791864762</v>
+        <v>0.467616879374457</v>
       </c>
       <c r="G15" t="n">
         <v>0.08428150021070376</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2808036479653256</v>
+        <v>0.280803647842334</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1470517109277883</v>
+        <v>0.1470517108760386</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02024626170970604</v>
+        <v>0.02024626169646662</v>
       </c>
       <c r="K15" t="n">
-        <v>0.512220023929174</v>
+        <v>0.5122201226601502</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5472466657528773</v>
+        <v>0.5472466647555404</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2054544340532677</v>
+        <v>0.2054535590989125</v>
       </c>
       <c r="N15" t="n">
-        <v>0.02732880500144134</v>
+        <v>0.0273285829940129</v>
       </c>
       <c r="O15" t="n">
-        <v>4.082594718855475</v>
+        <v>4.082595455460667</v>
       </c>
       <c r="P15" t="n">
-        <v>4.343708182579936</v>
+        <v>4.343708175211913</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.9796688837151163</v>
+        <v>0.9796688857763722</v>
       </c>
       <c r="R15" t="n">
-        <v>0.007535364136179344</v>
+        <v>0.007535363752040688</v>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
@@ -2051,38 +2051,38 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>0.9488242111984214</v>
+        <v>0.9488242268979464</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.01113928888121617</v>
+        <v>0.01113928720738072</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>-1.700885672526133</v>
+        <v>-1.700884998320291</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.00430044094977637</v>
+        <v>0.004300440413029735</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="n">
-        <v>0.9243393103573231</v>
+        <v>0.9243393071797614</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.01007206922145105</v>
+        <v>0.01007206939944675</v>
       </c>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="n">
-        <v>0.8326849008110861</v>
+        <v>0.8326848130514461</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.004577903203204117</v>
+        <v>0.004577904438395841</v>
       </c>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
-        <v>0.9999999465617552</v>
+        <v>0.9999999470086192</v>
       </c>
       <c r="AM15" t="n">
-        <v>8.554318119230041e-07</v>
+        <v>8.518476381268013e-07</v>
       </c>
       <c r="AN15" t="inlineStr"/>
     </row>
@@ -2109,25 +2109,25 @@
         <v>21.39130434782609</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3751087963773801</v>
+        <v>0.3751087964018581</v>
       </c>
       <c r="G16" t="n">
         <v>0.1484062459672215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06809149804835848</v>
+        <v>0.06809149804106746</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3926949046640935</v>
+        <v>0.3926949046425352</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01569855494294647</v>
+        <v>0.01569855494731771</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5547407510209782</v>
+        <v>0.5547407800811401</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5733753977865961</v>
+        <v>0.5733754846439694</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2136,16 +2136,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.399547914881412</v>
+        <v>4.399548131317051</v>
       </c>
       <c r="P16" t="n">
-        <v>4.53828267416197</v>
+        <v>4.538283320590577</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9757558264078261</v>
+        <v>0.9757558261462026</v>
       </c>
       <c r="R16" t="n">
-        <v>0.009470351170750822</v>
+        <v>0.009470351221831196</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
@@ -2155,31 +2155,31 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>0.9946929737023286</v>
+        <v>0.9946929732411659</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.005370193034839947</v>
+        <v>0.005370193267869897</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>0.9590837394407519</v>
+        <v>0.9590837381243648</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.004169089230149025</v>
+        <v>0.004169089297214486</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="n">
-        <v>0.909418027163619</v>
+        <v>0.9094180286826921</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.003613765977076533</v>
+        <v>0.00361376594888901</v>
       </c>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="n">
-        <v>0.8395852168630731</v>
+        <v>0.8395852161931516</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.01814845648655414</v>
+        <v>0.01814845652331161</v>
       </c>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="inlineStr"/>
@@ -2211,43 +2211,43 @@
         <v>51.25</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4780640258980272</v>
+        <v>0.478064025668827</v>
       </c>
       <c r="G17" t="n">
         <v>0.06194347657762291</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2550441184335309</v>
+        <v>0.2550441188812936</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1330574186338084</v>
+        <v>0.1330574185135598</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07189096045701066</v>
+        <v>0.07189096035869673</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5024881191354954</v>
+        <v>0.5024881234082471</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5288586751569063</v>
+        <v>0.5288586742179018</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4340558664594968</v>
+        <v>0.4340559422249156</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1543382506437194</v>
+        <v>0.1543383139697778</v>
       </c>
       <c r="O17" t="n">
-        <v>4.009971608901167</v>
+        <v>4.009971640793164</v>
       </c>
       <c r="P17" t="n">
-        <v>4.20666188061859</v>
+        <v>4.206661873624398</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9881534027509168</v>
+        <v>0.9881534073866074</v>
       </c>
       <c r="R17" t="n">
-        <v>0.005052354965176604</v>
+        <v>0.005052353976040599</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
@@ -2257,38 +2257,38 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>0.9717219102085268</v>
+        <v>0.9717219337850957</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.008459746560558453</v>
+        <v>0.008459743028688745</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>0.6387246672313837</v>
+        <v>0.6387247003099141</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.001858941428806582</v>
+        <v>0.001858941343703827</v>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="n">
-        <v>0.992996618002341</v>
+        <v>0.992996608970268</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.002263234891360768</v>
+        <v>0.002263236355651629</v>
       </c>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="n">
-        <v>-0.7835307476540299</v>
+        <v>-0.7835309069184482</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.006872648732564511</v>
+        <v>0.006872648977071946</v>
       </c>
       <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
-        <v>0.9972964487803031</v>
+        <v>0.9972964475920096</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0005029369656487576</v>
+        <v>0.0005029370752844756</v>
       </c>
       <c r="AN17" t="inlineStr"/>
     </row>
@@ -2315,43 +2315,43 @@
         <v>31.46666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4515185462382498</v>
+        <v>0.451518546451847</v>
       </c>
       <c r="G18" t="n">
         <v>0.1008878127522195</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2508910324934933</v>
+        <v>0.2508910318037907</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1666097192940944</v>
+        <v>0.1666097196951048</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03009288922194302</v>
+        <v>0.03009288929703804</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5490011313733419</v>
+        <v>0.5490011262433148</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5506707167572154</v>
+        <v>0.5506707170759214</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2144891651553351</v>
+        <v>0.2144899356381871</v>
       </c>
       <c r="N18" t="n">
-        <v>0.03642154007914782</v>
+        <v>0.03642181600609797</v>
       </c>
       <c r="O18" t="n">
-        <v>4.356795527549973</v>
+        <v>4.356795489334097</v>
       </c>
       <c r="P18" t="n">
-        <v>4.369232563220775</v>
+        <v>4.369232565594396</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9844596409725355</v>
+        <v>0.9844596372485284</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006447169778601816</v>
+        <v>0.006447170550429618</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
@@ -2361,38 +2361,38 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>0.925781813178142</v>
+        <v>0.9257817936504679</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.01399032159579558</v>
+        <v>0.01399032345493568</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
-        <v>0.8262208064774124</v>
+        <v>0.8262211446500043</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.001148172259881364</v>
+        <v>0.001148171142714889</v>
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="n">
-        <v>0.9973241852381616</v>
+        <v>0.9973241855526884</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.001552599418118485</v>
+        <v>0.001552599317711766</v>
       </c>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="n">
-        <v>0.9707421190050074</v>
+        <v>0.9707421170755998</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.00287760563031676</v>
+        <v>0.002877605741726046</v>
       </c>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>0.993566815617775</v>
+        <v>0.9935668172933028</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.0003023470880712413</v>
+        <v>0.0003023470502159269</v>
       </c>
       <c r="AN18" t="inlineStr"/>
     </row>
@@ -2419,25 +2419,25 @@
         <v>77.71428571428571</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2928786705374068</v>
+        <v>0.2928786705098768</v>
       </c>
       <c r="G19" t="n">
         <v>0.04084967320261438</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2980196009674419</v>
+        <v>0.2980196010147655</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3557027147401188</v>
+        <v>0.3557027147337084</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01254934055241822</v>
+        <v>0.01254934053903507</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4773251588100098</v>
+        <v>0.4773257066590098</v>
       </c>
       <c r="L19" t="n">
-        <v>0.557407236502968</v>
+        <v>0.5574072214185882</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2446,16 +2446,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.82203959903637</v>
+        <v>3.822043693296584</v>
       </c>
       <c r="P19" t="n">
-        <v>4.419352345783507</v>
+        <v>4.419352233934877</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.9870541844013571</v>
+        <v>0.9870541811707304</v>
       </c>
       <c r="R19" t="n">
-        <v>0.008016574953401417</v>
+        <v>0.008016575953874725</v>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
@@ -2465,38 +2465,38 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>0.684894949120765</v>
+        <v>0.6848949645415789</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.008358221540882463</v>
+        <v>0.008358221321937722</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>0.0339622334556906</v>
+        <v>0.03396238556178333</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.002928222768507439</v>
+        <v>0.00292822253797787</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="n">
-        <v>0.7305985674293305</v>
+        <v>0.7305985229476777</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.01464972211562931</v>
+        <v>0.01464972334201329</v>
       </c>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="n">
-        <v>0.7876202587310586</v>
+        <v>0.7876198884693261</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.005316785888196324</v>
+        <v>0.005316790522620117</v>
       </c>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
-        <v>0.9987782105249791</v>
+        <v>0.9987782104165641</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.000102194730566972</v>
+        <v>0.0001021947349149745</v>
       </c>
       <c r="AN19" t="inlineStr"/>
     </row>
@@ -2523,43 +2523,43 @@
         <v>55.77777777777778</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3719943274037391</v>
+        <v>0.3719943273800574</v>
       </c>
       <c r="G20" t="n">
         <v>0.05691519635742743</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2459185029100323</v>
+        <v>0.2459185030013721</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3196907365948976</v>
+        <v>0.3196907365258876</v>
       </c>
       <c r="J20" t="n">
-        <v>0.005481236733903614</v>
+        <v>0.005481236735255395</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5783758603000023</v>
+        <v>0.5783758520538617</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5737878378029928</v>
+        <v>0.5737878319806895</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4211378052355061</v>
+        <v>0.4211375660081009</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1374112956337796</v>
+        <v>0.1374110990094285</v>
       </c>
       <c r="O20" t="n">
-        <v>4.575504098150747</v>
+        <v>4.575504036785888</v>
       </c>
       <c r="P20" t="n">
-        <v>4.541358413194546</v>
+        <v>4.54135836986114</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9755804995114662</v>
+        <v>0.9755805029319908</v>
       </c>
       <c r="R20" t="n">
-        <v>0.009174408923704153</v>
+        <v>0.009174408281710626</v>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
@@ -2569,38 +2569,38 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>0.8647795136952487</v>
+        <v>0.8647794960030953</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.01071247217864532</v>
+        <v>0.01071247287271835</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
-        <v>0.6825498641508045</v>
+        <v>0.6825498939051582</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.003844558553258426</v>
+        <v>0.003844558373084685</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="n">
-        <v>0.9741405335941882</v>
+        <v>0.974140530930426</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.004291060609633838</v>
+        <v>0.004291060836602464</v>
       </c>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="n">
-        <v>0.7979500153190703</v>
+        <v>0.7979500706485327</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.01650676836801308</v>
+        <v>0.01650676611520463</v>
       </c>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>0.5253865720811438</v>
+        <v>0.5253865271023095</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.0006516147161024418</v>
+        <v>0.000651614747630272</v>
       </c>
       <c r="AN20" t="inlineStr"/>
     </row>
@@ -2627,25 +2627,25 @@
         <v>17.60714285714286</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3926349948370401</v>
+        <v>0.3926349942752794</v>
       </c>
       <c r="G21" t="n">
         <v>0.1803020058598151</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3377870452012128</v>
+        <v>0.3377870456849771</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08927595410193191</v>
+        <v>0.08927595417992841</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5.04831636563563e-18</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5119505968393867</v>
+        <v>0.5119505969026676</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5214040378706312</v>
+        <v>0.5214040378862334</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2654,16 +2654,16 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.080584583903153</v>
+        <v>4.080584584375281</v>
       </c>
       <c r="P21" t="n">
-        <v>4.151092398028675</v>
+        <v>4.15109239814509</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.9807245874358685</v>
+        <v>0.9807245874807303</v>
       </c>
       <c r="R21" t="n">
-        <v>0.009035299282911835</v>
+        <v>0.009035299271082077</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
@@ -2673,38 +2673,38 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>0.9293877291295994</v>
+        <v>0.9293877282785208</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.01043825431261878</v>
+        <v>0.01043825434415492</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>0.9960348199549983</v>
+        <v>0.9960348202929616</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.00207858561234625</v>
+        <v>0.002078585523764444</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="n">
-        <v>0.5037533632643423</v>
+        <v>0.5037533681207083</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.01542970426672279</v>
+        <v>0.015429704227928</v>
       </c>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="n">
-        <v>0.8043675129155022</v>
+        <v>0.8043675127348946</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.0075373420832216</v>
+        <v>0.007537342072434253</v>
       </c>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
-        <v>0.9830011533144901</v>
+        <v>0.9830011525208797</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.0001348887621392687</v>
+        <v>0.0001348887652203537</v>
       </c>
       <c r="AN21" t="inlineStr"/>
     </row>
@@ -2731,43 +2731,43 @@
         <v>29.3125</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4135808655857899</v>
+        <v>0.4135808655594087</v>
       </c>
       <c r="G22" t="n">
         <v>0.1083020272785731</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2033297621759581</v>
+        <v>0.203329762176548</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2477420255951969</v>
+        <v>0.247742025507402</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02704531936448205</v>
+        <v>0.02704531947806826</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5268307831677946</v>
+        <v>0.5268304488274074</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5502395706595578</v>
+        <v>0.5502394267022589</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2371734845628231</v>
+        <v>0.2371718369124033</v>
       </c>
       <c r="N22" t="n">
-        <v>0.06531715824998359</v>
+        <v>0.06531668735477097</v>
       </c>
       <c r="O22" t="n">
-        <v>4.191566915241262</v>
+        <v>4.191564422390334</v>
       </c>
       <c r="P22" t="n">
-        <v>4.366007210331949</v>
+        <v>4.366006137721229</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.981778520680347</v>
+        <v>0.9817785598877675</v>
       </c>
       <c r="R22" t="n">
-        <v>0.006823665825279303</v>
+        <v>0.006823658484480494</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
@@ -2777,38 +2777,38 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>0.892625612258153</v>
+        <v>0.8926260886305495</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.009660496913106801</v>
+        <v>0.009660475475622961</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
-        <v>0.9076380112991456</v>
+        <v>0.9076387557964798</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.001684482195522065</v>
+        <v>0.001684475406500688</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="n">
-        <v>0.3418877129747621</v>
+        <v>0.3418881362895494</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.01119711870660374</v>
+        <v>0.01119711512139951</v>
       </c>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="n">
-        <v>0.9604867993236423</v>
+        <v>0.9604867429356013</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.002846280209049821</v>
+        <v>0.002846282229519412</v>
       </c>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="n">
-        <v>0.8225078020850068</v>
+        <v>0.8225075280778347</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.001781184224621996</v>
+        <v>0.001781185611311563</v>
       </c>
       <c r="AN22" t="inlineStr"/>
     </row>
@@ -2835,43 +2835,43 @@
         <v>39.58333333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6238519511711706</v>
+        <v>0.6238519513177977</v>
       </c>
       <c r="G23" t="n">
         <v>0.08020050125313281</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2028318968739128</v>
+        <v>0.2028318965921395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06932561212208042</v>
+        <v>0.06932561224073039</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0237900385797033</v>
+        <v>0.02379003859619956</v>
       </c>
       <c r="K23" t="n">
-        <v>0.484531289021057</v>
+        <v>0.4845312822572839</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5341169703775777</v>
+        <v>0.5341169708622687</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3059299700505546</v>
+        <v>0.3059298119055867</v>
       </c>
       <c r="N23" t="n">
-        <v>0.100233206885056</v>
+        <v>0.1002330856209562</v>
       </c>
       <c r="O23" t="n">
-        <v>3.875883377277486</v>
+        <v>3.875883326748309</v>
       </c>
       <c r="P23" t="n">
-        <v>4.245845263686942</v>
+        <v>4.245845267294212</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.9807992217311796</v>
+        <v>0.9807992242192265</v>
       </c>
       <c r="R23" t="n">
-        <v>0.01037404124332526</v>
+        <v>0.01037404057097937</v>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -2881,38 +2881,38 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>0.8918270714684264</v>
+        <v>0.8918270860744716</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.02305751497639328</v>
+        <v>0.02305751344025227</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>-0.9802205738419052</v>
+        <v>-0.9802215615409089</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.001343821933000081</v>
+        <v>0.001343822268137347</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="n">
-        <v>0.9853473260644688</v>
+        <v>0.9853473262634698</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.002038821034385091</v>
+        <v>0.002038821010540471</v>
       </c>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="n">
-        <v>0.8569640178500566</v>
+        <v>0.856963916192805</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.0006140313026391147</v>
+        <v>0.0006140315282955807</v>
       </c>
       <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="n">
-        <v>0.9947026274492846</v>
+        <v>0.9947026270700142</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.0003390850424057322</v>
+        <v>0.0003390850558665835</v>
       </c>
       <c r="AN23" t="inlineStr"/>
     </row>
@@ -2939,25 +2939,25 @@
         <v>18.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5366376492551596</v>
+        <v>0.5366376495537714</v>
       </c>
       <c r="G24" t="n">
         <v>0.1688618709895305</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1622397270835717</v>
+        <v>0.1622397269217724</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1157024432834648</v>
+        <v>0.1157024431484001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01655830938827357</v>
+        <v>0.01655830938652574</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5381273422429782</v>
+        <v>0.5381273409542512</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5469554563350643</v>
+        <v>0.5469554552120094</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2966,16 +2966,16 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.275774819085798</v>
+        <v>4.275774809481438</v>
       </c>
       <c r="P24" t="n">
-        <v>4.341554147160157</v>
+        <v>4.341554138793168</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.9926953288581162</v>
+        <v>0.9926953287131751</v>
       </c>
       <c r="R24" t="n">
-        <v>0.005075595189499516</v>
+        <v>0.005075595246891651</v>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
@@ -2985,31 +2985,31 @@
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>0.9989979145197011</v>
+        <v>0.9989979145292962</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.002540241183442363</v>
+        <v>0.002540241171715482</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>0.9608443827013903</v>
+        <v>0.9608443828761388</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.003124251098636244</v>
+        <v>0.003124251091664596</v>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="n">
-        <v>0.8446192709595116</v>
+        <v>0.8446192682941442</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.009714199361370081</v>
+        <v>0.009714199503360223</v>
       </c>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="n">
-        <v>0.9769001235953902</v>
+        <v>0.9769001262985881</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.001026863601820317</v>
+        <v>0.001026863538079088</v>
       </c>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
@@ -3041,25 +3041,25 @@
         <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3559522748638808</v>
+        <v>0.3559522750970078</v>
       </c>
       <c r="G25" t="n">
         <v>0.04668534080298786</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2688668009066632</v>
+        <v>0.2688668010518658</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2729559277122325</v>
+        <v>0.2729559273787527</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05553965571423582</v>
+        <v>0.05553965566938588</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5494012369207484</v>
+        <v>0.5494012367047949</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5531651098141975</v>
+        <v>0.5531651096136052</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3068,65 +3068,65 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.359776070804065</v>
+        <v>4.359776069195355</v>
       </c>
       <c r="P25" t="n">
-        <v>4.387811859846882</v>
+        <v>4.387811858352807</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.9827869502360601</v>
+        <v>0.9827869502327035</v>
       </c>
       <c r="R25" t="n">
-        <v>0.02175869289332351</v>
+        <v>0.02175869289595122</v>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
-        <v>-0.3143661111299618</v>
+        <v>-0.3143661115098733</v>
       </c>
       <c r="U25" t="n">
-        <v>0.04220960126964817</v>
+        <v>0.04220960127574842</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="n">
-        <v>0.2705704395949385</v>
+        <v>0.2705704401435304</v>
       </c>
       <c r="X25" t="n">
-        <v>0.001083696845556093</v>
+        <v>0.001083696845148578</v>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>0.9037293283445984</v>
+        <v>0.9037293282809171</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.01069635760359922</v>
+        <v>0.01069635760155928</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
-        <v>0.5155857894256859</v>
+        <v>0.5155857898015717</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.003410800249187533</v>
+        <v>0.003410800247864213</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="n">
-        <v>0.9999642980004979</v>
+        <v>0.9999642980079823</v>
       </c>
       <c r="AG25" t="n">
-        <v>9.787797672631068e-05</v>
+        <v>9.787796732242698e-05</v>
       </c>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="n">
-        <v>0.9912692940008837</v>
+        <v>0.9912692925383154</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.000583606673247077</v>
+        <v>0.000583606708414751</v>
       </c>
       <c r="AK25" t="inlineStr"/>
       <c r="AL25" t="n">
-        <v>-0.06019105087399779</v>
+        <v>-0.06019105215306464</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.003409599200541214</v>
+        <v>0.003409599174756292</v>
       </c>
       <c r="AN25" t="inlineStr"/>
     </row>
@@ -3153,25 +3153,25 @@
         <v>55</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4002539035826087</v>
+        <v>0.4002539033355717</v>
       </c>
       <c r="G26" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1994618786146296</v>
+        <v>0.199461878586617</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2900964126834302</v>
+        <v>0.2900964128573777</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05246774739927379</v>
+        <v>0.0524677475003759</v>
       </c>
       <c r="K26" t="n">
-        <v>0.540731726273736</v>
+        <v>0.5407317262128234</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5490181805573094</v>
+        <v>0.5490181805095745</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3180,65 +3180,65 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.295183238249074</v>
+        <v>4.295183237795165</v>
       </c>
       <c r="P26" t="n">
-        <v>4.35691974105193</v>
+        <v>4.356919740696322</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.9795222297738044</v>
+        <v>0.9795222298130901</v>
       </c>
       <c r="R26" t="n">
-        <v>0.02199523776444483</v>
+        <v>0.02199523774299785</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
-        <v>0.2503683661072617</v>
+        <v>0.2503683675309779</v>
       </c>
       <c r="U26" t="n">
-        <v>0.04251844761102798</v>
+        <v>0.04251844757065201</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
-        <v>-0.6471722246888199</v>
+        <v>-0.6471722266848419</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0008997036024602547</v>
+        <v>0.0008997036030053793</v>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>0.9509637374357274</v>
+        <v>0.9509637376174738</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.01195532135634414</v>
+        <v>0.01195532132646673</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>-0.4457842790344297</v>
+        <v>-0.4457842804035308</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.004122830932079933</v>
+        <v>0.004122830934032012</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="n">
-        <v>0.9173165762320066</v>
+        <v>0.9173165746315359</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.003848952943997378</v>
+        <v>0.003848952967535248</v>
       </c>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="n">
-        <v>0.9927408269512144</v>
+        <v>0.992740827486649</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.0007247754950350273</v>
+        <v>0.00072477547289676</v>
       </c>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="n">
-        <v>0.5346525047973455</v>
+        <v>0.5346525293350575</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.0009452755193291395</v>
+        <v>0.0009452754946355403</v>
       </c>
       <c r="AN26" t="inlineStr"/>
     </row>
@@ -3265,25 +3265,25 @@
         <v>67</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4605706049045288</v>
+        <v>0.4605706047574397</v>
       </c>
       <c r="G27" t="n">
         <v>0.04738213693437573</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2439684145997375</v>
+        <v>0.2439684149537734</v>
       </c>
       <c r="I27" t="n">
-        <v>0.174859558721163</v>
+        <v>0.1748595584867289</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07321928484019485</v>
+        <v>0.07321928486768225</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5300735358050577</v>
+        <v>0.5300735357526247</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5351292280837466</v>
+        <v>0.5351292280405441</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3292,65 +3292,65 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.215743336360242</v>
+        <v>4.215743335969353</v>
       </c>
       <c r="P27" t="n">
-        <v>4.253428619002744</v>
+        <v>4.25342861868073</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.9962122268506304</v>
+        <v>0.9962122268492332</v>
       </c>
       <c r="R27" t="n">
-        <v>0.009988956378272563</v>
+        <v>0.009988956380123724</v>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
-        <v>0.9032455835895219</v>
+        <v>0.9032455835943591</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0163288926400523</v>
+        <v>0.01632889263964412</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
-        <v>0.3403901770992426</v>
+        <v>0.3403901771675889</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0009101553906670243</v>
+        <v>0.0009101553906198709</v>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
-        <v>0.8956302996488192</v>
+        <v>0.8956302993721201</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.01369924677302828</v>
+        <v>0.01369924677752384</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>0.795753143896083</v>
+        <v>0.7957531434048898</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.001652632528219481</v>
+        <v>0.001652632530206689</v>
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="n">
-        <v>0.878561005675181</v>
+        <v>0.8785610063098785</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.009734872774329884</v>
+        <v>0.009734872780640608</v>
       </c>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="n">
-        <v>0.7015923908315007</v>
+        <v>0.7015923862825086</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.002943001475169708</v>
+        <v>0.002943001481190409</v>
       </c>
       <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="n">
-        <v>0.434080415220143</v>
+        <v>0.4340804140633849</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.004898268664987468</v>
+        <v>0.00489826867824539</v>
       </c>
       <c r="AN27" t="inlineStr"/>
     </row>
@@ -3377,43 +3377,43 @@
         <v>274.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7158795401171276</v>
+        <v>0.7158795401305122</v>
       </c>
       <c r="G28" t="n">
         <v>0.01156082729280107</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1423140067580003</v>
+        <v>0.1423140067686963</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1093709740016232</v>
+        <v>0.1093709739889803</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02087465183044777</v>
+        <v>0.02087465181901007</v>
       </c>
       <c r="K28" t="n">
-        <v>0.5203824890675836</v>
+        <v>0.5203824972436116</v>
       </c>
       <c r="L28" t="n">
-        <v>0.5468676968391812</v>
+        <v>0.546867700056754</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2358816670151607</v>
+        <v>0.235880591093669</v>
       </c>
       <c r="N28" t="n">
-        <v>0.04142854948115181</v>
+        <v>0.0414281644980241</v>
       </c>
       <c r="O28" t="n">
-        <v>4.143481723210112</v>
+        <v>4.143481784187457</v>
       </c>
       <c r="P28" t="n">
-        <v>4.340893939552014</v>
+        <v>4.340893963520034</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9515815760435493</v>
+        <v>0.9515815901034564</v>
       </c>
       <c r="R28" t="n">
-        <v>0.02291442583235275</v>
+        <v>0.02291442250496915</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
@@ -3425,38 +3425,38 @@
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>0.6722847004638964</v>
+        <v>0.6722848197723788</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.04690819476408412</v>
+        <v>0.04690818622878828</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>0.9522477831395815</v>
+        <v>0.9522477144758847</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.002613568048843253</v>
+        <v>0.002613569937689022</v>
       </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="n">
-        <v>0.5243685243442856</v>
+        <v>0.5243684731902135</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.01152871094829263</v>
+        <v>0.0115287115485102</v>
       </c>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="n">
-        <v>0.3925752358161078</v>
+        <v>0.3925751988397843</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.01693585956432243</v>
+        <v>0.0169358600707697</v>
       </c>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="n">
-        <v>0.9901335997416376</v>
+        <v>0.9901336079992792</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.0003438769191753161</v>
+        <v>0.0003438767754056901</v>
       </c>
       <c r="AN28" t="inlineStr"/>
     </row>
@@ -3483,25 +3483,25 @@
         <v>15.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5922072970736373</v>
+        <v>0.5922072966992186</v>
       </c>
       <c r="G29" t="n">
         <v>0.2102386208346473</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01553978349820245</v>
+        <v>0.01553978410683548</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1433667741521803</v>
+        <v>0.1433667739479109</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03864752444133265</v>
+        <v>0.03864752441138786</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5450393411938402</v>
+        <v>0.5450393413035584</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5378951225118166</v>
+        <v>0.5378951225425983</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3510,16 +3510,16 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.327280143443206</v>
+        <v>4.327280144260669</v>
       </c>
       <c r="P29" t="n">
-        <v>4.274042576065238</v>
+        <v>4.274042576294665</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9370092198966595</v>
+        <v>0.9370092203899122</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01619595499649923</v>
+        <v>0.01619595492353491</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
@@ -3531,38 +3531,38 @@
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>0.7199198589712297</v>
+        <v>0.719919860584556</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.03448679252226174</v>
+        <v>0.03448679238595346</v>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>0.9343812983619562</v>
+        <v>0.9343812992958096</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.008872642059008218</v>
+        <v>0.008872641992009715</v>
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="n">
-        <v>0.6184579859230938</v>
+        <v>0.6184579868308682</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.008730513457351945</v>
+        <v>0.008730513374497255</v>
       </c>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="n">
-        <v>0.9545880790724479</v>
+        <v>0.9545880793902278</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.005536965959767819</v>
+        <v>0.005536965929026571</v>
       </c>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="n">
-        <v>0.9388067148510899</v>
+        <v>0.9388067155314166</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.001476325829841406</v>
+        <v>0.001476325819546223</v>
       </c>
       <c r="AN29" t="inlineStr"/>
     </row>
@@ -3589,43 +3589,43 @@
         <v>45.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6915723419858851</v>
+        <v>0.6915723419696138</v>
       </c>
       <c r="G30" t="n">
         <v>0.06992518005733864</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07335276932576335</v>
+        <v>0.07335276911610503</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1459822594046087</v>
+        <v>0.1459822596625786</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0191674492264043</v>
+        <v>0.01916744919436398</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5803769440286095</v>
+        <v>0.5803769884098039</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5467235057226325</v>
+        <v>0.5467235005998814</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1656685183293913</v>
+        <v>0.1656689325846756</v>
       </c>
       <c r="N30" t="n">
-        <v>0.009265298389339413</v>
+        <v>0.009265331111876383</v>
       </c>
       <c r="O30" t="n">
-        <v>4.590394956480194</v>
+        <v>4.590395286727254</v>
       </c>
       <c r="P30" t="n">
-        <v>4.339807576284242</v>
+        <v>4.339807538076314</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9734941725865006</v>
+        <v>0.9734941520145561</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01341950732385387</v>
+        <v>0.01341951253128414</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
@@ -3637,38 +3637,38 @@
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>0.8671532172930863</v>
+        <v>0.8671530726851873</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.02482672711248347</v>
+        <v>0.02482674062435431</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>0.997541705724161</v>
+        <v>0.9975416291293397</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.0002234340345439503</v>
+        <v>0.0002234375205507549</v>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="n">
-        <v>0.01505622351020164</v>
+        <v>0.01505659793861391</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.01342141175353233</v>
+        <v>0.01342140926097131</v>
       </c>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="n">
-        <v>0.8736855960878586</v>
+        <v>0.8736854605419373</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.007438761718713984</v>
+        <v>0.007438765719801801</v>
       </c>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="n">
-        <v>0.5113721296791657</v>
+        <v>0.5113721845093215</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.001879968085850792</v>
+        <v>0.00187996796935288</v>
       </c>
       <c r="AN30" t="inlineStr"/>
     </row>
@@ -3695,25 +3695,25 @@
         <v>26.3</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5100618132893889</v>
+        <v>0.510061813306836</v>
       </c>
       <c r="G31" t="n">
         <v>0.1207073450419458</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08244690044211486</v>
+        <v>0.08244690045861332</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2664816652636977</v>
+        <v>0.2664816652601923</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02030227596285282</v>
+        <v>0.02030227593241257</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5411091241769229</v>
+        <v>0.5411091243856065</v>
       </c>
       <c r="L31" t="n">
-        <v>0.5556445995349577</v>
+        <v>0.5556445997103447</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.297995521688784</v>
+        <v>4.297995523243836</v>
       </c>
       <c r="P31" t="n">
-        <v>4.406273731714898</v>
+        <v>4.406273733021131</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9845846215736355</v>
+        <v>0.9845846207792551</v>
       </c>
       <c r="R31" t="n">
-        <v>0.008108372867425035</v>
+        <v>0.008108373078418126</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
@@ -3743,38 +3743,38 @@
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
-        <v>0.9403393012386818</v>
+        <v>0.9403392953662553</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.01304611971851409</v>
+        <v>0.01304612035435265</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>0.8908991023708824</v>
+        <v>0.8908991050495451</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.008041470559999596</v>
+        <v>0.008041470466006895</v>
       </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="n">
-        <v>-0.04007470500952648</v>
+        <v>-0.04007469953179266</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.00927314704035594</v>
+        <v>0.009273147068069237</v>
       </c>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="n">
-        <v>0.9703497265043083</v>
+        <v>0.9703497213672005</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.002701992476453797</v>
+        <v>0.00270199270119878</v>
       </c>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="n">
-        <v>0.05262509718589548</v>
+        <v>0.05262510335571136</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.004091009304045872</v>
+        <v>0.004091009294624781</v>
       </c>
       <c r="AN31" t="inlineStr"/>
     </row>
@@ -3801,25 +3801,25 @@
         <v>32.6</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6207177798737793</v>
+        <v>0.6207177798836309</v>
       </c>
       <c r="G32" t="n">
         <v>0.09738046547862497</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1026556514757471</v>
+        <v>0.102655651448909</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1515085776379964</v>
+        <v>0.1515085776593587</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02773752553385222</v>
+        <v>0.0277375255294765</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5785259936431176</v>
+        <v>0.5785259286975886</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5570048359248688</v>
+        <v>0.5570048517873958</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3828,16 +3828,16 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.576621334530718</v>
+        <v>4.576620851231514</v>
       </c>
       <c r="P32" t="n">
-        <v>4.416392399057208</v>
+        <v>4.416392517297742</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9813117562949464</v>
+        <v>0.9813117711006507</v>
       </c>
       <c r="R32" t="n">
-        <v>0.01316370649800837</v>
+        <v>0.01316370128386094</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
@@ -3849,38 +3849,38 @@
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>0.8830149249119658</v>
+        <v>0.8830160774891798</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.009754853694145426</v>
+        <v>0.009754805639069901</v>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>0.2196324728205126</v>
+        <v>0.2196327230667259</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.01753505445950276</v>
+        <v>0.01753505169578304</v>
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="n">
-        <v>-0.2312443221242326</v>
+        <v>-0.2312454990409245</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.01411120524233461</v>
+        <v>0.01411121202064484</v>
       </c>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="n">
-        <v>0.3378479862451139</v>
+        <v>0.337847701940807</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.01686047971490034</v>
+        <v>0.01686048333005009</v>
       </c>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="n">
-        <v>0.0827074752067728</v>
+        <v>0.0827074599527291</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.004868207156664338</v>
+        <v>0.004868207214364416</v>
       </c>
       <c r="AN32" t="inlineStr"/>
     </row>
@@ -3905,43 +3905,43 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>0.6421516036650835</v>
+        <v>0.642151603719554</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002523163010079717</v>
+        <v>0.002523163255140709</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2245698007084695</v>
+        <v>0.2245698005775707</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1058026140953321</v>
+        <v>0.1058026139657058</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02495281852103528</v>
+        <v>0.0249528184820288</v>
       </c>
       <c r="K33" t="n">
-        <v>0.5508868290868433</v>
+        <v>0.5508862626579282</v>
       </c>
       <c r="L33" t="n">
-        <v>0.5458029700241758</v>
+        <v>0.545802899750793</v>
       </c>
       <c r="M33" t="n">
-        <v>0.30045665397837</v>
+        <v>0.3004620558617649</v>
       </c>
       <c r="N33" t="n">
-        <v>0.01884087476792937</v>
+        <v>0.01884103640913854</v>
       </c>
       <c r="O33" t="n">
-        <v>4.370842435405677</v>
+        <v>4.370838216122932</v>
       </c>
       <c r="P33" t="n">
-        <v>4.332969072833048</v>
+        <v>4.332968549367762</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.9676863728354042</v>
+        <v>0.9676858613911634</v>
       </c>
       <c r="R33" t="n">
-        <v>0.005702873743655971</v>
+        <v>0.005702918874528184</v>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
@@ -3951,38 +3951,38 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
-        <v>0.9209140137953842</v>
+        <v>0.9209124481648904</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.01136391082119986</v>
+        <v>0.01136402330530227</v>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>0.5598075583597079</v>
+        <v>0.5598082576741732</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.004257771468192942</v>
+        <v>0.004257768062534983</v>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="n">
-        <v>0.9333973606963083</v>
+        <v>0.9333976511606614</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.003078316942466647</v>
+        <v>0.003078310226183776</v>
       </c>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="n">
-        <v>0.7698562698815211</v>
+        <v>0.7698526475791609</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.00227631204009091</v>
+        <v>0.002276329943967573</v>
       </c>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
-        <v>0.2950358869805424</v>
+        <v>0.2950296601526815</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.0008301361037336391</v>
+        <v>0.0008301397635470196</v>
       </c>
       <c r="AN33" t="inlineStr"/>
     </row>
@@ -4009,25 +4009,25 @@
         <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7519633395058384</v>
+        <v>0.7519633396250179</v>
       </c>
       <c r="G34" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H34" t="n">
-        <v>0.01478397129559729</v>
+        <v>0.0147839710365304</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1023682012617217</v>
+        <v>0.1023682013871307</v>
       </c>
       <c r="J34" t="n">
-        <v>0.008784365836720525</v>
+        <v>0.008784365851198749</v>
       </c>
       <c r="K34" t="n">
-        <v>0.536901696262555</v>
+        <v>0.5369016959858964</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5432389027487502</v>
+        <v>0.5432389027490659</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.266640352725299</v>
+        <v>4.266640350663374</v>
       </c>
       <c r="P34" t="n">
-        <v>4.313865019699602</v>
+        <v>4.313865019701939</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.9392370431768626</v>
+        <v>0.939237042117992</v>
       </c>
       <c r="R34" t="n">
-        <v>0.01718982928280536</v>
+        <v>0.01718982943601216</v>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
@@ -4057,38 +4057,38 @@
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>0.9025777770358581</v>
+        <v>0.9025777752172841</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.03736462267539677</v>
+        <v>0.03736462303170694</v>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
-        <v>0.9954666026972713</v>
+        <v>0.9954666035000507</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.001592709087179328</v>
+        <v>0.001592708948342082</v>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="n">
-        <v>0.7077091980568507</v>
+        <v>0.7077092020821509</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.004162081399060013</v>
+        <v>0.00416208139210575</v>
       </c>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="n">
-        <v>0.5015557242603633</v>
+        <v>0.5015557239555242</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.00783696143241468</v>
+        <v>0.007836961439294451</v>
       </c>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="n">
-        <v>0.2670092201505117</v>
+        <v>0.2670092148361114</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.0008322850727627393</v>
+        <v>0.0008322850673228221</v>
       </c>
       <c r="AN34" t="inlineStr"/>
     </row>
@@ -4115,25 +4115,25 @@
         <v>74.09999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.687523750659823</v>
+        <v>0.6875237506860816</v>
       </c>
       <c r="G35" t="n">
         <v>0.042842148105306</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2018749037744333</v>
+        <v>0.201874903841659</v>
       </c>
       <c r="I35" t="n">
-        <v>0.03464191229956181</v>
+        <v>0.03464191218332047</v>
       </c>
       <c r="J35" t="n">
-        <v>0.033117285160876</v>
+        <v>0.03311728518363292</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5002346248069625</v>
+        <v>0.5002346247082619</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5375970958928967</v>
+        <v>0.5375970959168979</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4142,16 +4142,16 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.9931505467131</v>
+        <v>3.993150545976317</v>
       </c>
       <c r="P35" t="n">
-        <v>4.271817773745477</v>
+        <v>4.271817773924242</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9962031555067061</v>
+        <v>0.9962031568892693</v>
       </c>
       <c r="R35" t="n">
-        <v>0.00613854420043662</v>
+        <v>0.006138543083140492</v>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>0.9758020481878399</v>
+        <v>0.9758020680506921</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.00848855460540931</v>
+        <v>0.00848855112217693</v>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -4173,24 +4173,24 @@
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="n">
-        <v>0.64945627498078</v>
+        <v>0.6494562724442927</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.008842089311811454</v>
+        <v>0.008842089348229592</v>
       </c>
       <c r="AH35" t="inlineStr"/>
       <c r="AI35" t="n">
-        <v>0.6948344030196475</v>
+        <v>0.6948343947747667</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.002232387366728052</v>
+        <v>0.002232387390152476</v>
       </c>
       <c r="AK35" t="inlineStr"/>
       <c r="AL35" t="n">
-        <v>0.5727487813570584</v>
+        <v>0.5727487740214252</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.002219386128153858</v>
+        <v>0.002219386148146078</v>
       </c>
       <c r="AN35" t="inlineStr"/>
     </row>
@@ -4217,25 +4217,25 @@
         <v>46.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6184344404805445</v>
+        <v>0.6184344404849657</v>
       </c>
       <c r="G36" t="n">
         <v>0.06871435442864013</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1345326977341799</v>
+        <v>0.1345326978111002</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1554100927459354</v>
+        <v>0.1554100926475006</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02290841461070009</v>
+        <v>0.0229084146277933</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5508842687946176</v>
+        <v>0.5508842674969333</v>
       </c>
       <c r="L36" t="n">
-        <v>0.5490979189898959</v>
+        <v>0.5490979182560349</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4244,16 +4244,16 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.370823363997192</v>
+        <v>4.370823354330846</v>
       </c>
       <c r="P36" t="n">
-        <v>4.357516428485859</v>
+        <v>4.357516423019093</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9839315696536894</v>
+        <v>0.9839315684529176</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01148646560125316</v>
+        <v>0.01148646602723091</v>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
@@ -4265,38 +4265,38 @@
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
-        <v>0.8166610429078107</v>
+        <v>0.816661020519712</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.01861310289764294</v>
+        <v>0.01861310403019409</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>0.3723614624476508</v>
+        <v>0.3723614460559656</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.008126943414296529</v>
+        <v>0.008126943626044976</v>
       </c>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="n">
-        <v>0.06702911052602845</v>
+        <v>0.06702911439401316</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.01347622341055103</v>
+        <v>0.01347622343537479</v>
       </c>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="n">
-        <v>0.7326810460920691</v>
+        <v>0.7326810391177341</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.00605705288442605</v>
+        <v>0.006057052976002668</v>
       </c>
       <c r="AK36" t="inlineStr"/>
       <c r="AL36" t="n">
-        <v>0.1524810339639457</v>
+        <v>0.1524810380024521</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.004071075789554511</v>
+        <v>0.004071075783492895</v>
       </c>
       <c r="AN36" t="inlineStr"/>
     </row>
@@ -4323,25 +4323,25 @@
         <v>55</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4310490712245829</v>
+        <v>0.4310490710111513</v>
       </c>
       <c r="G37" t="n">
         <v>0.05772005772005771</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3585099706610048</v>
+        <v>0.3585099709374001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1452580722152676</v>
+        <v>0.1452580721451264</v>
       </c>
       <c r="J37" t="n">
-        <v>0.007462828179086988</v>
+        <v>0.007462828186264588</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5416254005209055</v>
+        <v>0.5416253932753577</v>
       </c>
       <c r="L37" t="n">
-        <v>0.5505442080965769</v>
+        <v>0.5505442076041522</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4350,61 +4350,61 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4.301842628273871</v>
+        <v>4.301842574283188</v>
       </c>
       <c r="P37" t="n">
-        <v>4.368288287673698</v>
+        <v>4.368288284003592</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.9904183339057777</v>
+        <v>0.9904183400608575</v>
       </c>
       <c r="R37" t="n">
-        <v>0.006522427874597541</v>
+        <v>0.006522425777975614</v>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="n">
-        <v>-1.532500512853302</v>
+        <v>-1.532501830093369</v>
       </c>
       <c r="X37" t="n">
-        <v>0.0006808056502324749</v>
+        <v>0.0006808058272875947</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
-        <v>0.9759297077302049</v>
+        <v>0.9759297513464497</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.007365976870870116</v>
+        <v>0.007365970192693787</v>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>-0.7305957074055771</v>
+        <v>-0.7305957601726785</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.008329356008159492</v>
+        <v>0.008329356022493621</v>
       </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="n">
-        <v>0.9057722058075757</v>
+        <v>0.9057722490890664</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.009989438641628256</v>
+        <v>0.009989436364236678</v>
       </c>
       <c r="AH37" t="inlineStr"/>
       <c r="AI37" t="n">
-        <v>0.9607746496072406</v>
+        <v>0.9607746790144679</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.001776891613454449</v>
+        <v>0.001776890942890679</v>
       </c>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="n">
-        <v>0.9999955925352465</v>
+        <v>0.999995594932255</v>
       </c>
       <c r="AM37" t="n">
-        <v>2.066570228598871e-06</v>
+        <v>2.066008190402833e-06</v>
       </c>
       <c r="AN37" t="inlineStr"/>
     </row>
@@ -4431,25 +4431,25 @@
         <v>23</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4115513533477569</v>
+        <v>0.4115513534924096</v>
       </c>
       <c r="G38" t="n">
         <v>0.1380262249827467</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3184506857669814</v>
+        <v>0.318450685478181</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1287866383384099</v>
+        <v>0.1287866384976123</v>
       </c>
       <c r="J38" t="n">
-        <v>0.003185097564105027</v>
+        <v>0.003185097549050355</v>
       </c>
       <c r="K38" t="n">
-        <v>0.5410877791334675</v>
+        <v>0.5410877784062029</v>
       </c>
       <c r="L38" t="n">
-        <v>0.5459534785704414</v>
+        <v>0.5459534769004961</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4458,61 +4458,61 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4.297836464385832</v>
+        <v>4.297836458966457</v>
       </c>
       <c r="P38" t="n">
-        <v>4.334089179456488</v>
+        <v>4.334089167015388</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9430380972433829</v>
+        <v>0.9430380885096223</v>
       </c>
       <c r="R38" t="n">
-        <v>0.0133919071904237</v>
+        <v>0.01339190820614503</v>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
-        <v>0.2639470867320597</v>
+        <v>0.2639473950996036</v>
       </c>
       <c r="X38" t="n">
-        <v>0.001124531513097592</v>
+        <v>0.001124531277537722</v>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>0.7469339915377098</v>
+        <v>0.7469339292169226</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.02426319150403365</v>
+        <v>0.02426319453073373</v>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>-0.5464580451682217</v>
+        <v>-0.5464580036950251</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.01804949870042787</v>
+        <v>0.01804949804850456</v>
       </c>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="n">
-        <v>0.9907604013767453</v>
+        <v>0.9907603512579023</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.002231262732024745</v>
+        <v>0.002231268769398914</v>
       </c>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="n">
-        <v>-2.316352245161167</v>
+        <v>-2.316351388665645</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.006015688175171676</v>
+        <v>0.006015687773131145</v>
       </c>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="n">
-        <v>0.9999993534681905</v>
+        <v>0.9999993530653966</v>
       </c>
       <c r="AM38" t="n">
-        <v>3.222645951117273e-07</v>
+        <v>3.223649747371968e-07</v>
       </c>
       <c r="AN38" t="inlineStr"/>
     </row>
@@ -4539,25 +4539,25 @@
         <v>48</v>
       </c>
       <c r="F39" t="n">
-        <v>0.464866072408512</v>
+        <v>0.4648660724078407</v>
       </c>
       <c r="G39" t="n">
         <v>0.06613756613756613</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3147165341115007</v>
+        <v>0.3147165341147267</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1215057334841287</v>
+        <v>0.1215057334732506</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03277409385829239</v>
+        <v>0.03277409386661587</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5532307663355256</v>
+        <v>0.5532307752309462</v>
       </c>
       <c r="L39" t="n">
-        <v>0.5491049323283788</v>
+        <v>0.5491049349716622</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4566,16 +4566,16 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.388301465052076</v>
+        <v>4.388301531307524</v>
       </c>
       <c r="P39" t="n">
-        <v>4.357568293928008</v>
+        <v>4.357568313617461</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.9819945676145284</v>
+        <v>0.9819945679206817</v>
       </c>
       <c r="R39" t="n">
-        <v>0.008981661082384249</v>
+        <v>0.008981661005760262</v>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
@@ -4585,38 +4585,38 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>0.8614104763354866</v>
+        <v>0.8614104811972901</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.0124599518462974</v>
+        <v>0.01245995162672164</v>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>0.2315287535118379</v>
+        <v>0.2315286334208446</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.001304206671885018</v>
+        <v>0.001304206773790893</v>
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="n">
-        <v>-0.05242748113915696</v>
+        <v>-0.05242748866655367</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.0146940678776024</v>
+        <v>0.01469406793063627</v>
       </c>
       <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="n">
-        <v>0.781611202634598</v>
+        <v>0.7816112310192532</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.005071144298890516</v>
+        <v>0.00507114396847763</v>
       </c>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="n">
-        <v>-0.1198831906614264</v>
+        <v>-0.1198832156203771</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.002183503754813192</v>
+        <v>0.002183503781482074</v>
       </c>
       <c r="AN39" t="inlineStr"/>
     </row>
@@ -4643,43 +4643,43 @@
         <v>70.70000000000002</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4301189564620539</v>
+        <v>0.4301189564542686</v>
       </c>
       <c r="G40" t="n">
         <v>0.04490244942861631</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1726240369116226</v>
+        <v>0.1726240368983525</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3491894964880415</v>
+        <v>0.3491894964967999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.003165060709665684</v>
+        <v>0.00316506072196271</v>
       </c>
       <c r="K40" t="n">
-        <v>0.5283164027424528</v>
+        <v>0.5283099149850731</v>
       </c>
       <c r="L40" t="n">
-        <v>0.5692409188383837</v>
+        <v>0.56924096681146</v>
       </c>
       <c r="M40" t="n">
-        <v>0.522701138985566</v>
+        <v>0.5227146867138378</v>
       </c>
       <c r="N40" t="n">
-        <v>0.1104856991032153</v>
+        <v>0.1104907330792118</v>
       </c>
       <c r="O40" t="n">
-        <v>4.202643391765502</v>
+        <v>4.20259502185762</v>
       </c>
       <c r="P40" t="n">
-        <v>4.507508523809872</v>
+        <v>4.507508879265339</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.9916978149582863</v>
+        <v>0.9916978971936908</v>
       </c>
       <c r="R40" t="n">
-        <v>0.005473136365717831</v>
+        <v>0.00547310925888409</v>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
@@ -4689,38 +4689,38 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
-        <v>0.9670261955693887</v>
+        <v>0.9670260995143988</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.0109583768475607</v>
+        <v>0.0109583928107157</v>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
-        <v>0.7153572480560326</v>
+        <v>0.7153459794275399</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.001213759100701683</v>
+        <v>0.001213783126019256</v>
       </c>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="n">
-        <v>0.9821727339140446</v>
+        <v>0.9821730143209756</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.003353711307356606</v>
+        <v>0.003353684929493501</v>
       </c>
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="n">
-        <v>0.9990123328687575</v>
+        <v>0.9990131096055457</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.001411341110100427</v>
+        <v>0.001410786036499719</v>
       </c>
       <c r="AK40" t="inlineStr"/>
       <c r="AL40" t="n">
-        <v>0.9999999999897455</v>
+        <v>0.999999997168464</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.94705706972353e-09</v>
+        <v>3.235435655724003e-08</v>
       </c>
       <c r="AN40" t="inlineStr"/>
     </row>
@@ -4747,43 +4747,43 @@
         <v>84.84</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3369254806988865</v>
+        <v>0.3369254807409055</v>
       </c>
       <c r="G41" t="n">
         <v>0.03741870785718027</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2464337952095151</v>
+        <v>0.2464337951089697</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3649923484168429</v>
+        <v>0.3649923484758453</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01422966781757511</v>
+        <v>0.0142296678170992</v>
       </c>
       <c r="K41" t="n">
-        <v>0.5561311174839206</v>
+        <v>0.5561311111531306</v>
       </c>
       <c r="L41" t="n">
-        <v>0.5675786677022348</v>
+        <v>0.5675786550005436</v>
       </c>
       <c r="M41" t="n">
-        <v>0.09510322729313825</v>
+        <v>0.09510293087143251</v>
       </c>
       <c r="N41" t="n">
-        <v>0.009607910224360803</v>
+        <v>0.009607868112032972</v>
       </c>
       <c r="O41" t="n">
-        <v>4.409902885576174</v>
+        <v>4.409902838427838</v>
       </c>
       <c r="P41" t="n">
-        <v>4.495138427495989</v>
+        <v>4.495138332937546</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.9942326924938512</v>
+        <v>0.9942326992478621</v>
       </c>
       <c r="R41" t="n">
-        <v>0.005885746597548107</v>
+        <v>0.005885743152258408</v>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
@@ -4793,38 +4793,38 @@
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>0.8699122566411659</v>
+        <v>0.8699123696878514</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.01050329133840707</v>
+        <v>0.01050328677389923</v>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>0.7634550602741808</v>
+        <v>0.76345446291934</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.001212911736693704</v>
+        <v>0.001212913268196007</v>
       </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="n">
-        <v>0.9823332189033043</v>
+        <v>0.9823332734744143</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.003563851299466245</v>
+        <v>0.003563845795573162</v>
       </c>
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="n">
-        <v>0.954982546630979</v>
+        <v>0.9549826152907458</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.006840394089492075</v>
+        <v>0.006840388874152072</v>
       </c>
       <c r="AK41" t="inlineStr"/>
       <c r="AL41" t="n">
-        <v>0.8188063758434938</v>
+        <v>0.8188063788650857</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.001388435755810789</v>
+        <v>0.001388435744499317</v>
       </c>
       <c r="AN41" t="inlineStr"/>
     </row>
@@ -4851,43 +4851,43 @@
         <v>124.31</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4255446328458828</v>
+        <v>0.4255446328415167</v>
       </c>
       <c r="G42" t="n">
         <v>0.02553779401981477</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2146647956812922</v>
+        <v>0.214664795708344</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3235805049574504</v>
+        <v>0.3235805049438804</v>
       </c>
       <c r="J42" t="n">
-        <v>0.01067227249555984</v>
+        <v>0.01067227248644411</v>
       </c>
       <c r="K42" t="n">
-        <v>0.5695103219420882</v>
+        <v>0.5695090403804223</v>
       </c>
       <c r="L42" t="n">
-        <v>0.567741715497726</v>
+        <v>0.5677403256515395</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3991687508264905</v>
+        <v>0.3991692016855862</v>
       </c>
       <c r="N42" t="n">
-        <v>0.06191300225348243</v>
+        <v>0.06191315743207212</v>
       </c>
       <c r="O42" t="n">
-        <v>4.509519969177892</v>
+        <v>4.509510429360552</v>
       </c>
       <c r="P42" t="n">
-        <v>4.496354142500471</v>
+        <v>4.496343796019599</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.9618113939159544</v>
+        <v>0.9618113956506159</v>
       </c>
       <c r="R42" t="n">
-        <v>0.01294095259659222</v>
+        <v>0.01294095230389864</v>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
@@ -4897,31 +4897,31 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>0.8583697096695226</v>
+        <v>0.8583697209373519</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.0206523885608478</v>
+        <v>0.020652387738042</v>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>0.9998279033187278</v>
+        <v>0.9998278869589716</v>
       </c>
       <c r="AD42" t="n">
-        <v>7.011592156942258e-05</v>
+        <v>7.011925415004302e-05</v>
       </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="n">
-        <v>0.6869359442877778</v>
+        <v>0.6869359360382292</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.01632990586074336</v>
+        <v>0.01632990608752157</v>
       </c>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="n">
-        <v>0.9660122728424613</v>
+        <v>0.966012279850898</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.005701216788251034</v>
+        <v>0.005701216199333304</v>
       </c>
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
@@ -4953,43 +4953,43 @@
         <v>40.1</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5997176448026437</v>
+        <v>0.5997176446896944</v>
       </c>
       <c r="G43" t="n">
         <v>0.0791671614614258</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2378772798847145</v>
+        <v>0.2378772801295146</v>
       </c>
       <c r="I43" t="n">
-        <v>0.05923193023736853</v>
+        <v>0.05923193014095748</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0240059836138475</v>
+        <v>0.02400598357840774</v>
       </c>
       <c r="K43" t="n">
-        <v>0.4953620074672234</v>
+        <v>0.4953673905457935</v>
       </c>
       <c r="L43" t="n">
-        <v>0.5435126257415349</v>
+        <v>0.5435124309696449</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3683045390121662</v>
+        <v>0.3682914447695772</v>
       </c>
       <c r="N43" t="n">
-        <v>0.07179043718877728</v>
+        <v>0.07178734094783114</v>
       </c>
       <c r="O43" t="n">
-        <v>3.956773080980899</v>
+        <v>3.956813274070416</v>
       </c>
       <c r="P43" t="n">
-        <v>4.315885400832582</v>
+        <v>4.315883952271286</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.9294625116452134</v>
+        <v>0.9294581933505259</v>
       </c>
       <c r="R43" t="n">
-        <v>0.01622785549969679</v>
+        <v>0.01622835222532864</v>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
@@ -4999,38 +4999,38 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>0.8591416301352739</v>
+        <v>0.8591311289726685</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.03227717007729149</v>
+        <v>0.0322783731944384</v>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>0.5715983214402245</v>
+        <v>0.5716141520614147</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.003091070578040153</v>
+        <v>0.003091013465729548</v>
       </c>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="n">
-        <v>0.7441255299772154</v>
+        <v>0.7441213277136913</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.01603035637342281</v>
+        <v>0.01603048803568875</v>
       </c>
       <c r="AH43" t="inlineStr"/>
       <c r="AI43" t="n">
-        <v>0.7376034787767961</v>
+        <v>0.7376329209397076</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.002871528873232446</v>
+        <v>0.002871367767411471</v>
       </c>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="n">
-        <v>0.991892510691032</v>
+        <v>0.9918926148755154</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.0003578289390546378</v>
+        <v>0.0003578266393019511</v>
       </c>
       <c r="AN43" t="inlineStr"/>
     </row>
@@ -5057,25 +5057,25 @@
         <v>25.2</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3587984910438237</v>
+        <v>0.3587984911488203</v>
       </c>
       <c r="G44" t="n">
         <v>0.1259763164525069</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2964643700107539</v>
+        <v>0.2964643700757857</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1968371786437586</v>
+        <v>0.1968371786061268</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02192364384915694</v>
+        <v>0.02192364371676016</v>
       </c>
       <c r="K44" t="n">
-        <v>0.5286870787682787</v>
+        <v>0.5286870788523484</v>
       </c>
       <c r="L44" t="n">
-        <v>0.5600074997541628</v>
+        <v>0.5600074997451531</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5084,16 +5084,16 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.205406969984286</v>
+        <v>4.205406970611063</v>
       </c>
       <c r="P44" t="n">
-        <v>4.438748696822004</v>
+        <v>4.438748696755018</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.95302310452405</v>
+        <v>0.9530231045110747</v>
       </c>
       <c r="R44" t="n">
-        <v>0.007382335648650627</v>
+        <v>0.007382335651406289</v>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
@@ -5103,38 +5103,38 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>0.9556761552670739</v>
+        <v>0.955676155014881</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.009440932723754175</v>
+        <v>0.009440932754758139</v>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>0.8126900677434666</v>
+        <v>0.8126900683056585</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.004799897038070332</v>
+        <v>0.004799897030867129</v>
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="n">
-        <v>0.8998961627984626</v>
+        <v>0.8998961630219063</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.01106594864011849</v>
+        <v>0.01106594863051115</v>
       </c>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="n">
-        <v>0.9233222961529891</v>
+        <v>0.9233222961764832</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.006015608589755103</v>
+        <v>0.006015608581377027</v>
       </c>
       <c r="AK44" t="inlineStr"/>
       <c r="AL44" t="n">
-        <v>0.6252075221395293</v>
+        <v>0.6252075159771944</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.00129669189296649</v>
+        <v>0.001296691893196228</v>
       </c>
       <c r="AN44" t="inlineStr"/>
     </row>
@@ -5161,25 +5161,25 @@
         <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4805050132618147</v>
+        <v>0.4805050130472089</v>
       </c>
       <c r="G45" t="n">
         <v>0.1587301587301587</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1510431451475349</v>
+        <v>0.1510431452397918</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1848438942219129</v>
+        <v>0.1848438943574318</v>
       </c>
       <c r="J45" t="n">
-        <v>0.02487778863857871</v>
+        <v>0.02487778862540869</v>
       </c>
       <c r="K45" t="n">
-        <v>0.5400703130547023</v>
+        <v>0.5400682057539531</v>
       </c>
       <c r="L45" t="n">
-        <v>0.5560424067601982</v>
+        <v>0.5560427753777556</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5188,16 +5188,16 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.290254436529441</v>
+        <v>4.290238732877078</v>
       </c>
       <c r="P45" t="n">
-        <v>4.409240661505166</v>
+        <v>4.409243406450039</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.9689003003205184</v>
+        <v>0.9689000522508463</v>
       </c>
       <c r="R45" t="n">
-        <v>0.0086126776460247</v>
+        <v>0.008612711993460836</v>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
@@ -5207,38 +5207,38 @@
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="n">
-        <v>0.9761786969789389</v>
+        <v>0.9761782419009816</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.01320113187623589</v>
+        <v>0.01320125796474662</v>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
-        <v>0.9228403531276196</v>
+        <v>0.9228405772571957</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.007285102563709765</v>
+        <v>0.007285091982996913</v>
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="n">
-        <v>0.8734203387177651</v>
+        <v>0.8734204167665813</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.008454722298625272</v>
+        <v>0.008454719699811132</v>
       </c>
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="n">
-        <v>0.9225908945229462</v>
+        <v>0.9225910791922862</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.008466968692137505</v>
+        <v>0.008466958599618869</v>
       </c>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="n">
-        <v>0.9804677110250209</v>
+        <v>0.980467803565608</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.0006136701179116748</v>
+        <v>0.0006136686638361343</v>
       </c>
       <c r="AN45" t="inlineStr"/>
     </row>
@@ -5265,25 +5265,25 @@
         <v>13.8</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4123104193140011</v>
+        <v>0.4123104194730447</v>
       </c>
       <c r="G46" t="n">
         <v>0.2300437083045778</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09500900007204896</v>
+        <v>0.09500899989902098</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2190898484594311</v>
+        <v>0.2190898485295714</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04354702384994095</v>
+        <v>0.04354702379378513</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4692195827002179</v>
+        <v>0.4692227989288898</v>
       </c>
       <c r="L46" t="n">
-        <v>0.56319358864237</v>
+        <v>0.5631935498193604</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5292,16 +5292,16 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.761450846446995</v>
+        <v>3.761474892830758</v>
       </c>
       <c r="P46" t="n">
-        <v>4.462444238329396</v>
+        <v>4.462443951202665</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9695306941104365</v>
+        <v>0.9695306743059184</v>
       </c>
       <c r="R46" t="n">
-        <v>0.008322570492744614</v>
+        <v>0.008322573200325848</v>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
@@ -5311,38 +5311,38 @@
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
-        <v>0.9840113589995604</v>
+        <v>0.9840113061080106</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.009750328092818736</v>
+        <v>0.009750344224852572</v>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>0.9224336542903625</v>
+        <v>0.9224336846664369</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.01033758898922709</v>
+        <v>0.0103375869650541</v>
       </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="n">
-        <v>0.9848925210034284</v>
+        <v>0.9848925307757307</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.002011984109332633</v>
+        <v>0.002011983455999561</v>
       </c>
       <c r="AH46" t="inlineStr"/>
       <c r="AI46" t="n">
-        <v>0.8728316232390262</v>
+        <v>0.872831664241837</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.01180908740359581</v>
+        <v>0.01180908550323005</v>
       </c>
       <c r="AK46" t="inlineStr"/>
       <c r="AL46" t="n">
-        <v>0.9880876414415648</v>
+        <v>0.9880876398478945</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.0009426710156491396</v>
+        <v>0.0009426710778015792</v>
       </c>
       <c r="AN46" t="inlineStr"/>
     </row>
@@ -5369,25 +5369,25 @@
         <v>19</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4235443992070436</v>
+        <v>0.4235443991299785</v>
       </c>
       <c r="G47" t="n">
         <v>0.1670843776106934</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2433419961172016</v>
+        <v>0.2433419961113411</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1505472905220324</v>
+        <v>0.1505472906218897</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01548193654302897</v>
+        <v>0.01548193652609739</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5376530400040005</v>
+        <v>0.5376530401280268</v>
       </c>
       <c r="L47" t="n">
-        <v>0.55386159540626</v>
+        <v>0.5538615954093717</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -5396,16 +5396,16 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.272240003116125</v>
+        <v>4.272240004040461</v>
       </c>
       <c r="P47" t="n">
-        <v>4.392994941751244</v>
+        <v>4.392994941774486</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.9451092518699958</v>
+        <v>0.9451092518371923</v>
       </c>
       <c r="R47" t="n">
-        <v>0.008804600464171093</v>
+        <v>0.008804600465676347</v>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
@@ -5415,38 +5415,38 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="n">
-        <v>0.940644718982248</v>
+        <v>0.9406447191409113</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.01342367472314932</v>
+        <v>0.01342367470477476</v>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>0.8033244109864681</v>
+        <v>0.8033244105694615</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.00692931419805967</v>
+        <v>0.006929314205405702</v>
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="n">
-        <v>0.847695687677937</v>
+        <v>0.8476956870377512</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.01163620960645925</v>
+        <v>0.01163620962902435</v>
       </c>
       <c r="AH47" t="inlineStr"/>
       <c r="AI47" t="n">
-        <v>0.9016049470413948</v>
+        <v>0.901604947292363</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.004864614147289625</v>
+        <v>0.004864614147542084</v>
       </c>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="n">
-        <v>0.9099581517169765</v>
+        <v>0.9099581527661619</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.0005732918389398196</v>
+        <v>0.0005732918358290306</v>
       </c>
       <c r="AN47" t="inlineStr"/>
     </row>
@@ -5473,25 +5473,25 @@
         <v>26.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4466462867107708</v>
+        <v>0.4466462865765082</v>
       </c>
       <c r="G48" t="n">
         <v>0.1197963462114405</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3318502634836513</v>
+        <v>0.3318502636697235</v>
       </c>
       <c r="I48" t="n">
-        <v>0.06116662707319055</v>
+        <v>0.06116662702741293</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04054047652094685</v>
+        <v>0.04054047651491494</v>
       </c>
       <c r="K48" t="n">
-        <v>0.4047097120777118</v>
+        <v>0.4047095718033272</v>
       </c>
       <c r="L48" t="n">
-        <v>0.5459567870506425</v>
+        <v>0.545956786370435</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5500,16 +5500,16 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.278188650913639</v>
+        <v>3.27818759776892</v>
       </c>
       <c r="P48" t="n">
-        <v>4.334035035067895</v>
+        <v>4.334035029847181</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.9639931396374642</v>
+        <v>0.9639931396920778</v>
       </c>
       <c r="R48" t="n">
-        <v>0.009784098841558167</v>
+        <v>0.009784098834266893</v>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
@@ -5519,38 +5519,38 @@
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>0.9507073691867312</v>
+        <v>0.9507073692285446</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.01623439938749992</v>
+        <v>0.01623439937648523</v>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>0.885564897739694</v>
+        <v>0.8855648979047368</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.005714404488955672</v>
+        <v>0.005714404484834903</v>
       </c>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="n">
-        <v>0.9510188166467399</v>
+        <v>0.9510188167945697</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.01283437782524244</v>
+        <v>0.01283437781265882</v>
       </c>
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="n">
-        <v>0.7409315243339216</v>
+        <v>0.7409315238739723</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.004206145926056573</v>
+        <v>0.004206145927768051</v>
       </c>
       <c r="AK48" t="inlineStr"/>
       <c r="AL48" t="n">
-        <v>0.9996682151621836</v>
+        <v>0.9996682151629799</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.0001410349541343809</v>
+        <v>0.0001410349539647752</v>
       </c>
       <c r="AN48" t="inlineStr"/>
     </row>
@@ -5577,43 +5577,43 @@
         <v>27.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4784766675558373</v>
+        <v>0.4784766676196412</v>
       </c>
       <c r="G49" t="n">
         <v>0.1167133520074696</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1617722833471003</v>
+        <v>0.1617722832354314</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2200624129180908</v>
+        <v>0.2200624129775048</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02297528417150188</v>
+        <v>0.0229752841599529</v>
       </c>
       <c r="K49" t="n">
-        <v>0.507334054451019</v>
+        <v>0.5073345342215706</v>
       </c>
       <c r="L49" t="n">
-        <v>0.5559303586706785</v>
+        <v>0.5559303762407005</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1424750500673412</v>
+        <v>0.1424770076860469</v>
       </c>
       <c r="N49" t="n">
-        <v>0.007061884483731409</v>
+        <v>0.007062051847249928</v>
       </c>
       <c r="O49" t="n">
-        <v>4.046137816931933</v>
+        <v>4.046141397159318</v>
       </c>
       <c r="P49" t="n">
-        <v>4.408391981495804</v>
+        <v>4.408392112494288</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.9239242745457639</v>
+        <v>0.9239247147496599</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01307369440207055</v>
+        <v>0.01307365657683994</v>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
@@ -5623,38 +5623,38 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>0.9320841862665314</v>
+        <v>0.9320855102051478</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.01757876140134717</v>
+        <v>0.01757859006220606</v>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
-        <v>0.9208852584045786</v>
+        <v>0.920884629014465</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.002697357934196381</v>
+        <v>0.002697368663467601</v>
       </c>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="n">
-        <v>0.4430907100250938</v>
+        <v>0.4430906026442899</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.01377740177948114</v>
+        <v>0.01377740309040373</v>
       </c>
       <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="n">
-        <v>0.2814832788216017</v>
+        <v>0.2814812427381936</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.01862424005392624</v>
+        <v>0.01862426644983823</v>
       </c>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="n">
-        <v>0.8771289558488665</v>
+        <v>0.8771288451155599</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.001280514343327963</v>
+        <v>0.001280514917511123</v>
       </c>
       <c r="AN49" t="inlineStr"/>
     </row>
@@ -5681,25 +5681,25 @@
         <v>22.6</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4707222729765161</v>
+        <v>0.4707222730832482</v>
       </c>
       <c r="G50" t="n">
         <v>0.1404691670178395</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06718571998428063</v>
+        <v>0.06718571980350242</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2979720652205344</v>
+        <v>0.2979720652617544</v>
       </c>
       <c r="J50" t="n">
-        <v>0.02365077480082941</v>
+        <v>0.02365077483365554</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5409958952894118</v>
+        <v>0.540998905599272</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5605201676033635</v>
+        <v>0.5605220283389617</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -5708,16 +5708,16 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4.297151770118208</v>
+        <v>4.297174202195596</v>
       </c>
       <c r="P50" t="n">
-        <v>4.442562212890054</v>
+        <v>4.442576016404089</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.9608045769180966</v>
+        <v>0.9608048395334117</v>
       </c>
       <c r="R50" t="n">
-        <v>0.01058154850218405</v>
+        <v>0.01058151305540473</v>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
@@ -5727,31 +5727,31 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
-        <v>0.9819033004737431</v>
+        <v>0.9819038754006788</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.01131730506638015</v>
+        <v>0.01131712529372419</v>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>0.9374170034323297</v>
+        <v>0.9374168392624717</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.005330505898001532</v>
+        <v>0.005330512889579681</v>
       </c>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="n">
-        <v>0.9482343494354788</v>
+        <v>0.9482341287657269</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.002324519793881028</v>
+        <v>0.002324524740709713</v>
       </c>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="n">
-        <v>0.8050630900901391</v>
+        <v>0.8050626038217311</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.01771919545651057</v>
+        <v>0.01771921756038426</v>
       </c>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
@@ -5783,25 +5783,25 @@
         <v>12.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4132915616414226</v>
+        <v>0.4132915619983448</v>
       </c>
       <c r="G51" t="n">
         <v>0.2602133749674733</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02750138666645612</v>
+        <v>0.02750138682641973</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2472592619614906</v>
+        <v>0.247259261508163</v>
       </c>
       <c r="J51" t="n">
-        <v>0.05173441476315732</v>
+        <v>0.05173441469959904</v>
       </c>
       <c r="K51" t="n">
-        <v>0.4812086802605804</v>
+        <v>0.4812090458799397</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5582457840330085</v>
+        <v>0.5582457985853087</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -5810,16 +5810,16 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.851059526098111</v>
+        <v>3.851062257943341</v>
       </c>
       <c r="P51" t="n">
-        <v>4.425622904874372</v>
+        <v>4.425623013431624</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.9284299964927997</v>
+        <v>0.9284302111968471</v>
       </c>
       <c r="R51" t="n">
-        <v>0.01074432703134815</v>
+        <v>0.01074431091631254</v>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
@@ -5829,38 +5829,38 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
-        <v>0.9295092822420135</v>
+        <v>0.9295097899543076</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.01569655784531013</v>
+        <v>0.01569650133491646</v>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>0.7965003248261033</v>
+        <v>0.7965002581684573</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.01440401834558218</v>
+        <v>0.01440402070464707</v>
       </c>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="n">
-        <v>-0.8078403432370145</v>
+        <v>-0.8078417074611575</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.003372999102247724</v>
+        <v>0.003373000388212927</v>
       </c>
       <c r="AH51" t="inlineStr"/>
       <c r="AI51" t="n">
-        <v>0.8916714400390217</v>
+        <v>0.8916714729925945</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.01056733408254436</v>
+        <v>0.01056733245141099</v>
       </c>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="n">
-        <v>0.9956322801226107</v>
+        <v>0.9956322739637581</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.0005472399253436916</v>
+        <v>0.0005472403105589382</v>
       </c>
       <c r="AN51" t="inlineStr"/>
     </row>
@@ -5887,25 +5887,25 @@
         <v>28.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4153806106757402</v>
+        <v>0.4153806106021484</v>
       </c>
       <c r="G52" t="n">
         <v>0.1113895850737956</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3106906626687218</v>
+        <v>0.3106906628036006</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1579071580203451</v>
+        <v>0.1579071579734052</v>
       </c>
       <c r="J52" t="n">
-        <v>0.004631983561397277</v>
+        <v>0.004631983547050241</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5429836066241071</v>
+        <v>0.5429836102873031</v>
       </c>
       <c r="L52" t="n">
-        <v>0.5519809004860716</v>
+        <v>0.5519809006218619</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -5914,16 +5914,16 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4.311963123218198</v>
+        <v>4.3119631505133</v>
       </c>
       <c r="P52" t="n">
-        <v>4.378988121467831</v>
+        <v>4.378988122480944</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.9652852496903884</v>
+        <v>0.9652852489118535</v>
       </c>
       <c r="R52" t="n">
-        <v>0.008997260360846616</v>
+        <v>0.008997260461854279</v>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
@@ -5933,38 +5933,38 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
-        <v>0.9775778295623077</v>
+        <v>0.9775778307024698</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.006857003628598683</v>
+        <v>0.006857003452033116</v>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>0.9189528216211351</v>
+        <v>0.9189528149507483</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.002013919310586962</v>
+        <v>0.002013919393462274</v>
       </c>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="n">
-        <v>0.7873706895020927</v>
+        <v>0.7873706870413455</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.01655815742488062</v>
+        <v>0.01655815752584053</v>
       </c>
       <c r="AH52" t="inlineStr"/>
       <c r="AI52" t="n">
-        <v>0.7108994128057953</v>
+        <v>0.710899385173644</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.008864422778274969</v>
+        <v>0.008864423224188109</v>
       </c>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="n">
-        <v>0.001044304216321068</v>
+        <v>0.001044365897988953</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.0009636035248012068</v>
+        <v>0.0009636034867096767</v>
       </c>
       <c r="AN52" t="inlineStr"/>
     </row>
@@ -5991,43 +5991,43 @@
         <v>26.8</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4510893860666219</v>
+        <v>0.4510893861537268</v>
       </c>
       <c r="G53" t="n">
         <v>0.1184553423359393</v>
       </c>
       <c r="H53" t="n">
-        <v>0.200863297038614</v>
+        <v>0.2008632968133135</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2264019040843809</v>
+        <v>0.2264019042000988</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00319007047444387</v>
+        <v>0.003190070496921492</v>
       </c>
       <c r="K53" t="n">
-        <v>0.5670780971791589</v>
+        <v>0.5670778507893233</v>
       </c>
       <c r="L53" t="n">
-        <v>0.5591499193549173</v>
+        <v>0.559149955133811</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1240744627952637</v>
+        <v>0.1240675546456378</v>
       </c>
       <c r="N53" t="n">
-        <v>0.004988707459151543</v>
+        <v>0.004988308538799751</v>
       </c>
       <c r="O53" t="n">
-        <v>4.491413962140649</v>
+        <v>4.491412127883297</v>
       </c>
       <c r="P53" t="n">
-        <v>4.432383425697124</v>
+        <v>4.43238369216994</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.9852417438817525</v>
+        <v>0.9852419322216532</v>
       </c>
       <c r="R53" t="n">
-        <v>0.005223126113549885</v>
+        <v>0.00522309278597276</v>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
@@ -6037,38 +6037,38 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="n">
-        <v>0.9776580948010445</v>
+        <v>0.9776583125707952</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.008662723351526966</v>
+        <v>0.008662681136492928</v>
       </c>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>0.7157641763372806</v>
+        <v>0.7157696431346874</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.005472920023092795</v>
+        <v>0.005472867391639681</v>
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="n">
-        <v>0.9851775095484872</v>
+        <v>0.9851774075332962</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.003005789052673199</v>
+        <v>0.003005799393165001</v>
       </c>
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="n">
-        <v>0.9816799404673644</v>
+        <v>0.9816804226091278</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.00394163611045416</v>
+        <v>0.003941584243508088</v>
       </c>
       <c r="AK53" t="inlineStr"/>
       <c r="AL53" t="n">
-        <v>0.8771047225238296</v>
+        <v>0.877101308802778</v>
       </c>
       <c r="AM53" t="n">
-        <v>0.0001552541574540863</v>
+        <v>0.0001552563129695453</v>
       </c>
       <c r="AN53" t="inlineStr"/>
     </row>
@@ -6095,43 +6095,43 @@
         <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4286683890706328</v>
+        <v>0.4286683889482371</v>
       </c>
       <c r="G54" t="n">
         <v>0.1269841269841269</v>
       </c>
       <c r="H54" t="n">
-        <v>0.2576179527120835</v>
+        <v>0.2576179529315623</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1597790966902238</v>
+        <v>0.15977909662141</v>
       </c>
       <c r="J54" t="n">
-        <v>0.02695043454293275</v>
+        <v>0.02695043451466368</v>
       </c>
       <c r="K54" t="n">
-        <v>0.5192367329134363</v>
+        <v>0.5192366779258668</v>
       </c>
       <c r="L54" t="n">
-        <v>0.5515678024324538</v>
+        <v>0.5515677839918689</v>
       </c>
       <c r="M54" t="n">
-        <v>0.3229157324759777</v>
+        <v>0.3229150577034521</v>
       </c>
       <c r="N54" t="n">
-        <v>0.03857309580623619</v>
+        <v>0.03857301123878863</v>
       </c>
       <c r="O54" t="n">
-        <v>4.134936389104962</v>
+        <v>4.13493597898387</v>
       </c>
       <c r="P54" t="n">
-        <v>4.375886144305886</v>
+        <v>4.375886006937696</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.9340780364024328</v>
+        <v>0.9340779415627251</v>
       </c>
       <c r="R54" t="n">
-        <v>0.00932322964076867</v>
+        <v>0.009323236348494895</v>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
@@ -6141,38 +6141,38 @@
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>0.9127659723197946</v>
+        <v>0.9127658671205883</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.01521716787538714</v>
+        <v>0.01521717703971186</v>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>0.3683017101695465</v>
+        <v>0.3683029080147882</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.004583494923799544</v>
+        <v>0.004583490578117217</v>
       </c>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="n">
-        <v>0.8070285197022052</v>
+        <v>0.8070280613670997</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.01302756271362885</v>
+        <v>0.01302757820781633</v>
       </c>
       <c r="AH54" t="inlineStr"/>
       <c r="AI54" t="n">
-        <v>0.9328120890658789</v>
+        <v>0.9328121797319994</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.003321413215073124</v>
+        <v>0.003321410986293672</v>
       </c>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="n">
-        <v>0.8510080464395345</v>
+        <v>0.8510083448907195</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.001137213614732013</v>
+        <v>0.001137212474085545</v>
       </c>
       <c r="AN54" t="inlineStr"/>
     </row>
@@ -6199,43 +6199,43 @@
         <v>29</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4347068963260962</v>
+        <v>0.4347068963151978</v>
       </c>
       <c r="G55" t="n">
         <v>0.1094690749863163</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2837256736143648</v>
+        <v>0.2837256736186445</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1694315236798098</v>
+        <v>0.1694315237196296</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00266683139341308</v>
+        <v>0.002666831360211718</v>
       </c>
       <c r="K55" t="n">
-        <v>0.5563410684470536</v>
+        <v>0.5563410613774147</v>
       </c>
       <c r="L55" t="n">
-        <v>0.5566633662362249</v>
+        <v>0.5566633637758814</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2315986820760616</v>
+        <v>0.2315980980051433</v>
       </c>
       <c r="N55" t="n">
-        <v>0.02992057583063879</v>
+        <v>0.02992044904201858</v>
       </c>
       <c r="O55" t="n">
-        <v>4.411466481943051</v>
+        <v>4.411466429292571</v>
       </c>
       <c r="P55" t="n">
-        <v>4.41386670503176</v>
+        <v>4.413866686708394</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.8656895894651874</v>
+        <v>0.8656895358538711</v>
       </c>
       <c r="R55" t="n">
-        <v>0.01477855881258635</v>
+        <v>0.01477856176381772</v>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
@@ -6245,38 +6245,38 @@
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="n">
-        <v>0.7588511292980465</v>
+        <v>0.7588513883922561</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.02370435879225456</v>
+        <v>0.02370434605326187</v>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
-        <v>0.1885740618111673</v>
+        <v>0.1885745162327568</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.003944085022411729</v>
+        <v>0.003944083918011714</v>
       </c>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="n">
-        <v>0.5591732286465172</v>
+        <v>0.5591721506770527</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.02126773132531239</v>
+        <v>0.02126775733373867</v>
       </c>
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="n">
-        <v>0.6969689764574305</v>
+        <v>0.6969692546355859</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.007862455357550723</v>
+        <v>0.007862451758334709</v>
       </c>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="n">
-        <v>0.7697483982478852</v>
+        <v>0.7697488583699308</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.0006648086147663551</v>
+        <v>0.0006648079503361207</v>
       </c>
       <c r="AN55" t="inlineStr"/>
     </row>
@@ -6303,25 +6303,25 @@
         <v>19.9</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3573142119608926</v>
+        <v>0.3573142119374196</v>
       </c>
       <c r="G56" t="n">
         <v>0.1595277977187525</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2647607177751945</v>
+        <v>0.2647607177672366</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1794591218770647</v>
+        <v>0.179459121882217</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03893815066809572</v>
+        <v>0.03893815069437438</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5097180810386136</v>
+        <v>0.5097180812285835</v>
       </c>
       <c r="L56" t="n">
-        <v>0.5518535577083454</v>
+        <v>0.5518535577063126</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -6330,16 +6330,16 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>4.063927352245716</v>
+        <v>4.063927353663189</v>
       </c>
       <c r="P56" t="n">
-        <v>4.378024103527062</v>
+        <v>4.378024103512052</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.8290942444541722</v>
+        <v>0.8290942443754199</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01212977896087996</v>
+        <v>0.01212977896340412</v>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
@@ -6349,38 +6349,38 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>0.7283256784225867</v>
+        <v>0.7283256773140883</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.01819792556061479</v>
+        <v>0.01819792558573751</v>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
-        <v>-0.1642604336165421</v>
+        <v>-0.1642604344447396</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.009456969361349826</v>
+        <v>0.009456969364713437</v>
       </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="n">
-        <v>0.6280877513406949</v>
+        <v>0.6280877531772295</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.01612351822136859</v>
+        <v>0.01612351819748031</v>
       </c>
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="n">
-        <v>0.7483831336531044</v>
+        <v>0.7483831332446416</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.00729292864910951</v>
+        <v>0.007292928655823623</v>
       </c>
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="n">
-        <v>0.915257761023231</v>
+        <v>0.9152577609598676</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.001379955025367335</v>
+        <v>0.00137995502558049</v>
       </c>
       <c r="AN56" t="inlineStr"/>
     </row>
@@ -6407,25 +6407,25 @@
         <v>13.4</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3569988198360919</v>
+        <v>0.3569988198034146</v>
       </c>
       <c r="G57" t="n">
         <v>0.2369106846718786</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1636235303975117</v>
+        <v>0.1636235302919157</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2180246773556286</v>
+        <v>0.2180246774233276</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02444228773888892</v>
+        <v>0.02444228780946331</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5362984060044483</v>
+        <v>0.5362984060841561</v>
       </c>
       <c r="L57" t="n">
-        <v>0.554455161301568</v>
+        <v>0.5544551612839508</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -6434,16 +6434,16 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4.26214400069415</v>
+        <v>4.262144001288224</v>
       </c>
       <c r="P57" t="n">
-        <v>4.397413072186263</v>
+        <v>4.397413072055139</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.9075211627563269</v>
+        <v>0.9075211626788839</v>
       </c>
       <c r="R57" t="n">
-        <v>0.009247306723752669</v>
+        <v>0.009247306725298221</v>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
@@ -6453,38 +6453,38 @@
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
-        <v>0.817918593012726</v>
+        <v>0.8179185931687083</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.01615090791475431</v>
+        <v>0.01615090790159598</v>
       </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>0.6169303172194858</v>
+        <v>0.6169303178994402</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.008922752914418243</v>
+        <v>0.008922752906499234</v>
       </c>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="n">
-        <v>0.7460658066096132</v>
+        <v>0.7460658037718496</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.007736042969368808</v>
+        <v>0.007736042997610403</v>
       </c>
       <c r="AH57" t="inlineStr"/>
       <c r="AI57" t="n">
-        <v>0.9245547766948449</v>
+        <v>0.9245547762630314</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.00505468598589359</v>
+        <v>0.005054686009566027</v>
       </c>
       <c r="AK57" t="inlineStr"/>
       <c r="AL57" t="n">
-        <v>0.6597688663710393</v>
+        <v>0.6597688607359593</v>
       </c>
       <c r="AM57" t="n">
-        <v>0.001303783315303731</v>
+        <v>0.00130378332796253</v>
       </c>
       <c r="AN57" t="inlineStr"/>
     </row>
@@ -6511,43 +6511,43 @@
         <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3897461385626112</v>
+        <v>0.3897461386008995</v>
       </c>
       <c r="G58" t="n">
         <v>0.1221001221001221</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2557628102080468</v>
+        <v>0.2557628103268892</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2061345128303654</v>
+        <v>0.2061345125957501</v>
       </c>
       <c r="J58" t="n">
-        <v>0.02625641629885448</v>
+        <v>0.02625641637633904</v>
       </c>
       <c r="K58" t="n">
-        <v>0.5115706784830822</v>
+        <v>0.5115706920577616</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5658850689946624</v>
+        <v>0.5658851085135792</v>
       </c>
       <c r="M58" t="n">
-        <v>0.6267182989987903</v>
+        <v>0.6267182538808871</v>
       </c>
       <c r="N58" t="n">
-        <v>0.08247842331091572</v>
+        <v>0.08247818065311213</v>
       </c>
       <c r="O58" t="n">
-        <v>4.077750057352576</v>
+        <v>4.077750158632536</v>
       </c>
       <c r="P58" t="n">
-        <v>4.482453740644113</v>
+        <v>4.48245403487511</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.9901554915404083</v>
+        <v>0.9901555024233272</v>
       </c>
       <c r="R58" t="n">
-        <v>0.004172220686021936</v>
+        <v>0.004172218379401016</v>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
@@ -6557,38 +6557,38 @@
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
-        <v>0.9873814863589049</v>
+        <v>0.9873814678545459</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.006517818485245936</v>
+        <v>0.006517823266426861</v>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>0.9785044102272578</v>
+        <v>0.9785043195282748</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.001349368949458598</v>
+        <v>0.001349371796234697</v>
       </c>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="n">
-        <v>0.9789336013243369</v>
+        <v>0.9789335948297329</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.005576852627025074</v>
+        <v>0.005576853486716911</v>
       </c>
       <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="n">
-        <v>0.9834196429093729</v>
+        <v>0.9834199112724096</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.003303430461131876</v>
+        <v>0.003303403725051393</v>
       </c>
       <c r="AK58" t="inlineStr"/>
       <c r="AL58" t="n">
-        <v>0.9425643257586086</v>
+        <v>0.9425642619607106</v>
       </c>
       <c r="AM58" t="n">
-        <v>0.0008487843429751338</v>
+        <v>0.0008487848179716835</v>
       </c>
       <c r="AN58" t="inlineStr"/>
     </row>
@@ -6615,25 +6615,25 @@
         <v>10.6506024096385</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4031657915982697</v>
+        <v>0.4031657917179133</v>
       </c>
       <c r="G59" t="n">
         <v>0.2980679451267702</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09858303468278869</v>
+        <v>0.098583034577217</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1793800069532604</v>
+        <v>0.1793800069472718</v>
       </c>
       <c r="J59" t="n">
-        <v>0.02080322163891103</v>
+        <v>0.02080322163082778</v>
       </c>
       <c r="K59" t="n">
-        <v>0.5293059348727757</v>
+        <v>0.529305935645196</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5537011020857625</v>
+        <v>0.553701101692763</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>4.210020762317669</v>
+        <v>4.210020768076263</v>
       </c>
       <c r="P59" t="n">
-        <v>4.391793516466226</v>
+        <v>4.39179351353965</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.7893019037545375</v>
+        <v>0.7893018896285579</v>
       </c>
       <c r="R59" t="n">
-        <v>0.01964749602167767</v>
+        <v>0.01964749668248941</v>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
@@ -6661,38 +6661,38 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="n">
-        <v>0.7511808006713493</v>
+        <v>0.7511807624920737</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.03127042221855022</v>
+        <v>0.03127042462895777</v>
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
-        <v>0.456024180753672</v>
+        <v>0.4560241866266972</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.02279286721567782</v>
+        <v>0.02279286709263642</v>
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="n">
-        <v>0.1390582692687956</v>
+        <v>0.1390582794964369</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.01076441605967704</v>
+        <v>0.01076441596643148</v>
       </c>
       <c r="AH59" t="inlineStr"/>
       <c r="AI59" t="n">
-        <v>-1.015799239317717</v>
+        <v>-1.015799154053648</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.01761129966795367</v>
+        <v>0.01761129929423078</v>
       </c>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="n">
-        <v>-0.662332675334125</v>
+        <v>-0.6623326364022384</v>
       </c>
       <c r="AM59" t="n">
-        <v>0.00259535524947564</v>
+        <v>0.00259535522326054</v>
       </c>
       <c r="AN59" t="inlineStr"/>
     </row>
@@ -6719,25 +6719,25 @@
         <v>45.2784503631961</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6185024514073951</v>
+        <v>0.6185024514128479</v>
       </c>
       <c r="G60" t="n">
         <v>0.07011289364230544</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1901432799511997</v>
+        <v>0.1901432797896153</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1060804578008114</v>
+        <v>0.1060804579527164</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0151609171982884</v>
+        <v>0.015160917202515</v>
       </c>
       <c r="K60" t="n">
-        <v>0.520091897588902</v>
+        <v>0.5200918946229371</v>
       </c>
       <c r="L60" t="n">
-        <v>0.5419720878153651</v>
+        <v>0.5419720835506272</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -6746,16 +6746,16 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>4.141314459674549</v>
+        <v>4.141314437553916</v>
       </c>
       <c r="P60" t="n">
-        <v>4.304414026823678</v>
+        <v>4.304413995045782</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.8246015048840531</v>
+        <v>0.8246014103624506</v>
       </c>
       <c r="R60" t="n">
-        <v>0.02604866526239791</v>
+        <v>0.02604867227997971</v>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
@@ -6765,38 +6765,38 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="n">
-        <v>0.34159354583436</v>
+        <v>0.3415931666269646</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.0568477079221997</v>
+        <v>0.05684772429543986</v>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>-1.724682159987728</v>
+        <v>-1.72468140026304</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.008748456186128822</v>
+        <v>0.00874845496646021</v>
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="n">
-        <v>0.6533379756932023</v>
+        <v>0.6533377946428448</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.006493303028177932</v>
+        <v>0.00649330471258459</v>
       </c>
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="n">
-        <v>-7.498498238228663</v>
+        <v>-7.498491217956332</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.006486444317226213</v>
+        <v>0.006486441684080717</v>
       </c>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="n">
-        <v>0.9388936035041684</v>
+        <v>0.9388935906796291</v>
       </c>
       <c r="AM60" t="n">
-        <v>0.0004800875104764872</v>
+        <v>0.0004800875617407061</v>
       </c>
       <c r="AN60" t="inlineStr"/>
     </row>
@@ -6823,43 +6823,43 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G61" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J61" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4963841461331371</v>
+        <v>0.4963830729515357</v>
       </c>
       <c r="L61" t="n">
-        <v>0.5417894463426931</v>
+        <v>0.5417895370374243</v>
       </c>
       <c r="M61" t="n">
-        <v>0.1204125434549804</v>
+        <v>0.1204127566586757</v>
       </c>
       <c r="N61" t="n">
-        <v>0.005130341714084428</v>
+        <v>0.005130306768387163</v>
       </c>
       <c r="O61" t="n">
-        <v>3.964404756002983</v>
+        <v>3.964396743418508</v>
       </c>
       <c r="P61" t="n">
-        <v>4.303049516459621</v>
+        <v>4.303050191774812</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.973359555994064</v>
+        <v>0.9733613948134049</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01163685650571532</v>
+        <v>0.01163645489005226</v>
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
@@ -6871,38 +6871,38 @@
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="n">
-        <v>0.9512193711693016</v>
+        <v>0.9512231828236286</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.0246150143285852</v>
+        <v>0.02461405261722705</v>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
-        <v>0.1004408317049967</v>
+        <v>0.1004300134131567</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.005141370487281874</v>
+        <v>0.005141401341267187</v>
       </c>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="n">
-        <v>0.6638897331901619</v>
+        <v>0.6638862390014421</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.005874038839727621</v>
+        <v>0.00587406938369248</v>
       </c>
       <c r="AH61" t="inlineStr"/>
       <c r="AI61" t="n">
-        <v>0.9015481007833585</v>
+        <v>0.9015494061808701</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.002508118635099341</v>
+        <v>0.002508102011556329</v>
       </c>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="n">
-        <v>0.3338899037005356</v>
+        <v>0.3338870620650272</v>
       </c>
       <c r="AM61" t="n">
-        <v>0.002223323641177635</v>
+        <v>0.002223328366631026</v>
       </c>
       <c r="AN61" t="inlineStr"/>
     </row>
@@ -6929,43 +6929,43 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G62" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I62" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K62" t="n">
-        <v>0.5450073111588626</v>
+        <v>0.5450073111550779</v>
       </c>
       <c r="L62" t="n">
-        <v>0.5421749813290176</v>
+        <v>0.5421749813680846</v>
       </c>
       <c r="M62" t="n">
-        <v>0.7880158723096803</v>
+        <v>0.7880158775281606</v>
       </c>
       <c r="N62" t="n">
-        <v>0.2493507376162362</v>
+        <v>0.2493507411125835</v>
       </c>
       <c r="O62" t="n">
-        <v>4.327041501018048</v>
+        <v>4.32704150098985</v>
       </c>
       <c r="P62" t="n">
-        <v>4.30593748337531</v>
+        <v>4.3059374836664</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.986584021353077</v>
+        <v>0.9865840219327927</v>
       </c>
       <c r="R62" t="n">
-        <v>0.007638866953173154</v>
+        <v>0.00763886678840765</v>
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
@@ -6977,38 +6977,38 @@
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="n">
-        <v>0.9818252866463979</v>
+        <v>0.9818252878491284</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.01406161214788852</v>
+        <v>0.01406161168331102</v>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
-        <v>-0.4102785677597443</v>
+        <v>-0.4102785680864165</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.003953394804954631</v>
+        <v>0.003953394798998515</v>
       </c>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="n">
-        <v>0.6031113765094324</v>
+        <v>0.603111373042058</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.0084348505995414</v>
+        <v>0.008434850633832876</v>
       </c>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="n">
-        <v>0.9795773164699276</v>
+        <v>0.9795773167488525</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.002121593282107927</v>
+        <v>0.00212159326763049</v>
       </c>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>0.8627701935028548</v>
+        <v>0.862770193223754</v>
       </c>
       <c r="AM62" t="n">
-        <v>0.001855839523183129</v>
+        <v>0.001855839526293849</v>
       </c>
       <c r="AN62" t="inlineStr"/>
     </row>
@@ -7035,43 +7035,43 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G63" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I63" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J63" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K63" t="n">
-        <v>0.5050331926392826</v>
+        <v>0.5050340113780182</v>
       </c>
       <c r="L63" t="n">
-        <v>0.5420051715105731</v>
+        <v>0.5420052601032673</v>
       </c>
       <c r="M63" t="n">
-        <v>0.3926051668648807</v>
+        <v>0.3926433997715765</v>
       </c>
       <c r="N63" t="n">
-        <v>0.0671576182304284</v>
+        <v>0.06717111055906759</v>
       </c>
       <c r="O63" t="n">
-        <v>4.028967021104511</v>
+        <v>4.028973131483649</v>
       </c>
       <c r="P63" t="n">
-        <v>4.304657828588299</v>
+        <v>4.304658489088633</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.993146461752922</v>
+        <v>0.9931472128780439</v>
       </c>
       <c r="R63" t="n">
-        <v>0.00605496589397783</v>
+        <v>0.006054634082645126</v>
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
@@ -7083,38 +7083,38 @@
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="n">
-        <v>0.9866640677774584</v>
+        <v>0.986665716515155</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.01271602691257459</v>
+        <v>0.01271524083893458</v>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
-        <v>0.6671581015502692</v>
+        <v>0.6671481058506361</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.002519205200372174</v>
+        <v>0.002519243014599644</v>
       </c>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="n">
-        <v>0.9894548928536367</v>
+        <v>0.9894549181799384</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.001142062695144151</v>
+        <v>0.001142061324973855</v>
       </c>
       <c r="AH63" t="inlineStr"/>
       <c r="AI63" t="n">
-        <v>0.8586571035976174</v>
+        <v>0.8586608090783918</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0.003352884622953562</v>
+        <v>0.003352840677748875</v>
       </c>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="n">
-        <v>0.3617325033325532</v>
+        <v>0.3617307120625557</v>
       </c>
       <c r="AM63" t="n">
-        <v>0.00184498716418021</v>
+        <v>0.001844989747448664</v>
       </c>
       <c r="AN63" t="inlineStr"/>
     </row>
@@ -7141,43 +7141,43 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G64" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I64" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K64" t="n">
-        <v>0.4864960531109634</v>
+        <v>0.4864936899293685</v>
       </c>
       <c r="L64" t="n">
-        <v>0.5426643651982641</v>
+        <v>0.542664366854681</v>
       </c>
       <c r="M64" t="n">
-        <v>0.4253990809188536</v>
+        <v>0.4254003432228124</v>
       </c>
       <c r="N64" t="n">
-        <v>0.03264464345778306</v>
+        <v>0.03264474303030896</v>
       </c>
       <c r="O64" t="n">
-        <v>3.890560537641748</v>
+        <v>3.890542885099665</v>
       </c>
       <c r="P64" t="n">
-        <v>4.309571782714835</v>
+        <v>4.309571794104172</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.9685932789461209</v>
+        <v>0.9685933944629944</v>
       </c>
       <c r="R64" t="n">
-        <v>0.01187386013204562</v>
+        <v>0.01187383829599813</v>
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
@@ -7189,38 +7189,38 @@
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="n">
-        <v>0.9475401721383335</v>
+        <v>0.9475404098171757</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.02418921373398097</v>
+        <v>0.02418915893841174</v>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
-        <v>0.2368240865817285</v>
+        <v>0.236823528133152</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.004717844749262385</v>
+        <v>0.004717846498154631</v>
       </c>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="n">
-        <v>0.4041267257454908</v>
+        <v>0.404126442103905</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.009393223440010902</v>
+        <v>0.00939322566906752</v>
       </c>
       <c r="AH64" t="inlineStr"/>
       <c r="AI64" t="n">
-        <v>0.9747398387252907</v>
+        <v>0.9747398485736918</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.002293776722581101</v>
+        <v>0.002293776275241965</v>
       </c>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="n">
-        <v>0.8406716469126118</v>
+        <v>0.8406715762719165</v>
       </c>
       <c r="AM64" t="n">
-        <v>0.002256267322241268</v>
+        <v>0.00225626782507433</v>
       </c>
       <c r="AN64" t="inlineStr"/>
     </row>
@@ -7247,43 +7247,43 @@
         <v>53.51961950059453</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7472990942554644</v>
+        <v>0.7472990942424869</v>
       </c>
       <c r="G65" t="n">
         <v>0.05931662452435613</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1189424488256474</v>
+        <v>0.1189424488653025</v>
       </c>
       <c r="I65" t="n">
-        <v>0.05728789975449577</v>
+        <v>0.05728789972030301</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01715393264003622</v>
+        <v>0.01715393264755156</v>
       </c>
       <c r="K65" t="n">
-        <v>0.4897404220545651</v>
+        <v>0.4897403046305538</v>
       </c>
       <c r="L65" t="n">
-        <v>0.5433803602594763</v>
+        <v>0.5433803574132221</v>
       </c>
       <c r="M65" t="n">
-        <v>0.259123631540967</v>
+        <v>0.2591234306321728</v>
       </c>
       <c r="N65" t="n">
-        <v>0.02483611279084425</v>
+        <v>0.02483607741704125</v>
       </c>
       <c r="O65" t="n">
-        <v>3.914793425256979</v>
+        <v>3.914792548262575</v>
       </c>
       <c r="P65" t="n">
-        <v>4.314898845667633</v>
+        <v>4.314898824411944</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.9778646832476886</v>
+        <v>0.9778646459061928</v>
       </c>
       <c r="R65" t="n">
-        <v>0.01071656634449585</v>
+        <v>0.01071657538357885</v>
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
@@ -7295,38 +7295,38 @@
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="n">
-        <v>0.9629137010605526</v>
+        <v>0.9629136259727262</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.02201618928625144</v>
+        <v>0.02201621157389068</v>
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
-        <v>0.6561159865697148</v>
+        <v>0.6561160874527104</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.003970902243478991</v>
+        <v>0.003970901648795149</v>
       </c>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="n">
-        <v>0.6662999847298431</v>
+        <v>0.6663000393798069</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.008130799338731775</v>
+        <v>0.008130798674700302</v>
       </c>
       <c r="AH65" t="inlineStr"/>
       <c r="AI65" t="n">
-        <v>0.9346055395823537</v>
+        <v>0.934605502938663</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.002206343502215114</v>
+        <v>0.002206344123840584</v>
       </c>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="n">
-        <v>0.576669543402839</v>
+        <v>0.5766695313334098</v>
       </c>
       <c r="AM65" t="n">
-        <v>0.001859255976223689</v>
+        <v>0.001859256002949987</v>
       </c>
       <c r="AN65" t="inlineStr"/>
     </row>
@@ -7353,43 +7353,43 @@
         <v>54.48315911730546</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6806747812354861</v>
+        <v>0.6806747812675474</v>
       </c>
       <c r="G66" t="n">
         <v>0.05826760463298514</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1324809677416384</v>
+        <v>0.1324809676982178</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09760455450858101</v>
+        <v>0.09760455450536588</v>
       </c>
       <c r="J66" t="n">
-        <v>0.03097209188130944</v>
+        <v>0.0309720918958838</v>
       </c>
       <c r="K66" t="n">
-        <v>0.5058386519967449</v>
+        <v>0.5058386592092137</v>
       </c>
       <c r="L66" t="n">
-        <v>0.5430289830034628</v>
+        <v>0.543028979399121</v>
       </c>
       <c r="M66" t="n">
-        <v>0.3699568244870225</v>
+        <v>0.3699566287385427</v>
       </c>
       <c r="N66" t="n">
-        <v>0.0271495297562646</v>
+        <v>0.02714949926789888</v>
       </c>
       <c r="O66" t="n">
-        <v>4.034978182807103</v>
+        <v>4.034978236632926</v>
       </c>
       <c r="P66" t="n">
-        <v>4.31229429669068</v>
+        <v>4.312294269838946</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.9753032211695043</v>
+        <v>0.9753031233382525</v>
       </c>
       <c r="R66" t="n">
-        <v>0.01062952113692031</v>
+        <v>0.01062954219050808</v>
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
@@ -7401,38 +7401,38 @@
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="n">
-        <v>0.9586240957633888</v>
+        <v>0.9586238897194366</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.02141186885153401</v>
+        <v>0.02141192216600077</v>
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
-        <v>0.5091594646722968</v>
+        <v>0.5091598827255241</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.00431881754532872</v>
+        <v>0.0043188157132601</v>
       </c>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="n">
-        <v>0.6771872170638409</v>
+        <v>0.6771873310631564</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.008680646487265974</v>
+        <v>0.008680644951292279</v>
       </c>
       <c r="AH66" t="inlineStr"/>
       <c r="AI66" t="n">
-        <v>0.9538088809542411</v>
+        <v>0.9538088926931155</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0.002989116143492937</v>
+        <v>0.002989115763400346</v>
       </c>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="n">
-        <v>0.8562093144269013</v>
+        <v>0.8562093337180657</v>
       </c>
       <c r="AM66" t="n">
-        <v>0.002099061260383179</v>
+        <v>0.002099061121541857</v>
       </c>
       <c r="AN66" t="inlineStr"/>
     </row>
@@ -7459,25 +7459,25 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G67" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.5593926976864663</v>
+        <v>0.5593936874221827</v>
       </c>
       <c r="L67" t="n">
-        <v>0.5512002886797739</v>
+        <v>0.5512003086498466</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -7486,61 +7486,61 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>4.434191938319421</v>
+        <v>4.434199308462619</v>
       </c>
       <c r="P67" t="n">
-        <v>4.373176826468922</v>
+        <v>4.373176975311817</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.9016017879882344</v>
+        <v>0.9015940507738633</v>
       </c>
       <c r="R67" t="n">
-        <v>0.02268848376272927</v>
+        <v>0.02268937576273409</v>
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="n">
-        <v>0.7840801696326886</v>
+        <v>0.7840879146484121</v>
       </c>
       <c r="X67" t="n">
-        <v>0.0008077150173946896</v>
+        <v>0.0008077005309494228</v>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>0.7336310103394725</v>
+        <v>0.7336079160784745</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.05318033173531437</v>
+        <v>0.05318263705126365</v>
       </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
-        <v>0.7404052560833239</v>
+        <v>0.7404147223985609</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.002791319834743385</v>
+        <v>0.002791268940503431</v>
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="n">
-        <v>0.6497400710206538</v>
+        <v>0.6497408037175836</v>
       </c>
       <c r="AG67" t="n">
-        <v>0.01298112300062097</v>
+        <v>0.01298110948995891</v>
       </c>
       <c r="AH67" t="inlineStr"/>
       <c r="AI67" t="n">
-        <v>0.8056547580162973</v>
+        <v>0.8056586602864831</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0.009129790771392391</v>
+        <v>0.009129699073991047</v>
       </c>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="n">
-        <v>0.6647114106311883</v>
+        <v>0.6647224204204034</v>
       </c>
       <c r="AM67" t="n">
-        <v>0.000154534243857436</v>
+        <v>0.0001545317177784986</v>
       </c>
       <c r="AN67" t="inlineStr"/>
     </row>
@@ -7567,25 +7567,25 @@
         <v>54.52272727272727</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6524665781462966</v>
+        <v>0.652466577913562</v>
       </c>
       <c r="G68" t="n">
         <v>0.0582253187505376</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1475232058308549</v>
+        <v>0.147523206464546</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1417848972723109</v>
+        <v>0.1417848968713543</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.5709449617807177</v>
+        <v>0.5709449616839343</v>
       </c>
       <c r="L68" t="n">
-        <v>0.5513570683522704</v>
+        <v>0.551357068374749</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -7594,61 +7594,61 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>4.520199018951153</v>
+        <v>4.520199018230743</v>
       </c>
       <c r="P68" t="n">
-        <v>4.374341569472314</v>
+        <v>4.374341569639728</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.786817436540392</v>
+        <v>0.7868174318899132</v>
       </c>
       <c r="R68" t="n">
-        <v>0.0308005048001323</v>
+        <v>0.03080050513236027</v>
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
-        <v>0.5373321545204689</v>
+        <v>0.5373321622734338</v>
       </c>
       <c r="X68" t="n">
-        <v>0.001112370878778731</v>
+        <v>0.001112370869458684</v>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>0.4243442330989456</v>
+        <v>0.4243442199372209</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.07380413240840066</v>
+        <v>0.07380413322938724</v>
       </c>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
-        <v>0.5179732162829653</v>
+        <v>0.5179732250987092</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.003705276902267366</v>
+        <v>0.00370527686838463</v>
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="n">
-        <v>0.7400229691060459</v>
+        <v>0.7400229682911407</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.007497890498027606</v>
+        <v>0.007497890537400424</v>
       </c>
       <c r="AH68" t="inlineStr"/>
       <c r="AI68" t="n">
-        <v>0.6598640180531672</v>
+        <v>0.6598640138207021</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.01315153447838448</v>
+        <v>0.013151534528061</v>
       </c>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="n">
-        <v>0.07980018132295041</v>
+        <v>0.07980020476623151</v>
       </c>
       <c r="AM68" t="n">
-        <v>0.0008525508457932999</v>
+        <v>0.000852550836971294</v>
       </c>
       <c r="AN68" t="inlineStr"/>
     </row>
@@ -7675,43 +7675,43 @@
         <v>51.72972972972973</v>
       </c>
       <c r="F69" t="n">
-        <v>0.387003570840844</v>
+        <v>0.3870035708733858</v>
       </c>
       <c r="G69" t="n">
         <v>0.06136902688626825</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3121616657195941</v>
+        <v>0.3121616658061397</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1933504308693656</v>
+        <v>0.1933504307114432</v>
       </c>
       <c r="J69" t="n">
-        <v>0.04611530568392795</v>
+        <v>0.04611530572276303</v>
       </c>
       <c r="K69" t="n">
-        <v>0.551076722083462</v>
+        <v>0.5510767095590137</v>
       </c>
       <c r="L69" t="n">
-        <v>0.5516659031529068</v>
+        <v>0.5516658946205685</v>
       </c>
       <c r="M69" t="n">
-        <v>0.2531780513365061</v>
+        <v>0.2531718269277423</v>
       </c>
       <c r="N69" t="n">
-        <v>0.03555068735324171</v>
+        <v>0.03554871987744262</v>
       </c>
       <c r="O69" t="n">
-        <v>4.372256927767693</v>
+        <v>4.372256834474767</v>
       </c>
       <c r="P69" t="n">
-        <v>4.376645601003035</v>
+        <v>4.376645537447736</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.9706578517667198</v>
+        <v>0.9706577415014696</v>
       </c>
       <c r="R69" t="n">
-        <v>0.01003950984602801</v>
+        <v>0.0100395287110205</v>
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
@@ -7721,38 +7721,38 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
-        <v>0.9481006358183436</v>
+        <v>0.9481000756425069</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.01262099929794639</v>
+        <v>0.01262106741489944</v>
       </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
-        <v>0.6860762449492538</v>
+        <v>0.6860783193368083</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.003558094502644299</v>
+        <v>0.003558082746797492</v>
       </c>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="n">
-        <v>0.8522691986763569</v>
+        <v>0.8522687786331039</v>
       </c>
       <c r="AG69" t="n">
-        <v>0.01556430384638484</v>
+        <v>0.0155643259765007</v>
       </c>
       <c r="AH69" t="inlineStr"/>
       <c r="AI69" t="n">
-        <v>0.9214912320744859</v>
+        <v>0.9214917198876655</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.008501533371077206</v>
+        <v>0.008501506954164876</v>
       </c>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="n">
-        <v>0.5404852662213813</v>
+        <v>0.5404847814323475</v>
       </c>
       <c r="AM69" t="n">
-        <v>0.004181567420456924</v>
+        <v>0.004181569630897232</v>
       </c>
       <c r="AN69" t="inlineStr"/>
     </row>
@@ -7779,25 +7779,25 @@
         <v>33.0828025477707</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3260336956980185</v>
+        <v>0.3260336958414495</v>
       </c>
       <c r="G70" t="n">
         <v>0.09595931813875594</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3161491466910983</v>
+        <v>0.31614914647049</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2279586239396759</v>
+        <v>0.2279586239311767</v>
       </c>
       <c r="J70" t="n">
-        <v>0.03389921553245138</v>
+        <v>0.03389921561812766</v>
       </c>
       <c r="K70" t="n">
-        <v>0.5503708566416453</v>
+        <v>0.5503708593126074</v>
       </c>
       <c r="L70" t="n">
-        <v>0.5571388279955621</v>
+        <v>0.5571388295650735</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -7806,16 +7806,16 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>4.366998961487805</v>
+        <v>4.36699898138397</v>
       </c>
       <c r="P70" t="n">
-        <v>4.417406803997117</v>
+        <v>4.417406815686455</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.9577440876459358</v>
+        <v>0.9577440933429551</v>
       </c>
       <c r="R70" t="n">
-        <v>0.01008780000550043</v>
+        <v>0.01008779932543208</v>
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
@@ -7825,38 +7825,38 @@
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
-        <v>0.8854756377355057</v>
+        <v>0.8854756784958662</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.01511082379202798</v>
+        <v>0.01511082110804725</v>
       </c>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
-        <v>0.9253918248346422</v>
+        <v>0.9253918350395194</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.003168426386055833</v>
+        <v>0.003168426169367762</v>
       </c>
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="n">
-        <v>0.9431770989989549</v>
+        <v>0.943177101382609</v>
       </c>
       <c r="AG70" t="n">
-        <v>0.01082413293580442</v>
+        <v>0.01082413269763145</v>
       </c>
       <c r="AH70" t="inlineStr"/>
       <c r="AI70" t="n">
-        <v>0.8105629049318468</v>
+        <v>0.8105628816400188</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.0121904795837367</v>
+        <v>0.0121904803383382</v>
       </c>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="n">
-        <v>0.7706955991884092</v>
+        <v>0.7706955697723902</v>
       </c>
       <c r="AM70" t="n">
-        <v>0.002161706969927251</v>
+        <v>0.002161707118333637</v>
       </c>
       <c r="AN70" t="inlineStr"/>
     </row>
@@ -7883,43 +7883,43 @@
         <v>47.07964601769911</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3936990724378037</v>
+        <v>0.3936990724969831</v>
       </c>
       <c r="G71" t="n">
         <v>0.06743048096431555</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2058669949880412</v>
+        <v>0.2058669949713333</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3043928180016056</v>
+        <v>0.3043928180135104</v>
       </c>
       <c r="J71" t="n">
-        <v>0.02861063360823382</v>
+        <v>0.02861063355385755</v>
       </c>
       <c r="K71" t="n">
-        <v>0.5607074877638749</v>
+        <v>0.5607074822876876</v>
       </c>
       <c r="L71" t="n">
-        <v>0.5617693768775038</v>
+        <v>0.5617693758458691</v>
       </c>
       <c r="M71" t="n">
-        <v>0.0977182329233427</v>
+        <v>0.09771815779603388</v>
       </c>
       <c r="N71" t="n">
-        <v>0.005487302083923218</v>
+        <v>0.005487295454850088</v>
       </c>
       <c r="O71" t="n">
-        <v>4.443982390835941</v>
+        <v>4.443982350059031</v>
       </c>
       <c r="P71" t="n">
-        <v>4.451889222000164</v>
+        <v>4.451889214318278</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.9608701726475205</v>
+        <v>0.9608701797015489</v>
       </c>
       <c r="R71" t="n">
-        <v>0.01080088054605496</v>
+        <v>0.01080087957300119</v>
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
@@ -7929,38 +7929,38 @@
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>0.9410713149500289</v>
+        <v>0.9410713291893859</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.01444751125149274</v>
+        <v>0.01444750951012523</v>
       </c>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
-        <v>0.7637962374064738</v>
+        <v>0.7637962200957924</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.004305109981599602</v>
+        <v>0.004305110139354046</v>
       </c>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="n">
-        <v>0.9059491140440447</v>
+        <v>0.9059491073243143</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.009781060425771194</v>
+        <v>0.009781060766473639</v>
       </c>
       <c r="AH71" t="inlineStr"/>
       <c r="AI71" t="n">
-        <v>0.8454917558703836</v>
+        <v>0.8454917935144023</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.01611066546487351</v>
+        <v>0.01611066350378215</v>
       </c>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="n">
-        <v>0.9470678978140651</v>
+        <v>0.9470678727844656</v>
       </c>
       <c r="AM71" t="n">
-        <v>0.0008988129735431207</v>
+        <v>0.0008988131873175028</v>
       </c>
       <c r="AN71" t="inlineStr"/>
     </row>
@@ -7987,43 +7987,43 @@
         <v>37.36805555555556</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2796444532400447</v>
+        <v>0.279644453194911</v>
       </c>
       <c r="G72" t="n">
         <v>0.08495500039822655</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2106458171229023</v>
+        <v>0.2106458171994461</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3902452407206423</v>
+        <v>0.3902452407095023</v>
       </c>
       <c r="J72" t="n">
-        <v>0.03450948851818413</v>
+        <v>0.03450948849791399</v>
       </c>
       <c r="K72" t="n">
-        <v>0.567038931825131</v>
+        <v>0.5670389503687139</v>
       </c>
       <c r="L72" t="n">
-        <v>0.5683049613018839</v>
+        <v>0.5683049676004553</v>
       </c>
       <c r="M72" t="n">
-        <v>0.02889630540394161</v>
+        <v>0.02889572064417023</v>
       </c>
       <c r="N72" t="n">
-        <v>0.0007371817192045827</v>
+        <v>0.0007371586375843431</v>
       </c>
       <c r="O72" t="n">
-        <v>4.491122394156444</v>
+        <v>4.491122532204955</v>
       </c>
       <c r="P72" t="n">
-        <v>4.500547146409128</v>
+        <v>4.50054719329824</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.9585553851690581</v>
+        <v>0.9585554127173761</v>
       </c>
       <c r="R72" t="n">
-        <v>0.01162555989621234</v>
+        <v>0.01162555603131311</v>
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
@@ -8033,38 +8033,38 @@
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>0.857734449441842</v>
+        <v>0.8577345835866719</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.01575312450917711</v>
+        <v>0.01575311708033758</v>
       </c>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
-        <v>0.848894879494377</v>
+        <v>0.8488944838765582</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.004281760518148211</v>
+        <v>0.004281766123317786</v>
       </c>
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="n">
-        <v>0.9507772774019115</v>
+        <v>0.9507773529027196</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.006952689086984144</v>
+        <v>0.006952683758246179</v>
       </c>
       <c r="AH72" t="inlineStr"/>
       <c r="AI72" t="n">
-        <v>0.8647401787236401</v>
+        <v>0.8647402500404682</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.01894479007669282</v>
+        <v>0.01894478508464122</v>
       </c>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="n">
-        <v>0.9024114055544867</v>
+        <v>0.9024114060426639</v>
       </c>
       <c r="AM72" t="n">
-        <v>0.001424378101301547</v>
+        <v>0.001424378095507896</v>
       </c>
       <c r="AN72" t="inlineStr"/>
     </row>
@@ -8091,25 +8091,25 @@
         <v>80.48333333333333</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4426967929782777</v>
+        <v>0.4426967930157429</v>
       </c>
       <c r="G73" t="n">
         <v>0.03944423078819433</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3881444762932012</v>
+        <v>0.388144476200794</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1098624187784432</v>
+        <v>0.1098624188419678</v>
       </c>
       <c r="J73" t="n">
-        <v>0.01985208116188355</v>
+        <v>0.01985208115330091</v>
       </c>
       <c r="K73" t="n">
-        <v>0.559424568274783</v>
+        <v>0.5594245676823701</v>
       </c>
       <c r="L73" t="n">
-        <v>0.5542545518429339</v>
+        <v>0.5542545526095516</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -8118,16 +8118,16 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4.434429264975574</v>
+        <v>4.434429260564131</v>
       </c>
       <c r="P73" t="n">
-        <v>4.395925882920462</v>
+        <v>4.395925888630539</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.9946561456582593</v>
+        <v>0.9946561472613953</v>
       </c>
       <c r="R73" t="n">
-        <v>0.004861602442636507</v>
+        <v>0.004861601713124656</v>
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
@@ -8137,38 +8137,38 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
-        <v>0.9546487435590537</v>
+        <v>0.9546487638652917</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.007311845823971833</v>
+        <v>0.007311844189155673</v>
       </c>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
-        <v>0.3039560404521018</v>
+        <v>0.3039562521518108</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.001667763096576236</v>
+        <v>0.001667762842953613</v>
       </c>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="n">
-        <v>0.9721216431086848</v>
+        <v>0.9721216562424473</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.005602055005699502</v>
+        <v>0.005602053681119673</v>
       </c>
       <c r="AH73" t="inlineStr"/>
       <c r="AI73" t="n">
-        <v>0.8216020872551331</v>
+        <v>0.8216020629602244</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.005164276569283708</v>
+        <v>0.005164276930194954</v>
       </c>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="n">
-        <v>0.2548639667643721</v>
+        <v>0.2548638910378744</v>
       </c>
       <c r="AM73" t="n">
-        <v>0.001969415060487452</v>
+        <v>0.00196941516206369</v>
       </c>
       <c r="AN73" t="inlineStr"/>
     </row>
@@ -8195,25 +8195,25 @@
         <v>59.11538461538462</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2579745442485045</v>
+        <v>0.2579745444344787</v>
       </c>
       <c r="G74" t="n">
         <v>0.05370181037064575</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3841123147856094</v>
+        <v>0.384112314707</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2682526027331976</v>
+        <v>0.2682526026085332</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03595872786204279</v>
+        <v>0.0359587278793424</v>
       </c>
       <c r="K74" t="n">
-        <v>0.5539023547937509</v>
+        <v>0.5539023629027617</v>
       </c>
       <c r="L74" t="n">
-        <v>0.5600553730725266</v>
+        <v>0.5600553757714195</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -8222,16 +8222,16 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>4.393303571076886</v>
+        <v>4.393303631473435</v>
       </c>
       <c r="P74" t="n">
-        <v>4.439125499388008</v>
+        <v>4.439125519486911</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.9676665578531954</v>
+        <v>0.9676665595887798</v>
       </c>
       <c r="R74" t="n">
-        <v>0.008518072814554984</v>
+        <v>0.008518072585318169</v>
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
@@ -8241,38 +8241,38 @@
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="n">
-        <v>0.7906503234297318</v>
+        <v>0.7906503546038769</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.01093148264024884</v>
+        <v>0.01093148183620589</v>
       </c>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
-        <v>0.8362112174981582</v>
+        <v>0.8362111703589511</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.00134489853037209</v>
+        <v>0.00134489872390624</v>
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="n">
-        <v>0.8820519164274934</v>
+        <v>0.8820519177514337</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.01352325050198177</v>
+        <v>0.01352325042124536</v>
       </c>
       <c r="AH74" t="inlineStr"/>
       <c r="AI74" t="n">
-        <v>0.8658459153406076</v>
+        <v>0.8658459161014911</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.007405717521567467</v>
+        <v>0.007405717495382685</v>
       </c>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="n">
-        <v>0.7302212470244285</v>
+        <v>0.7302212396539235</v>
       </c>
       <c r="AM74" t="n">
-        <v>0.001938762866016105</v>
+        <v>0.001938762892607272</v>
       </c>
       <c r="AN74" t="inlineStr"/>
     </row>
@@ -8299,25 +8299,25 @@
         <v>38.49019607843137</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3797999037751007</v>
+        <v>0.379799903884584</v>
       </c>
       <c r="G75" t="n">
         <v>0.0824782281735924</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2705342292388105</v>
+        <v>0.2705342288932795</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2132258416518971</v>
+        <v>0.2132258419102607</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05396179716059933</v>
+        <v>0.05396179713828334</v>
       </c>
       <c r="K75" t="n">
-        <v>0.5371232694513625</v>
+        <v>0.5371232677635055</v>
       </c>
       <c r="L75" t="n">
-        <v>0.5502296926302926</v>
+        <v>0.5502296938253242</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -8326,16 +8326,16 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>4.268291721388134</v>
+        <v>4.268291708808715</v>
       </c>
       <c r="P75" t="n">
-        <v>4.365943769511382</v>
+        <v>4.365943778412547</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.9676649476119463</v>
+        <v>0.9676649506922748</v>
       </c>
       <c r="R75" t="n">
-        <v>0.007101517478086479</v>
+        <v>0.007101517139413083</v>
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
@@ -8345,38 +8345,38 @@
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>0.8871496550952456</v>
+        <v>0.8871496705864591</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.01200392420158328</v>
+        <v>0.01200392338369892</v>
       </c>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
-        <v>0.8451492726607359</v>
+        <v>0.8451492312134663</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.002374419361649531</v>
+        <v>0.002374419679417469</v>
       </c>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="n">
-        <v>0.9222494765015478</v>
+        <v>0.9222494813337405</v>
       </c>
       <c r="AG75" t="n">
-        <v>0.007318194732568614</v>
+        <v>0.007318194489686056</v>
       </c>
       <c r="AH75" t="inlineStr"/>
       <c r="AI75" t="n">
-        <v>0.8654124041024618</v>
+        <v>0.8654124112991015</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.006958858806779673</v>
+        <v>0.006958858634519037</v>
       </c>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="n">
-        <v>0.9882558302454952</v>
+        <v>0.9882558295223647</v>
       </c>
       <c r="AM75" t="n">
-        <v>0.0006663324087990279</v>
+        <v>0.000666332429856609</v>
       </c>
       <c r="AN75" t="inlineStr"/>
     </row>
@@ -8403,43 +8403,43 @@
         <v>67.76923076923077</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3107335005383793</v>
+        <v>0.3107335004737291</v>
       </c>
       <c r="G76" t="n">
         <v>0.04684431472172675</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5076173756922413</v>
+        <v>0.5076173757282579</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1034441405229936</v>
+        <v>0.1034441405920671</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03136066852465918</v>
+        <v>0.03136066848421915</v>
       </c>
       <c r="K76" t="n">
-        <v>0.5601812859072123</v>
+        <v>0.5601812787559608</v>
       </c>
       <c r="L76" t="n">
-        <v>0.5542270421319764</v>
+        <v>0.5542270416509723</v>
       </c>
       <c r="M76" t="n">
-        <v>0.0317967981228201</v>
+        <v>0.03179662817237572</v>
       </c>
       <c r="N76" t="n">
-        <v>0.001097192311935573</v>
+        <v>0.001097182540456927</v>
       </c>
       <c r="O76" t="n">
-        <v>4.440064137367118</v>
+        <v>4.440064084116293</v>
       </c>
       <c r="P76" t="n">
-        <v>4.395720827941094</v>
+        <v>4.395720824360647</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.9927200006677219</v>
+        <v>0.9927200042422102</v>
       </c>
       <c r="R76" t="n">
-        <v>0.005353969758232399</v>
+        <v>0.005353968443779705</v>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
@@ -8449,38 +8449,38 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="n">
-        <v>0.914825167941657</v>
+        <v>0.9148251543053921</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.008303409123960276</v>
+        <v>0.008303409784272166</v>
       </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
-        <v>0.9190752618506144</v>
+        <v>0.9190752750803008</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.0007843072954074451</v>
+        <v>0.00078430723129763</v>
       </c>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="n">
-        <v>0.9596394167327328</v>
+        <v>0.9596394620684904</v>
       </c>
       <c r="AG76" t="n">
-        <v>0.008480847656170387</v>
+        <v>0.008480842895909373</v>
       </c>
       <c r="AH76" t="inlineStr"/>
       <c r="AI76" t="n">
-        <v>0.9882871061576899</v>
+        <v>0.9882871184286371</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.0009095992855558673</v>
+        <v>0.0009095988097338191</v>
       </c>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="n">
-        <v>0.6886002130920674</v>
+        <v>0.6886000978665626</v>
       </c>
       <c r="AM76" t="n">
-        <v>0.001005520770240395</v>
+        <v>0.00100552095282308</v>
       </c>
       <c r="AN76" t="inlineStr"/>
     </row>
@@ -8507,43 +8507,43 @@
         <v>84.83333333333333</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2190992506065154</v>
+        <v>0.2190992505888929</v>
       </c>
       <c r="G77" t="n">
         <v>0.03742164842361306</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4560940070375605</v>
+        <v>0.4560940072232207</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2593330805653106</v>
+        <v>0.2593330804892675</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02805201336700053</v>
+        <v>0.02805201327500588</v>
       </c>
       <c r="K77" t="n">
-        <v>0.5411801492891922</v>
+        <v>0.5411804105489888</v>
       </c>
       <c r="L77" t="n">
-        <v>0.5509761206511651</v>
+        <v>0.5509764276924791</v>
       </c>
       <c r="M77" t="n">
-        <v>0.07522527212345076</v>
+        <v>0.07522880219273886</v>
       </c>
       <c r="N77" t="n">
-        <v>0.004190561813070513</v>
+        <v>0.004190895804240604</v>
       </c>
       <c r="O77" t="n">
-        <v>4.29852478003157</v>
+        <v>4.298526726860364</v>
       </c>
       <c r="P77" t="n">
-        <v>4.371503445291739</v>
+        <v>4.371505732388345</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.9763471268795081</v>
+        <v>0.9763476993020924</v>
       </c>
       <c r="R77" t="n">
-        <v>0.009222528314083349</v>
+        <v>0.009222416717846469</v>
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
@@ -8553,38 +8553,38 @@
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>0.8168364612673467</v>
+        <v>0.8168376715949566</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.007797399915782872</v>
+        <v>0.007797374156474688</v>
       </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
-        <v>-3.599334688359904</v>
+        <v>-3.599428122991661</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.002097262136702771</v>
+        <v>0.002097283439340383</v>
       </c>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="n">
-        <v>0.9033801265902224</v>
+        <v>0.9033848098447131</v>
       </c>
       <c r="AG77" t="n">
-        <v>0.01347479551908767</v>
+        <v>0.01347446895280797</v>
       </c>
       <c r="AH77" t="inlineStr"/>
       <c r="AI77" t="n">
-        <v>0.2022002169169386</v>
+        <v>0.2022055206333802</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.01333865782505892</v>
+        <v>0.01333861351542353</v>
       </c>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="n">
-        <v>0.8856566600326781</v>
+        <v>0.8856560349785257</v>
       </c>
       <c r="AM77" t="n">
-        <v>0.0007663431009781172</v>
+        <v>0.0007663451918387932</v>
       </c>
       <c r="AN77" t="inlineStr"/>
     </row>
@@ -8611,43 +8611,43 @@
         <v>194.7286349979082</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1878797147510616</v>
+        <v>0.1878797146293589</v>
       </c>
       <c r="G78" t="n">
         <v>0.01630270337301587</v>
       </c>
       <c r="H78" t="n">
-        <v>0.486383629371598</v>
+        <v>0.48638362926571</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2989072313345766</v>
+        <v>0.2989072315377535</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01052672116974796</v>
+        <v>0.01052672119416169</v>
       </c>
       <c r="K78" t="n">
-        <v>0.5620493770299488</v>
+        <v>0.5620497789278945</v>
       </c>
       <c r="L78" t="n">
-        <v>0.5617286666631309</v>
+        <v>0.5617290183263297</v>
       </c>
       <c r="M78" t="n">
-        <v>0.1609547940455152</v>
+        <v>0.1609647979692039</v>
       </c>
       <c r="N78" t="n">
-        <v>0.01512461808946006</v>
+        <v>0.01512642338148396</v>
       </c>
       <c r="O78" t="n">
-        <v>4.453974155675245</v>
+        <v>4.453977148152306</v>
       </c>
       <c r="P78" t="n">
-        <v>4.451586136153072</v>
+        <v>4.451588754618591</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.9822834841454851</v>
+        <v>0.9822835244431314</v>
       </c>
       <c r="R78" t="n">
-        <v>0.009665427566204674</v>
+        <v>0.009665416575135139</v>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
@@ -8657,38 +8657,38 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="n">
-        <v>0.3422108380902777</v>
+        <v>0.3422091735849652</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.009831994555338473</v>
+        <v>0.009832007001313335</v>
       </c>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
-        <v>0.1436898764006889</v>
+        <v>0.1436660984867771</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.00108238670420082</v>
+        <v>0.00108240173188676</v>
       </c>
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="n">
-        <v>0.8862268703883346</v>
+        <v>0.8862287098674702</v>
       </c>
       <c r="AG78" t="n">
-        <v>0.01387123129782569</v>
+        <v>0.0138711191769753</v>
       </c>
       <c r="AH78" t="inlineStr"/>
       <c r="AI78" t="n">
-        <v>-0.567516176031176</v>
+        <v>-0.567532388218128</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.01318997481721795</v>
+        <v>0.01319004309258864</v>
       </c>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="n">
-        <v>-0.3194356206241811</v>
+        <v>-0.3194217977147817</v>
       </c>
       <c r="AM78" t="n">
-        <v>0.001695959574249089</v>
+        <v>0.001695950667095618</v>
       </c>
       <c r="AN78" t="inlineStr"/>
     </row>
@@ -8709,31 +8709,31 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E79" t="n">
         <v>46.1</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5078749311749362</v>
+        <v>0.507874931382013</v>
       </c>
       <c r="G79" t="n">
         <v>0.06886340942740074</v>
       </c>
       <c r="H79" t="n">
-        <v>0.224536369038535</v>
+        <v>0.2245363687099741</v>
       </c>
       <c r="I79" t="n">
-        <v>0.198725290359128</v>
+        <v>0.1987252904806123</v>
       </c>
       <c r="J79" t="n">
-        <v>3.234988232153624e-17</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.5610550899029443</v>
+        <v>0.5610551126721091</v>
       </c>
       <c r="L79" t="n">
-        <v>0.5628967104249973</v>
+        <v>0.5628959950745231</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -8742,58 +8742,58 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>4.446570697558703</v>
+        <v>4.446570867100849</v>
       </c>
       <c r="P79" t="n">
-        <v>4.460283018455883</v>
+        <v>4.460277692209527</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.982243384299494</v>
+        <v>0.9822434255416213</v>
       </c>
       <c r="R79" t="n">
-        <v>0.01960156198295226</v>
+        <v>0.01960153921930902</v>
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="n">
-        <v>0.9236410073665533</v>
+        <v>0.9236411507157651</v>
       </c>
       <c r="U79" t="n">
-        <v>0.04292100560411066</v>
+        <v>0.04292096531615636</v>
       </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="n">
-        <v>0.6981942464365025</v>
+        <v>0.6981936820282105</v>
       </c>
       <c r="X79" t="n">
-        <v>0.001546153495189306</v>
+        <v>0.001546154940922919</v>
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
-        <v>0.9839019855367579</v>
+        <v>0.9839022337717617</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.009915735517281758</v>
+        <v>0.009915659066030489</v>
       </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
-        <v>0.874554951078451</v>
+        <v>0.8745544885032041</v>
       </c>
       <c r="AD79" t="n">
-        <v>0.002676926985810397</v>
+        <v>0.002676931921354011</v>
       </c>
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="n">
-        <v>0.988746861923252</v>
+        <v>0.9887469092312274</v>
       </c>
       <c r="AG79" t="n">
-        <v>0.003403543318451284</v>
+        <v>0.003403536166916018</v>
       </c>
       <c r="AH79" t="inlineStr"/>
       <c r="AI79" t="n">
-        <v>0.895514667962212</v>
+        <v>0.895514590463224</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.008637824505324111</v>
+        <v>0.008637827698550413</v>
       </c>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
@@ -8817,91 +8817,91 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>21</v>
+        <v>10.7</v>
       </c>
       <c r="E80" t="n">
         <v>45.1</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3936300671811785</v>
+        <v>0.3936300668840204</v>
       </c>
       <c r="G80" t="n">
         <v>0.07039031429275332</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3139495076888332</v>
+        <v>0.3139495080876725</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2220301108372348</v>
+        <v>0.2220301107355537</v>
       </c>
       <c r="J80" t="n">
-        <v>7.592549229303372e-17</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.5736197870707861</v>
+        <v>0.5736197714908451</v>
       </c>
       <c r="L80" t="n">
-        <v>0.5623591394170167</v>
+        <v>0.5623592155216665</v>
       </c>
       <c r="M80" t="n">
-        <v>0.02403048939813879</v>
+        <v>0.02403110530148767</v>
       </c>
       <c r="N80" t="n">
-        <v>0.0004806097879627758</v>
+        <v>0.0004806221060297533</v>
       </c>
       <c r="O80" t="n">
-        <v>4.540108243019789</v>
+        <v>4.540108127060703</v>
       </c>
       <c r="P80" t="n">
-        <v>4.456279041148765</v>
+        <v>4.456279607501397</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.9956478964383095</v>
+        <v>0.9956479238923412</v>
       </c>
       <c r="R80" t="n">
-        <v>0.009118215861198689</v>
+        <v>0.009118187101242693</v>
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="n">
-        <v>0.9860382557411835</v>
+        <v>0.9860383831366248</v>
       </c>
       <c r="U80" t="n">
-        <v>0.01876351616049722</v>
+        <v>0.01876343055543852</v>
       </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="n">
-        <v>0.9831985104016491</v>
+        <v>0.9831985712049945</v>
       </c>
       <c r="X80" t="n">
-        <v>0.0003467263499106868</v>
+        <v>0.0003467257225216393</v>
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>0.9868830554320623</v>
+        <v>0.9868829708437932</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.007353206449812684</v>
+        <v>0.007353230150042257</v>
       </c>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
-        <v>0.9849980239359901</v>
+        <v>0.9849980611554537</v>
       </c>
       <c r="AD80" t="n">
-        <v>0.001019099964008648</v>
+        <v>0.001019098699829269</v>
       </c>
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="n">
-        <v>0.9891682159533975</v>
+        <v>0.9891681393242538</v>
       </c>
       <c r="AG80" t="n">
-        <v>0.00552032468929934</v>
+        <v>0.005520344228008798</v>
       </c>
       <c r="AH80" t="inlineStr"/>
       <c r="AI80" t="n">
-        <v>0.9863948862715952</v>
+        <v>0.9863948439797809</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0.003821348107016561</v>
+        <v>0.00382135404297667</v>
       </c>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
@@ -8925,87 +8925,87 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E81" t="n">
         <v>53.2</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3868686426861032</v>
+        <v>0.386868642759827</v>
       </c>
       <c r="G81" t="n">
         <v>0.05967299200381906</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2367160880230922</v>
+        <v>0.2367160880153139</v>
       </c>
       <c r="I81" t="n">
-        <v>0.3167422772869857</v>
+        <v>0.3167422772210401</v>
       </c>
       <c r="J81" t="n">
-        <v>9.901399624920571e-18</v>
+        <v>1.098340305577317e-17</v>
       </c>
       <c r="K81" t="n">
-        <v>0.58328369577433</v>
+        <v>0.583284052080514</v>
       </c>
       <c r="L81" t="n">
-        <v>0.5692071072888926</v>
+        <v>0.5692505780036889</v>
       </c>
       <c r="M81" t="n">
-        <v>0.3055147787262624</v>
+        <v>0.3054878426312284</v>
       </c>
       <c r="N81" t="n">
-        <v>0.04150523718463438</v>
+        <v>0.04150123924397506</v>
       </c>
       <c r="O81" t="n">
-        <v>4.612023486339785</v>
+        <v>4.612026137412144</v>
       </c>
       <c r="P81" t="n">
-        <v>4.507262339291565</v>
+        <v>4.507585937876893</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.9911866101913818</v>
+        <v>0.9911947579223482</v>
       </c>
       <c r="R81" t="n">
-        <v>0.01275815469570156</v>
+        <v>0.01275225605467839</v>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="n">
-        <v>0.9734507136147083</v>
+        <v>0.9734853775316554</v>
       </c>
       <c r="U81" t="n">
-        <v>0.02441821380386815</v>
+        <v>0.02440226784984344</v>
       </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>0.9774051182660005</v>
+        <v>0.9774017159980765</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.009906747844501801</v>
+        <v>0.009907493681871139</v>
       </c>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
-        <v>0.9752122397824157</v>
+        <v>0.9752043257357101</v>
       </c>
       <c r="AD81" t="n">
-        <v>0.0009560347556745789</v>
+        <v>0.0009561873612312421</v>
       </c>
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="n">
-        <v>0.9660126718879699</v>
+        <v>0.9660108706055687</v>
       </c>
       <c r="AG81" t="n">
-        <v>0.005914545145569408</v>
+        <v>0.005914701878446566</v>
       </c>
       <c r="AH81" t="inlineStr"/>
       <c r="AI81" t="n">
-        <v>0.9644875473940431</v>
+        <v>0.9644836455271523</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0.009141328745771291</v>
+        <v>0.009141830919892931</v>
       </c>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
@@ -9029,87 +9029,87 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>21</v>
+        <v>13.7</v>
       </c>
       <c r="E82" t="n">
         <v>57.4</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3730456209331519</v>
+        <v>0.3730456210575596</v>
       </c>
       <c r="G82" t="n">
         <v>0.05530667551573475</v>
       </c>
       <c r="H82" t="n">
-        <v>0.261472183194441</v>
+        <v>0.2614721829646628</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3101755203566725</v>
+        <v>0.3101755204620427</v>
       </c>
       <c r="J82" t="n">
-        <v>1.336850539002381e-17</v>
+        <v>8.893357462748227e-17</v>
       </c>
       <c r="K82" t="n">
-        <v>0.5822582513598026</v>
+        <v>0.5822581982822064</v>
       </c>
       <c r="L82" t="n">
-        <v>0.5830713692718481</v>
+        <v>0.583071374054754</v>
       </c>
       <c r="M82" t="n">
-        <v>0.5111293151775895</v>
+        <v>0.5111305381518405</v>
       </c>
       <c r="N82" t="n">
-        <v>0.1383307409555058</v>
+        <v>0.1383313555070786</v>
       </c>
       <c r="O82" t="n">
-        <v>4.604393606839464</v>
+        <v>4.604393211905809</v>
       </c>
       <c r="P82" t="n">
-        <v>4.610443667869723</v>
+        <v>4.610443703455973</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.963308714175231</v>
+        <v>0.963308811121825</v>
       </c>
       <c r="R82" t="n">
-        <v>0.02583964416135188</v>
+        <v>0.02583961002464332</v>
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="n">
-        <v>0.8993020125474719</v>
+        <v>0.8993024012460036</v>
       </c>
       <c r="U82" t="n">
-        <v>0.04954346078878032</v>
+        <v>0.04954336516875091</v>
       </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>0.8932479277357017</v>
+        <v>0.8932478331713997</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.02187715314737478</v>
+        <v>0.02187716284714171</v>
       </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
-        <v>-0.6067829403559379</v>
+        <v>-0.6067836208092188</v>
       </c>
       <c r="AD82" t="n">
-        <v>0.003720342040132102</v>
+        <v>0.003720342827892108</v>
       </c>
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="n">
-        <v>0.7402802853326962</v>
+        <v>0.7402801837046775</v>
       </c>
       <c r="AG82" t="n">
-        <v>0.01833463359107143</v>
+        <v>0.01833463715284311</v>
       </c>
       <c r="AH82" t="inlineStr"/>
       <c r="AI82" t="n">
-        <v>0.9802022669412829</v>
+        <v>0.9802022336376627</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.007434512852158392</v>
+        <v>0.007434519107529168</v>
       </c>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
@@ -9133,85 +9133,85 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>0.3465778704093958</v>
+        <v>0.3465778699121797</v>
       </c>
       <c r="G83" t="n">
-        <v>0.07437667461883628</v>
+        <v>0.07437667876585422</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2955634795127128</v>
+        <v>0.2955634788718243</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2811992414815186</v>
+        <v>0.2811992393986867</v>
       </c>
       <c r="J83" t="n">
-        <v>0.002282733977536599</v>
+        <v>0.002282733051455125</v>
       </c>
       <c r="K83" t="n">
-        <v>0.5876714572894921</v>
+        <v>0.5876711610174999</v>
       </c>
       <c r="L83" t="n">
-        <v>0.5692117569781444</v>
+        <v>0.5692111746833854</v>
       </c>
       <c r="M83" t="n">
-        <v>0.07981456649599261</v>
+        <v>0.07981405005481879</v>
       </c>
       <c r="N83" t="n">
-        <v>0.002585205517971454</v>
+        <v>0.00258517746598597</v>
       </c>
       <c r="O83" t="n">
-        <v>4.644667992207475</v>
+        <v>4.64466578813065</v>
       </c>
       <c r="P83" t="n">
-        <v>4.507289777567745</v>
+        <v>4.507285443694283</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.9773624851312184</v>
+        <v>0.9773624111496315</v>
       </c>
       <c r="R83" t="n">
-        <v>0.01801346049152716</v>
+        <v>0.01801348991564184</v>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="n">
-        <v>0.9289935652030937</v>
+        <v>0.928993207205614</v>
       </c>
       <c r="U83" t="n">
-        <v>0.03453482350741809</v>
+        <v>0.03453491056547301</v>
       </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="n">
-        <v>0.9554906605334325</v>
+        <v>0.9554909373331476</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.01017329547634024</v>
+        <v>0.01017326381705235</v>
       </c>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
-        <v>0.6753332431721435</v>
+        <v>0.6753332243193895</v>
       </c>
       <c r="AD83" t="n">
-        <v>0.006368397836927414</v>
+        <v>0.006368398197519705</v>
       </c>
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="n">
-        <v>0.9250070261678919</v>
+        <v>0.9250071181740473</v>
       </c>
       <c r="AG83" t="n">
-        <v>0.01051240757884076</v>
+        <v>0.01051240109012383</v>
       </c>
       <c r="AH83" t="inlineStr"/>
       <c r="AI83" t="n">
-        <v>0.8739360413416268</v>
+        <v>0.8739359926669195</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.01323656355511342</v>
+        <v>0.01323656594310912</v>
       </c>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
@@ -9235,85 +9235,85 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>0.4410213099976569</v>
+        <v>0.4410213107040933</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0196358885772423</v>
+        <v>0.01963588269307707</v>
       </c>
       <c r="H84" t="n">
-        <v>0.3091324863805823</v>
+        <v>0.3091324872855457</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2286307167377633</v>
+        <v>0.2286307196912758</v>
       </c>
       <c r="J84" t="n">
-        <v>0.001579598306755124</v>
+        <v>0.001579599626008144</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5796778824583331</v>
+        <v>0.5796762487829182</v>
       </c>
       <c r="L84" t="n">
-        <v>0.563378885391299</v>
+        <v>0.5633789428613065</v>
       </c>
       <c r="M84" t="n">
-        <v>0.4887897418573557</v>
+        <v>0.4887899657334356</v>
       </c>
       <c r="N84" t="n">
-        <v>0.06502288007868076</v>
+        <v>0.06502296486764629</v>
       </c>
       <c r="O84" t="n">
-        <v>4.58519307493649</v>
+        <v>4.585180918231568</v>
       </c>
       <c r="P84" t="n">
-        <v>4.463870603773183</v>
+        <v>4.463871032620242</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.9980618652316851</v>
+        <v>0.9980618679395555</v>
       </c>
       <c r="R84" t="n">
-        <v>0.005169906999916839</v>
+        <v>0.005169903395306348</v>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="n">
-        <v>0.9972558346115841</v>
+        <v>0.9972558443485855</v>
       </c>
       <c r="U84" t="n">
-        <v>0.00700629324243527</v>
+        <v>0.007006280812363082</v>
       </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="n">
-        <v>0.9957378997957589</v>
+        <v>0.9957379154796772</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.004453930251991188</v>
+        <v>0.004453922065872308</v>
       </c>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
-        <v>0.9849722483041821</v>
+        <v>0.9849722621035858</v>
       </c>
       <c r="AD84" t="n">
-        <v>0.001109863325018791</v>
+        <v>0.001109862958344243</v>
       </c>
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="n">
-        <v>0.9656581688568103</v>
+        <v>0.9656581475019534</v>
       </c>
       <c r="AG84" t="n">
-        <v>0.007637545868635714</v>
+        <v>0.007637548277635458</v>
       </c>
       <c r="AH84" t="inlineStr"/>
       <c r="AI84" t="n">
-        <v>0.9950362094096518</v>
+        <v>0.9950361857284807</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.002269393917902525</v>
+        <v>0.00226939937294698</v>
       </c>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
@@ -9337,85 +9337,87 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>21</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>46.1</v>
+      </c>
       <c r="F85" t="n">
-        <v>0.5131512316840431</v>
+        <v>0.510053670891675</v>
       </c>
       <c r="G85" t="n">
-        <v>6.514458245503142e-16</v>
+        <v>0.06886340942740074</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2632803536988662</v>
+        <v>0.2213241491814443</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2235684146170903</v>
+        <v>0.19975877049948</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-17</v>
       </c>
       <c r="K85" t="n">
-        <v>0.5746033622443787</v>
+        <v>0.5615034371120724</v>
       </c>
       <c r="L85" t="n">
-        <v>0.5683264924564659</v>
+        <v>0.5578854690679895</v>
       </c>
       <c r="M85" t="n">
-        <v>0.1499511902499464</v>
+        <v>0.1374206744038114</v>
       </c>
       <c r="N85" t="n">
-        <v>0.005244004775718696</v>
+        <v>0.007151981664388713</v>
       </c>
       <c r="O85" t="n">
-        <v>4.54742871756644</v>
+        <v>4.449909121929075</v>
       </c>
       <c r="P85" t="n">
-        <v>4.500705163438571</v>
+        <v>4.422967786286185</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.9935362787147766</v>
+        <v>0.9946332071447892</v>
       </c>
       <c r="R85" t="n">
-        <v>0.0100477212629602</v>
+        <v>0.009267542336519502</v>
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="n">
-        <v>0.9807012436553757</v>
+        <v>0.9837711100363621</v>
       </c>
       <c r="U85" t="n">
-        <v>0.0178347464801778</v>
+        <v>0.01797955813250562</v>
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="n">
-        <v>0.9849304295659268</v>
+        <v>0.9939907239732956</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.009460064208359369</v>
+        <v>0.006305055710757827</v>
       </c>
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
-        <v>0.7662515113579828</v>
+        <v>0.84467780451781</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.007555128198113705</v>
+        <v>0.003138922751749275</v>
       </c>
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="n">
-        <v>0.9692067255052649</v>
+        <v>0.9541446877862595</v>
       </c>
       <c r="AG85" t="n">
-        <v>0.005667696465736062</v>
+        <v>0.006585372945582395</v>
       </c>
       <c r="AH85" t="inlineStr"/>
       <c r="AI85" t="n">
-        <v>0.9901688672941981</v>
+        <v>0.9797928648687496</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.002830153835848248</v>
+        <v>0.003632973130390608</v>
       </c>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
@@ -9439,85 +9441,87 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>21</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>10.7</v>
+      </c>
+      <c r="E86" t="n">
+        <v>45.1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0.3947553823403973</v>
+        <v>0.3945200239537214</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0245670665763035</v>
+        <v>0.07039031429275332</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3466305638791009</v>
+        <v>0.3115441195160394</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2327646937884924</v>
+        <v>0.2235455422374857</v>
       </c>
       <c r="J86" t="n">
-        <v>0.001282293415705915</v>
+        <v>4.155543639229597e-17</v>
       </c>
       <c r="K86" t="n">
-        <v>0.5894067212606844</v>
+        <v>0.5764761960078989</v>
       </c>
       <c r="L86" t="n">
-        <v>0.5676365455263553</v>
+        <v>0.5626075481741253</v>
       </c>
       <c r="M86" t="n">
-        <v>0.164012961575661</v>
+        <v>0.2236869670510078</v>
       </c>
       <c r="N86" t="n">
-        <v>0.005908826605035044</v>
+        <v>0.02024977701811836</v>
       </c>
       <c r="O86" t="n">
-        <v>4.65757690113081</v>
+        <v>4.561367017387481</v>
       </c>
       <c r="P86" t="n">
-        <v>4.495557844070868</v>
+        <v>4.458127471421912</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.99596761356452</v>
+        <v>0.9939870998300049</v>
       </c>
       <c r="R86" t="n">
-        <v>0.007573593973731987</v>
+        <v>0.009644835525950544</v>
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="n">
-        <v>0.9929286106879106</v>
+        <v>0.9854212993314668</v>
       </c>
       <c r="U86" t="n">
-        <v>0.01168885349986235</v>
+        <v>0.01877801437471045</v>
       </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="n">
-        <v>0.9954974462410984</v>
+        <v>0.9920031904956575</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.003903167956676739</v>
+        <v>0.005686994656156489</v>
       </c>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
-        <v>0.6317332072218212</v>
+        <v>0.9536749340516423</v>
       </c>
       <c r="AD86" t="n">
-        <v>0.009083611398404412</v>
+        <v>0.001809131631676832</v>
       </c>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="n">
-        <v>0.9900788421902922</v>
+        <v>0.9736552143445716</v>
       </c>
       <c r="AG86" t="n">
-        <v>0.005092426417373469</v>
+        <v>0.008485146562773088</v>
       </c>
       <c r="AH86" t="inlineStr"/>
       <c r="AI86" t="n">
-        <v>0.9749218023384573</v>
+        <v>0.995500854200584</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.005146630869014135</v>
+        <v>0.002210850534235695</v>
       </c>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
@@ -9541,85 +9545,87 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>21</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E87" t="n">
+        <v>57.4</v>
+      </c>
       <c r="F87" t="n">
-        <v>0.3717923415656336</v>
+        <v>0.3694757755244492</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>0.05530667551573475</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3014084132402625</v>
+        <v>0.2674527900009642</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3267992451941039</v>
+        <v>0.3077647589588519</v>
       </c>
       <c r="J87" t="n">
-        <v>1.327388309752159e-16</v>
+        <v>2.355429219724758e-17</v>
       </c>
       <c r="K87" t="n">
-        <v>0.5852585427094423</v>
+        <v>0.582386435138936</v>
       </c>
       <c r="L87" t="n">
-        <v>0.5859857945326804</v>
+        <v>0.5828529195968669</v>
       </c>
       <c r="M87" t="n">
-        <v>0.7690944556535395</v>
+        <v>0.4927907878033703</v>
       </c>
       <c r="N87" t="n">
-        <v>0.2037190790581341</v>
+        <v>0.1151876543389149</v>
       </c>
       <c r="O87" t="n">
-        <v>4.675916314716923</v>
+        <v>4.605347379894655</v>
       </c>
       <c r="P87" t="n">
-        <v>4.634914678866079</v>
+        <v>4.608818293484929</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.9654542854591001</v>
+        <v>0.9605457948807634</v>
       </c>
       <c r="R87" t="n">
-        <v>0.02083653717399546</v>
+        <v>0.02656236780485897</v>
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="n">
-        <v>0.9138792276411978</v>
+        <v>0.9036138448584889</v>
       </c>
       <c r="U87" t="n">
-        <v>0.03805170690026567</v>
+        <v>0.05121047533681464</v>
       </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="n">
-        <v>0.8841444013148053</v>
+        <v>0.9058839699845952</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.01902384117889745</v>
+        <v>0.0210432905395345</v>
       </c>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
-        <v>0.9259497523490778</v>
+        <v>-0.4563972053958567</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.003189701762696498</v>
+        <v>0.004721154690121919</v>
       </c>
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="n">
-        <v>0.745779150959581</v>
+        <v>0.7645954992811939</v>
       </c>
       <c r="AG87" t="n">
-        <v>0.01781453076027997</v>
+        <v>0.01938843223235958</v>
       </c>
       <c r="AH87" t="inlineStr"/>
       <c r="AI87" t="n">
-        <v>0.9867903147446578</v>
+        <v>0.9784431163112512</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.00578236735679459</v>
+        <v>0.008016448715760618</v>
       </c>
       <c r="AK87" t="inlineStr"/>
       <c r="AL87" t="inlineStr"/>
@@ -9643,85 +9649,87 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>21</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>13.7</v>
+      </c>
+      <c r="E88" t="n">
+        <v>53.2</v>
+      </c>
       <c r="F88" t="n">
-        <v>0.3917057203335357</v>
+        <v>0.3890440313612025</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>0.05967299200381906</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2685425476164555</v>
+        <v>0.2320759063377122</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3397517320500086</v>
+        <v>0.3192070702972664</v>
       </c>
       <c r="J88" t="n">
-        <v>1.912261794240524e-16</v>
+        <v>2.419504177564497e-17</v>
       </c>
       <c r="K88" t="n">
-        <v>0.590586229268512</v>
+        <v>0.5835775281999703</v>
       </c>
       <c r="L88" t="n">
-        <v>0.5714000476581824</v>
+        <v>0.5693202595258983</v>
       </c>
       <c r="M88" t="n">
-        <v>0.7351866714466452</v>
+        <v>0.349979228327973</v>
       </c>
       <c r="N88" t="n">
-        <v>0.08236529828281203</v>
+        <v>0.05758430619441923</v>
       </c>
       <c r="O88" t="n">
-        <v>4.666351041259506</v>
+        <v>4.614209716329934</v>
       </c>
       <c r="P88" t="n">
-        <v>4.523585173738249</v>
+        <v>4.508104622358899</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.9878274091918079</v>
+        <v>0.9880002298195961</v>
       </c>
       <c r="R88" t="n">
-        <v>0.01293543913470825</v>
+        <v>0.01473763906301795</v>
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="n">
-        <v>0.9644307692616069</v>
+        <v>0.9668903192728275</v>
       </c>
       <c r="U88" t="n">
-        <v>0.02377018461083583</v>
+        <v>0.02827245263696845</v>
       </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="n">
-        <v>0.9660910220376986</v>
+        <v>0.9697217369354986</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.01041887678790007</v>
+        <v>0.01183660496829356</v>
       </c>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
-        <v>-0.02401621413803712</v>
+        <v>0.9841367060578801</v>
       </c>
       <c r="AD88" t="n">
-        <v>0.006312291788673499</v>
+        <v>0.0007719705233563555</v>
       </c>
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="n">
-        <v>0.977555910915916</v>
+        <v>0.9640092858398088</v>
       </c>
       <c r="AG88" t="n">
-        <v>0.004465398413132405</v>
+        <v>0.006206369805255847</v>
       </c>
       <c r="AH88" t="inlineStr"/>
       <c r="AI88" t="n">
-        <v>0.9502231692949223</v>
+        <v>0.9582368764482156</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.01016210841659788</v>
+        <v>0.0103652431628681</v>
       </c>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
@@ -9745,85 +9753,85 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>21</v>
+        <v>22.9</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>0.468689526729295</v>
+        <v>0.4686895267262085</v>
       </c>
       <c r="G89" t="n">
-        <v>3.650881409255485e-16</v>
+        <v>2.428629807026475e-16</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1956707823068736</v>
+        <v>0.1956707823126708</v>
       </c>
       <c r="I89" t="n">
-        <v>0.335639690963831</v>
+        <v>0.3356396909611205</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.5779806317272085</v>
+        <v>0.5779818598694213</v>
       </c>
       <c r="L89" t="n">
-        <v>0.5697550295019791</v>
+        <v>0.5697895908149949</v>
       </c>
       <c r="M89" t="n">
-        <v>0.5626937765709654</v>
+        <v>0.5626688042349643</v>
       </c>
       <c r="N89" t="n">
-        <v>0.06639920394480998</v>
+        <v>0.06639387629390034</v>
       </c>
       <c r="O89" t="n">
-        <v>4.572562927515825</v>
+        <v>4.572572067036488</v>
       </c>
       <c r="P89" t="n">
-        <v>4.511340762019881</v>
+        <v>4.511598028851128</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.9966650542560334</v>
+        <v>0.9966671200450411</v>
       </c>
       <c r="R89" t="n">
-        <v>0.006834005921347447</v>
+        <v>0.006831888980499494</v>
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="n">
-        <v>0.9949552893220264</v>
+        <v>0.9949637316815912</v>
       </c>
       <c r="U89" t="n">
-        <v>0.009706454197730939</v>
+        <v>0.009698328886446362</v>
       </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
-        <v>0.9975449749781534</v>
+        <v>0.997543552822342</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.003775952041262557</v>
+        <v>0.003777045558003603</v>
       </c>
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
-        <v>0.9174350813537422</v>
+        <v>0.9174346675637157</v>
       </c>
       <c r="AD89" t="n">
-        <v>0.002784664113660759</v>
+        <v>0.002784670831294355</v>
       </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="n">
-        <v>0.9931407185205504</v>
+        <v>0.9931404938034072</v>
       </c>
       <c r="AG89" t="n">
-        <v>0.002012199181207847</v>
+        <v>0.00201223214965561</v>
       </c>
       <c r="AH89" t="inlineStr"/>
       <c r="AI89" t="n">
-        <v>0.9453163248355907</v>
+        <v>0.9453141080559704</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.01064151389529388</v>
+        <v>0.01064172960611518</v>
       </c>
       <c r="AK89" t="inlineStr"/>
       <c r="AL89" t="inlineStr"/>
@@ -9849,83 +9857,87 @@
       <c r="D90" t="n">
         <v>12.8</v>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>30.13605442176871</v>
+      </c>
       <c r="F90" t="n">
-        <v>0.6963378304438156</v>
+        <v>0.6739262842370797</v>
       </c>
       <c r="G90" t="n">
-        <v>0.06121827372612768</v>
+        <v>0.1053423626787058</v>
       </c>
       <c r="H90" t="n">
-        <v>0.04157121397092656</v>
+        <v>0.01105388716074765</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1708251520974169</v>
+        <v>0.1819763294359777</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03004752976171331</v>
+        <v>0.02770113648748916</v>
       </c>
       <c r="K90" t="n">
-        <v>0.5729495712298517</v>
+        <v>0.5785262774142708</v>
       </c>
       <c r="L90" t="n">
-        <v>0.5382134011256914</v>
+        <v>0.5408044316763888</v>
       </c>
       <c r="M90" t="n">
-        <v>0.6654125091509961</v>
+        <v>0.2256119953121207</v>
       </c>
       <c r="N90" t="n">
-        <v>0.1308745974910419</v>
+        <v>0.010836397288736</v>
       </c>
       <c r="O90" t="n">
-        <v>4.535119873192954</v>
+        <v>4.576623446244543</v>
       </c>
       <c r="P90" t="n">
-        <v>4.276387088985127</v>
+        <v>4.295695539159383</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.9895602482751137</v>
+        <v>0.9848273902572762</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01351091845765313</v>
+        <v>0.01462478832947895</v>
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="n">
-        <v>0.9806794056833744</v>
+        <v>0.9667031730126348</v>
       </c>
       <c r="U90" t="n">
-        <v>0.02251106944082309</v>
+        <v>0.02657555333772617</v>
       </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
+      <c r="X90" t="n">
+        <v>5.204170427930421e-18</v>
+      </c>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="n">
-        <v>0.9877028042845071</v>
+        <v>0.9895825022361832</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.0143254444219854</v>
+        <v>0.01109160630401993</v>
       </c>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
-        <v>0.8339382169405896</v>
+        <v>0.8667235203573421</v>
       </c>
       <c r="AD90" t="n">
-        <v>0.004642818150404649</v>
+        <v>0.005676344694925368</v>
       </c>
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="n">
-        <v>0.9949739767678161</v>
+        <v>0.9549113405368338</v>
       </c>
       <c r="AG90" t="n">
-        <v>0.0005399858509917179</v>
+        <v>0.0007010170948513971</v>
       </c>
       <c r="AH90" t="inlineStr"/>
       <c r="AI90" t="n">
-        <v>0.9843548440065371</v>
+        <v>0.98444957265355</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.004099874704513088</v>
+        <v>0.003835283092043795</v>
       </c>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>
